--- a/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>87</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5810</v>
+        <v>7725</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4413</v>
+        <v>5837</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2782</v>
+        <v>3691</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>778</v>
+        <v>1030</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>685</v>
+        <v>941</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>175</v>
+        <v>233</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>183</v>
+        <v>303</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>677</v>
+        <v>901</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>305</v>
+        <v>397</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>342</v>
+        <v>438</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>402</v>
+        <v>519</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>389</v>
+        <v>527</v>
       </c>
       <c r="G12" s="12" t="n">
+        <v>196</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>372</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>396</v>
+      </c>
+      <c r="J12" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="H12" s="12" t="n">
-        <v>273</v>
-      </c>
-      <c r="I12" s="12" t="n">
-        <v>301</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>116</v>
-      </c>
       <c r="K12" s="12" t="n">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>354</v>
+        <v>458</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>384</v>
+        <v>493</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>263</v>
+        <v>380</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>336</v>
+        <v>391</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>508</v>
+        <v>684</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>300</v>
+        <v>377</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>395</v>
+        <v>562</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>273</v>
+        <v>367</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>396</v>
+        <v>507</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>267</v>
+        <v>376</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>438</v>
+        <v>578</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>213</v>
+        <v>285</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>249</v>
+        <v>347</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>225</v>
+        <v>286</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>130</v>
+        <v>237</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>307</v>
+        <v>386</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>175</v>
+        <v>233</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>174</v>
+        <v>234</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1072,12 +1072,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05112</t>
+          <t>58414</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>LUCCA</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,51 +1087,51 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>181</v>
+        <v>226</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H16" s="12" t="n">
+        <v>127</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>139</v>
+      </c>
+      <c r="J16" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="I16" s="12" t="n">
-        <v>154</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>68</v>
-      </c>
       <c r="K16" s="12" t="n">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>137</v>
+        <v>274</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>58414</t>
+          <t>05112</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>LUCCA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,51 +1141,51 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>169</v>
+        <v>221</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>112</v>
+        <v>282</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>06334</t>
+          <t>04845</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VIGNOLA</t>
+          <t>FUCECCHIO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,51 +1195,51 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>158</v>
+        <v>204</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>107</v>
+        <v>235</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>05291</t>
+          <t>06334</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>PISA</t>
+          <t>VIGNOLA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,35 +1249,35 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>37</v>
+        <v>148</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1288,12 +1288,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>04845</t>
+          <t>05291</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FUCECCHIO</t>
+          <t>PISA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,35 +1303,35 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>166</v>
+        <v>252</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>8</v>
+        <v>176</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>106</v>
+        <v>157</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>85</v>
+        <v>169</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1361,28 +1361,28 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>131</v>
+        <v>180</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>4</v>
@@ -1396,12 +1396,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05054</t>
+          <t>06249</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ROSIGNANO MARITTIMO</t>
+          <t>SASSUOLO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,39 +1411,39 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>104</v>
+        <v>188</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>50</v>
+        <v>240</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>45</v>
+        <v>307</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>113</v>
+        <v>184</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>06249</t>
+          <t>05054</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SASSUOLO</t>
+          <t>ROSIGNANO MARITTIMO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,51 +1519,51 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>191</v>
+        <v>58</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>225</v>
+        <v>86</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>34710</t>
+          <t>05245</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>VECCHIANO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,35 +1573,35 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>122</v>
+        <v>33</v>
       </c>
       <c r="G25" s="12" t="n">
+        <v>129</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="K25" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H25" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="K25" s="12" t="n">
-        <v>27</v>
-      </c>
       <c r="L25" s="12" t="n">
-        <v>262</v>
+        <v>104</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1612,12 +1612,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>05245</t>
+          <t>34710</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>VECCHIANO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,39 +1627,39 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>18</v>
+        <v>178</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>69</v>
+        <v>353</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1685,31 +1685,31 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="G27" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="K27" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="L27" s="12" t="n">
+        <v>185</v>
+      </c>
+      <c r="M27" s="12" t="n">
         <v>5</v>
-      </c>
-      <c r="H27" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="I27" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="J27" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="K27" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="L27" s="12" t="n">
-        <v>146</v>
-      </c>
-      <c r="M27" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>05911</t>
+          <t>05349</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>PISTOIA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,51 +1735,51 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>63</v>
+        <v>235</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>34723</t>
+          <t>06019</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>MISANO ADRIATICO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,35 +1789,35 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>198</v>
+        <v>139</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1828,12 +1828,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,35 +1843,35 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>190</v>
+        <v>2</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>177</v>
+        <v>276</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1882,12 +1882,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05349</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>PISTOIA</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,51 +1897,51 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>166</v>
+        <v>50</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>12</v>
+        <v>236</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>29</v>
+        <v>165</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>146</v>
+        <v>237</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04634</t>
+          <t>05911</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI VALDARNO</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06019</t>
+          <t>25554</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>MISANO ADRIATICO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,39 +2005,39 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>98</v>
+        <v>214</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2063,47 +2063,47 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>06416</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,35 +2113,35 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2152,12 +2152,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>06416</t>
+          <t>04634</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>SAN GIOVANNI VALDARNO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,51 +2167,51 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>66</v>
+        <v>127</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>65</v>
+        <v>148</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>06210</t>
+          <t>04892</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CARPI</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,51 +2221,51 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>50</v>
+        <v>149</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>47</v>
+        <v>117</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>04892</t>
+          <t>53970</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,35 +2275,35 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2314,12 +2314,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>05239</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>PIOMBINO</t>
+          <t>SAN MINIATO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,35 +2329,35 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2368,12 +2368,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>53970</t>
+          <t>06210</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>CARPI</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,35 +2383,35 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2422,12 +2422,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>05543</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SASSO MARCONI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,51 +2437,51 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="F41" s="12" t="n">
+        <v>112</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="I41" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="G41" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="H41" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="I41" s="12" t="n">
-        <v>43</v>
-      </c>
       <c r="J41" s="12" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>05239</t>
+          <t>04516</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SAN MINIATO</t>
+          <t>CARRARA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,35 +2491,35 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2530,12 +2530,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>58000</t>
+          <t>53676</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>MIRANDOLA</t>
+          <t>PIOMBINO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2545,51 +2545,51 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="J43" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K43" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L43" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="M43" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K43" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="L43" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="M43" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>34802</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>PRATO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,35 +2599,35 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="F44" s="12" t="n">
         <v>90</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2657,31 +2657,31 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F45" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="G45" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="G45" s="12" t="n">
+      <c r="H45" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="H45" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="I45" s="12" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2692,12 +2692,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04516</t>
+          <t>05941</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>CARRARA</t>
+          <t>FORLÌ</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,51 +2707,51 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>1</v>
+        <v>291</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>45</v>
+        <v>114</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>34802</t>
+          <t>05514</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>PRATO</t>
+          <t>SAN GIOVANNI IN PERSICETO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,51 +2761,51 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="H47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="J47" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K47" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L47" s="12" t="n">
+        <v>101</v>
+      </c>
+      <c r="M47" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="I47" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="J47" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="K47" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L47" s="12" t="n">
-        <v>95</v>
-      </c>
-      <c r="M47" s="12" t="n">
-        <v>43</v>
-      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>55420</t>
+          <t>05543</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SASSO MARCONI</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,39 +2815,39 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F48" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="G48" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="G48" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="H48" s="12" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2873,31 +2873,31 @@
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -2908,12 +2908,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>06403</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>GUASTALLA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,35 +2923,35 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
@@ -2962,12 +2962,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>05941</t>
+          <t>58000</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>FORLÌ</t>
+          <t>MIRANDOLA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,51 +2977,51 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>204</v>
+        <v>17</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J51" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K51" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="L51" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="M51" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K51" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L51" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="M51" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>05536</t>
+          <t>06403</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>GUASTALLA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3031,35 +3031,35 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F52" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H52" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I52" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="J52" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="K52" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L52" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="M52" s="12" t="n">
         <v>40</v>
-      </c>
-      <c r="F52" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="G52" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="H52" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="I52" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="J52" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="K52" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L52" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="M52" s="12" t="n">
-        <v>21</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -3070,12 +3070,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>04951</t>
+          <t>55420</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>GROSSETO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,51 +3085,51 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>05514</t>
+          <t>05829</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI IN PERSICETO</t>
+          <t>FERRARA</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>04951</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>GROSSETO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,35 +3193,35 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="J55" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K55" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K55" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="L55" s="12" t="n">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
@@ -3232,12 +3232,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>05408</t>
+          <t>05536</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>CHIUSI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,35 +3247,35 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F56" s="12" t="n">
         <v>41</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
@@ -3286,12 +3286,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>04653</t>
+          <t>05408</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLION FIORENTINO</t>
+          <t>CHIUSI</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,51 +3301,51 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H57" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="I57" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="J57" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I57" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="J57" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="K57" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>MONTECCHIO EMILIA</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3359,31 +3359,31 @@
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F58" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="G58" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H58" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I58" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="G58" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="H58" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="I58" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="J58" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
@@ -3394,12 +3394,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05829</t>
+          <t>05290</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>FERRARA</t>
+          <t>PONTEDERA</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,51 +3409,51 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MONTECCHIO EMILIA</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,35 +3463,35 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
@@ -3502,12 +3502,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>54101</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>CECINA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,35 +3517,35 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I61" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="J61" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K61" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L61" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="M61" s="12" t="n">
         <v>18</v>
-      </c>
-      <c r="J61" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K61" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L61" s="12" t="n">
-        <v>71</v>
-      </c>
-      <c r="M61" s="12" t="n">
-        <v>7</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
@@ -3556,12 +3556,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,35 +3571,35 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
@@ -3610,12 +3610,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>05290</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>PONTEDERA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,51 +3625,51 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J63" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>04812</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,35 +3679,35 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>38</v>
+        <v>126</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3718,12 +3718,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,51 +3733,51 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G65" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H65" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="I65" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="J65" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K65" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L65" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="M65" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H65" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="J65" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="K65" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L65" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="M65" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>04812</t>
+          <t>06446</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,35 +3787,35 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H66" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="J66" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K66" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I66" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="J66" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K66" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="L66" s="12" t="n">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
@@ -3826,12 +3826,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>34201</t>
+          <t>04653</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SANTA CROCE SULL'ARNO</t>
+          <t>CASTIGLION FIORENTINO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3841,51 +3841,51 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K67" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SAN LAZZARO DI SAVENA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,51 +3895,51 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J68" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="M68" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05530</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3949,51 +3949,51 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K69" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L69" s="12" t="n">
+        <v>97</v>
+      </c>
+      <c r="M69" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L69" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="M69" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>05099</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>SANTA CROCE SULL'ARNO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4003,35 +4003,35 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
@@ -4042,12 +4042,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>MALALBERGO</t>
+          <t>SAN LAZZARO DI SAVENA</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4057,51 +4057,51 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K71" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="M71" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>54101</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>CECINA</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,35 +4111,35 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H72" s="12" t="n">
         <v>41</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
@@ -4150,12 +4150,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>04978</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SCARLINO</t>
+          <t>MALALBERGO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4165,51 +4165,51 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06446</t>
+          <t>05530</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4219,51 +4219,51 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="H74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>54479</t>
+          <t>04601</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>BENTIVOGLIO</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4273,51 +4273,51 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G75" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H75" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I75" s="12" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>04601</t>
+          <t>04978</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>SCARLINO</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4327,35 +4327,35 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K76" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
@@ -4366,12 +4366,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>05099</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4381,35 +4381,35 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H77" s="12" t="n">
         <v>23</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
@@ -4420,12 +4420,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>54479</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>BENTIVOGLIO</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4435,51 +4435,51 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="I78" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J78" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K78" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="J78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="L78" s="12" t="n">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>06259</t>
+          <t>53490</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>SANT'ILARIO D'ENZA</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4489,35 +4489,35 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J79" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>54593</t>
+          <t>06259</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4543,51 +4543,51 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F80" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="G80" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="F80" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="G80" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H80" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>25518</t>
+          <t>04677</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>CASALECCHIO DI RENO</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4597,51 +4597,51 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>TODESCATO MARCO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F81" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G81" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="12" t="n">
+      <c r="I81" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J81" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K81" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L81" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="M81" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I81" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J81" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K81" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="M81" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05512</t>
+          <t>54066</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN PIETRO TERME</t>
+          <t>PIETRASANTA</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4651,35 +4651,35 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J82" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
@@ -4690,12 +4690,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>54066</t>
+          <t>05589</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>PIETRASANTA</t>
+          <t>ZOLA PREDOSA</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4705,51 +4705,51 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>05589</t>
+          <t>54593</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>ZOLA PREDOSA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4759,51 +4759,51 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04677</t>
+          <t>25518</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>CASALECCHIO DI RENO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4813,51 +4813,51 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>TODESCATO MARCO</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F85" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F85" s="12" t="n">
-        <v>33</v>
-      </c>
       <c r="G85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>05160</t>
+          <t>05512</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>BORGO A MOZZANO</t>
+          <t>CASTEL SAN PIETRO TERME</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4867,51 +4867,51 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="F86" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="G86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I86" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F86" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="G86" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H86" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I86" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="J86" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="M86" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>53490</t>
+          <t>05160</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SANT'ILARIO D'ENZA</t>
+          <t>BORGO A MOZZANO</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4921,23 +4921,23 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G87" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H87" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="I87" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J87" s="12" t="n">
         <v>1</v>
@@ -4946,14 +4946,14 @@
         <v>0</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F88" s="12" t="n">
         <v>0</v>
@@ -4991,16 +4991,16 @@
         <v>0</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M88" s="12" t="n">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         <v>0</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I89" s="12" t="n">
         <v>0</v>
@@ -5090,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="G90" s="12" t="n">
         <v>0</v>
@@ -5144,13 +5144,13 @@
         <v>0</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="G91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H91" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I91" s="12" t="n">
         <v>0</v>
@@ -5198,13 +5198,13 @@
         <v>0</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="G92" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="I92" s="12" t="n">
         <v>0</v>
@@ -5252,13 +5252,13 @@
         <v>0</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G93" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H93" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I93" s="12" t="n">
         <v>0</v>
@@ -5306,13 +5306,13 @@
         <v>0</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>192</v>
+        <v>271</v>
       </c>
       <c r="G94" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>326</v>
+        <v>433</v>
       </c>
       <c r="I94" s="12" t="n">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="G95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H95" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I95" s="12" t="n">
         <v>0</v>
@@ -5414,13 +5414,13 @@
         <v>0</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G96" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I96" s="12" t="n">
         <v>0</v>
@@ -5468,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G97" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>438</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.0593607305936073</v>
+        <v>26</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>458</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.2620087336244541</v>
+        <v>120</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>562</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.300711743772242</v>
+        <v>169</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>347</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.005763688760806916</v>
+        <v>2</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>234</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.03846153846153846</v>
+        <v>9</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>274</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.0218978102189781</v>
+        <v>6</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>182</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.005494505494505495</v>
+        <v>1</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>120</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.4916666666666666</v>
+        <v>59</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>184</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.4239130434782609</v>
+        <v>78</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>169</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.0650887573964497</v>
+        <v>11</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>137</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.0291970802919708</v>
+        <v>4</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>184</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.05434782608695652</v>
+        <v>10</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>164</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.1951219512195122</v>
+        <v>32</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>151</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.03311258278145696</v>
+        <v>5</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>104</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.09615384615384616</v>
+        <v>10</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>353</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.0084985835694051</v>
+        <v>3</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>185</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.02702702702702703</v>
+        <v>5</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>208</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.09615384615384616</v>
+        <v>20</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>139</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.04316546762589928</v>
+        <v>6</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>276</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0.0108695652173913</v>
+        <v>3</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>237</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>0.008438818565400843</v>
+        <v>2</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>80</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>0.025</v>
+        <v>2</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>214</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>0.3551401869158878</v>
+        <v>76</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>90</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>0.07777777777777778</v>
+        <v>7</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>117</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>0.3076923076923077</v>
+        <v>36</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>129</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>0.2248062015503876</v>
+        <v>29</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>83</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>0.04819277108433735</v>
+        <v>4</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>70</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>0.1285714285714286</v>
+        <v>9</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>138</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>0.01449275362318841</v>
+        <v>2</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>64</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>0.1875</v>
+        <v>12</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>69</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>0.08695652173913043</v>
+        <v>6</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>126</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>0.4444444444444444</v>
+        <v>56</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>117</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>0.3675213675213675</v>
+        <v>43</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>101</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>0.2277227722772277</v>
+        <v>23</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>114</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>0.008771929824561403</v>
+        <v>1</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>106</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>0.01886792452830189</v>
+        <v>2</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>86</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>0.2674418604651163</v>
+        <v>23</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>76</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>0.0131578947368421</v>
+        <v>1</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>68</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>0.5882352941176471</v>
+        <v>40</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>65</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>0.03076923076923077</v>
+        <v>2</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>91</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>0.03296703296703297</v>
+        <v>3</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>53</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>0.6792452830188679</v>
+        <v>36</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>76</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>0.02631578947368421</v>
+        <v>2</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>35</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>0.1142857142857143</v>
+        <v>4</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>72</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>0.25</v>
+        <v>18</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>59</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>0.1525423728813559</v>
+        <v>9</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>78</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>0.2307692307692308</v>
+        <v>18</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>126</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>0.07142857142857142</v>
+        <v>9</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>55</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>0.01818181818181818</v>
+        <v>1</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>42</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>0.04761904761904762</v>
+        <v>2</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>31</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>0.03225806451612903</v>
+        <v>1</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>92</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>0.02173913043478261</v>
+        <v>2</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>97</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>0.03092783505154639</v>
+        <v>3</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>75</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>0.02666666666666667</v>
+        <v>2</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>72</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>0.09722222222222222</v>
+        <v>7</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>69</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>0.04347826086956522</v>
+        <v>3</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>57</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>0.01754385964912281</v>
+        <v>1</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>16</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>0.5625</v>
+        <v>9</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>47</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>0.0851063829787234</v>
+        <v>4</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>45</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>0.2444444444444444</v>
+        <v>11</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>55</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>0.1454545454545454</v>
+        <v>8</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>26</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>0.03846153846153846</v>
+        <v>1</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>32</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0.25</v>
+        <v>8</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>95</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0.01052631578947368</v>
+        <v>1</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>42</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>0.02380952380952381</v>
+        <v>1</v>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0.1111111111111111</v>
+        <v>1</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>87</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>7725</v>
+        <v>8167</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5837</v>
+        <v>6166</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3691</v>
+        <v>3913</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,28 +821,28 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>1030</v>
+        <v>1080</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>941</v>
+        <v>1004</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>901</v>
+        <v>947</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>26</v>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>519</v>
+        <v>546</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>527</v>
+        <v>562</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>372</v>
+        <v>401</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>493</v>
+        <v>515</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>380</v>
+        <v>413</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>684</v>
+        <v>736</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>562</v>
+        <v>607</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,28 +983,28 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>507</v>
+        <v>546</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>578</v>
+        <v>626</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>2</v>
@@ -1037,35 +1037,35 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1091,28 +1091,28 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>42</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>6</v>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>282</v>
+        <v>310</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>1</v>
@@ -1199,28 +1199,28 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>59</v>
@@ -1253,35 +1253,35 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>38</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1307,31 +1307,31 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1361,28 +1361,28 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>4</v>
@@ -1415,28 +1415,28 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>37</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>10</v>
@@ -1469,28 +1469,28 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>55</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>32</v>
@@ -1523,31 +1523,31 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>21</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1558,12 +1558,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>05245</t>
+          <t>34710</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>VECCHIANO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,51 +1573,51 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>33</v>
+        <v>195</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>104</v>
+        <v>376</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>34710</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>FAENZA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,51 +1627,51 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>178</v>
+        <v>121</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>353</v>
+        <v>194</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>05245</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>FAENZA</t>
+          <t>VECCHIANO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,51 +1681,51 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>108</v>
+        <v>37</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>185</v>
+        <v>110</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>05349</t>
+          <t>06019</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>PISTOIA</t>
+          <t>MISANO ADRIATICO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,51 +1735,51 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>235</v>
+        <v>110</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>208</v>
+        <v>146</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06019</t>
+          <t>05349</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>MISANO ADRIATICO</t>
+          <t>PISTOIA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,39 +1789,39 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>96</v>
+        <v>249</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>139</v>
+        <v>224</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>0</v>
@@ -1859,16 +1859,16 @@
         <v>0</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>29</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>3</v>
@@ -1882,12 +1882,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>05911</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,51 +1897,51 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>236</v>
+        <v>9</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>165</v>
+        <v>62</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>237</v>
+        <v>89</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>05911</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,32 +1951,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>9</v>
+        <v>241</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>59</v>
+        <v>176</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>80</v>
+        <v>242</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>2</v>
@@ -1990,12 +1990,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>06416</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,35 +2005,35 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>214</v>
+        <v>93</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2044,12 +2044,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>55380</t>
+          <t>25554</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MONTELUPO FIORENTINO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,51 +2059,51 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>109</v>
+        <v>220</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>06416</t>
+          <t>55380</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>MONTELUPO FIORENTINO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,51 +2113,51 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04634</t>
+          <t>04892</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI VALDARNO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,35 +2167,35 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="J36" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="K36" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="K36" s="12" t="n">
-        <v>24</v>
-      </c>
       <c r="L36" s="12" t="n">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2206,12 +2206,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04892</t>
+          <t>04634</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>SAN GIOVANNI VALDARNO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,35 +2221,35 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2279,16 +2279,16 @@
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>8</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I38" s="12" t="n">
         <v>49</v>
@@ -2297,10 +2297,10 @@
         <v>21</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>29</v>
@@ -2333,31 +2333,31 @@
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>16</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2387,31 +2387,31 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>8</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2422,12 +2422,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>34802</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>PRATO</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,35 +2437,35 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G42" s="12" t="n">
         <v>1</v>
@@ -2507,19 +2507,19 @@
         <v>2</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2530,12 +2530,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>PIOMBINO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2545,51 +2545,51 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>69</v>
+        <v>153</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>34802</t>
+          <t>05543</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>PRATO</t>
+          <t>SASSO MARCONI</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,51 +2599,51 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="F44" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="F44" s="12" t="n">
-        <v>90</v>
-      </c>
       <c r="G44" s="12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>53676</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>PIOMBINO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2653,35 +2653,35 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2692,12 +2692,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>05941</t>
+          <t>05514</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>FORLÌ</t>
+          <t>SAN GIOVANNI IN PERSICETO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,51 +2707,51 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>05514</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI IN PERSICETO</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,51 +2761,51 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F47" s="12" t="n">
         <v>71</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>05543</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SASSO MARCONI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,39 +2815,39 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2873,28 +2873,28 @@
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J49" s="12" t="n">
         <v>14</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="M49" s="12" t="n">
         <v>2</v>
@@ -2908,12 +2908,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>05941</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>FORLÌ</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,39 +2923,39 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>31</v>
+        <v>329</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2981,28 +2981,28 @@
         </is>
       </c>
       <c r="E51" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="F51" s="12" t="n">
         <v>60</v>
-      </c>
-      <c r="F51" s="12" t="n">
-        <v>51</v>
       </c>
       <c r="G51" s="12" t="n">
         <v>10</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>29</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>1</v>
@@ -3035,19 +3035,19 @@
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J52" s="12" t="n">
         <v>20</v>
@@ -3056,10 +3056,10 @@
         <v>9</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -3089,19 +3089,19 @@
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H53" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J53" s="12" t="n">
         <v>12</v>
@@ -3110,26 +3110,26 @@
         <v>21</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M53" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>05829</t>
+          <t>04951</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>FERRARA</t>
+          <t>GROSSETO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,14 +3139,14 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G54" s="12" t="n">
         <v>0</v>
@@ -3155,19 +3155,19 @@
         <v>0</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="J54" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K54" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K54" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="L54" s="12" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
@@ -3178,12 +3178,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>04951</t>
+          <t>05829</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>GROSSETO</t>
+          <t>FERRARA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,35 +3193,35 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
@@ -3251,31 +3251,31 @@
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J56" s="12" t="n">
         <v>21</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>45</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G57" s="12" t="n">
         <v>13</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I57" s="12" t="n">
         <v>33</v>
@@ -3326,7 +3326,7 @@
         <v>12</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M57" s="12" t="n">
         <v>2</v>
@@ -3340,12 +3340,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,35 +3355,35 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
@@ -3413,31 +3413,31 @@
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G59" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J59" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
@@ -3448,12 +3448,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>MONTECCHIO EMILIA</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3467,31 +3467,31 @@
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
@@ -3502,12 +3502,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MONTECCHIO EMILIA</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,35 +3517,35 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J61" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K61" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="L61" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="M61" s="12" t="n">
         <v>10</v>
-      </c>
-      <c r="K61" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L61" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="M61" s="12" t="n">
-        <v>18</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
@@ -3575,47 +3575,47 @@
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F62" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H62" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K62" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="M62" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,35 +3625,35 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
         <v>35</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>11</v>
+        <v>109</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="J63" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K63" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L63" s="12" t="n">
+        <v>103</v>
+      </c>
+      <c r="M63" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="K63" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="L63" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="M63" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
@@ -3664,12 +3664,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>04812</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,35 +3679,35 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>126</v>
+        <v>52</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3718,12 +3718,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>04812</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,35 +3733,35 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K65" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>55</v>
+        <v>131</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
@@ -3772,12 +3772,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06446</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,51 +3787,51 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>04653</t>
+          <t>06446</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLION FIORENTINO</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3841,51 +3841,51 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K67" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>04653</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>CASTIGLION FIORENTINO</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,35 +3895,35 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J68" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K68" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K68" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="L68" s="12" t="n">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
@@ -3953,28 +3953,28 @@
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="M69" s="12" t="n">
         <v>3</v>
@@ -4007,16 +4007,16 @@
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G70" s="12" t="n">
         <v>18</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I70" s="12" t="n">
         <v>23</v>
@@ -4025,10 +4025,10 @@
         <v>7</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M70" s="12" t="n">
         <v>0</v>
@@ -4042,12 +4042,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>04601</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SAN LAZZARO DI SAVENA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4057,51 +4057,51 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="G71" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H71" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I71" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="I71" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="J71" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K71" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L71" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="M71" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L71" s="12" t="n">
-        <v>75</v>
-      </c>
-      <c r="M71" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>54101</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>CECINA</t>
+          <t>MALALBERGO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,35 +4111,35 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
@@ -4150,12 +4150,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>MALALBERGO</t>
+          <t>SAN LAZZARO DI SAVENA</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4165,35 +4165,35 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="G73" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H73" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="I73" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="H73" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="I73" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="J73" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
@@ -4223,19 +4223,19 @@
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J74" s="12" t="n">
         <v>10</v>
@@ -4244,10 +4244,10 @@
         <v>4</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
@@ -4258,12 +4258,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>04601</t>
+          <t>54101</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>CECINA</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4273,51 +4273,51 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>04978</t>
+          <t>06259</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SCARLINO</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4327,51 +4327,51 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05099</t>
+          <t>04978</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>SCARLINO</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4381,51 +4381,51 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>54479</t>
+          <t>05099</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>BENTIVOGLIO</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4435,51 +4435,51 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>53490</t>
+          <t>54479</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SANT'ILARIO D'ENZA</t>
+          <t>BENTIVOGLIO</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4489,51 +4489,51 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06259</t>
+          <t>53490</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>SANT'ILARIO D'ENZA</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4543,35 +4543,35 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G81" s="12" t="n">
         <v>1</v>
@@ -4613,7 +4613,7 @@
         <v>9</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J81" s="12" t="n">
         <v>7</v>
@@ -4658,7 +4658,7 @@
         <v>18</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G82" s="12" t="n">
         <v>8</v>
@@ -4676,7 +4676,7 @@
         <v>4</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M82" s="12" t="n">
         <v>8</v>
@@ -4709,19 +4709,19 @@
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J83" s="12" t="n">
         <v>6</v>
@@ -4730,26 +4730,26 @@
         <v>0</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>54593</t>
+          <t>25518</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>CASALECCHIO DI RENO</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4759,51 +4759,51 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>TODESCATO MARCO</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
         <v>13</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>25518</t>
+          <t>54593</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>CASALECCHIO DI RENO</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4813,39 +4813,39 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>TODESCATO MARCO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="G85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H85" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I85" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J85" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K85" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L85" s="12" t="n">
+        <v>98</v>
+      </c>
+      <c r="M85" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I85" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="J85" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="12" t="n">
-        <v>66</v>
-      </c>
-      <c r="M85" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4874,7 +4874,7 @@
         <v>11</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G86" s="12" t="n">
         <v>0</v>
@@ -4928,13 +4928,13 @@
         <v>8</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G87" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I87" s="12" t="n">
         <v>4</v>
@@ -5036,7 +5036,7 @@
         <v>0</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G89" s="12" t="n">
         <v>0</v>
@@ -5090,7 +5090,7 @@
         <v>0</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G90" s="12" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
         <v>0</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G91" s="12" t="n">
         <v>0</v>
@@ -5198,13 +5198,13 @@
         <v>0</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G92" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="I92" s="12" t="n">
         <v>0</v>
@@ -5252,7 +5252,7 @@
         <v>0</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G93" s="12" t="n">
         <v>0</v>
@@ -5306,13 +5306,13 @@
         <v>0</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="G94" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="I94" s="12" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
         <v>0</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G95" s="12" t="n">
         <v>0</v>
@@ -5414,7 +5414,7 @@
         <v>0</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G96" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N97" headerRowCount="1">
-  <autoFilter ref="A10:N97"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N106" headerRowCount="1">
+  <autoFilter ref="A10:N106"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N97"/>
+  <dimension ref="A1:N106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,16 +673,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>8167</v>
+        <v>8613</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6166</v>
+        <v>6511</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3913</v>
+        <v>4165</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -1396,12 +1396,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>06249</t>
+          <t>53815</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SASSUOLO</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,35 +1411,35 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>244</v>
+        <v>77</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>329</v>
+        <v>77</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>10</v>
+        <v>142</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>51840</t>
+          <t>06249</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>BAGNO A RIPOLI</t>
+          <t>SASSUOLO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,51 +1465,51 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>125</v>
+        <v>203</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>60</v>
+        <v>244</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>67</v>
+        <v>329</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>05054</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ROSIGNANO MARITTIMO</t>
+          <t>BAGNO A RIPOLI</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,35 +1519,35 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1558,12 +1558,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>34710</t>
+          <t>05054</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>ROSIGNANO MARITTIMO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,51 +1573,51 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
+        <v>148</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>136</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="I25" s="12" t="n">
         <v>128</v>
       </c>
-      <c r="F25" s="12" t="n">
-        <v>195</v>
-      </c>
-      <c r="G25" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>95</v>
-      </c>
       <c r="J25" s="12" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>376</v>
+        <v>161</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>34710</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>FAENZA</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,51 +1627,51 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
         <v>128</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>121</v>
+        <v>195</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>194</v>
+        <v>376</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>05245</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>VECCHIANO</t>
+          <t>FAENZA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,51 +1681,51 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>135</v>
+        <v>6</v>
       </c>
       <c r="H27" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="K27" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="L27" s="12" t="n">
+        <v>194</v>
+      </c>
+      <c r="M27" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I27" s="12" t="n">
-        <v>109</v>
-      </c>
-      <c r="J27" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="K27" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="L27" s="12" t="n">
-        <v>110</v>
-      </c>
-      <c r="M27" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06019</t>
+          <t>05245</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>MISANO ADRIATICO</t>
+          <t>VECCHIANO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,35 +1735,35 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F28" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>109</v>
+      </c>
+      <c r="J28" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="K28" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="L28" s="12" t="n">
         <v>110</v>
       </c>
-      <c r="G28" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="I28" s="12" t="n">
-        <v>75</v>
-      </c>
-      <c r="J28" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="K28" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="L28" s="12" t="n">
-        <v>146</v>
-      </c>
       <c r="M28" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1774,12 +1774,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>05349</t>
+          <t>06019</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>PISTOIA</t>
+          <t>MISANO ADRIATICO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,51 +1789,51 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>249</v>
+        <v>110</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>224</v>
+        <v>146</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>34723</t>
+          <t>05349</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>PISTOIA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,51 +1843,51 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>292</v>
+        <v>224</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05911</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,51 +1897,51 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>89</v>
+        <v>292</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>05911</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,35 +1951,35 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>241</v>
+        <v>9</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>176</v>
+        <v>62</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>242</v>
+        <v>89</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -1990,12 +1990,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06416</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,51 +2005,51 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>117</v>
+        <v>52</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>38</v>
+        <v>241</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>59</v>
+        <v>176</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>93</v>
+        <v>242</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>06416</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,35 +2059,35 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>220</v>
+        <v>93</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2098,12 +2098,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>55380</t>
+          <t>25554</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>MONTELUPO FIORENTINO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,51 +2113,51 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>116</v>
+        <v>220</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04892</t>
+          <t>55380</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>MONTELUPO FIORENTINO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,51 +2167,51 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>158</v>
+        <v>121</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04634</t>
+          <t>05915</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI VALDARNO</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,51 +2221,51 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>141</v>
+        <v>74</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>53970</t>
+          <t>04892</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,35 +2275,35 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2314,12 +2314,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>05239</t>
+          <t>04634</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SAN MINIATO</t>
+          <t>SAN GIOVANNI VALDARNO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,51 +2329,51 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>95</v>
+        <v>156</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>06210</t>
+          <t>53970</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>CARPI</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,51 +2383,51 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>8</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>34802</t>
+          <t>05239</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>PRATO</t>
+          <t>SAN MINIATO</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,51 +2437,51 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F41" s="12" t="n">
+        <v>107</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="J41" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="K41" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="L41" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="G41" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="H41" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="I41" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="K41" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L41" s="12" t="n">
-        <v>134</v>
-      </c>
       <c r="M41" s="12" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>04516</t>
+          <t>06210</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>CARRARA</t>
+          <t>CARPI</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,35 +2491,35 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2530,12 +2530,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>34802</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>PRATO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2545,35 +2545,35 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2584,12 +2584,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05543</t>
+          <t>04516</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SASSO MARCONI</t>
+          <t>CARRARA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,35 +2599,35 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>87</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="J44" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="K44" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="L44" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="F44" s="12" t="n">
-        <v>66</v>
-      </c>
-      <c r="G44" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="H44" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="I44" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="J44" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="K44" s="12" t="n">
+      <c r="M44" s="12" t="n">
         <v>13</v>
-      </c>
-      <c r="L44" s="12" t="n">
-        <v>125</v>
-      </c>
-      <c r="M44" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2638,12 +2638,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>PIOMBINO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2653,51 +2653,51 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>76</v>
+        <v>153</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>05514</t>
+          <t>05543</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI IN PERSICETO</t>
+          <t>SASSO MARCONI</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,51 +2707,51 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J46" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="K46" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="K46" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="L46" s="12" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>53676</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>PIOMBINO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,51 +2761,51 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>05514</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SAN GIOVANNI IN PERSICETO</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,35 +2815,35 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
@@ -2854,12 +2854,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>14735</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>BORGO SAN LORENZO</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,51 +2869,51 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>05941</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>FORLÌ</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,51 +2923,51 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>329</v>
+        <v>32</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>58000</t>
+          <t>14735</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>MIRANDOLA</t>
+          <t>BORGO SAN LORENZO</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,35 +2977,35 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3016,12 +3016,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>06403</t>
+          <t>05941</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>GUASTALLA</t>
+          <t>FORLÌ</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3031,51 +3031,51 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>9</v>
+        <v>329</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>55420</t>
+          <t>58000</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MIRANDOLA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,51 +3085,51 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>04951</t>
+          <t>06403</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>GROSSETO</t>
+          <t>GUASTALLA</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>05829</t>
+          <t>55420</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>FERRARA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,51 +3193,51 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>05536</t>
+          <t>04951</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>GROSSETO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,51 +3247,51 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>05408</t>
+          <t>55416</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>CHIUSI</t>
+          <t>MONSUMMANO TERME</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,51 +3301,51 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>05829</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>FERRARA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,35 +3355,35 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
@@ -3394,12 +3394,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05290</t>
+          <t>05536</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>PONTEDERA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,51 +3409,51 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>05408</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>CHIUSI</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,51 +3463,51 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>MONTECCHIO EMILIA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,51 +3517,51 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="F61" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="G61" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="H61" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="I61" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="F61" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="G61" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="H61" s="12" t="n">
-        <v>81</v>
-      </c>
-      <c r="I61" s="12" t="n">
+      <c r="J61" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K61" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L61" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="M61" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="J61" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K61" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="L61" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="M61" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>05290</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>PONTEDERA</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,51 +3571,51 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,51 +3625,51 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="F63" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="G63" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H63" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I63" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="J63" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K63" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L63" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F63" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="G63" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="H63" s="12" t="n">
-        <v>109</v>
-      </c>
-      <c r="I63" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="J63" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K63" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L63" s="12" t="n">
-        <v>103</v>
-      </c>
       <c r="M63" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MONTECCHIO EMILIA</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,35 +3679,35 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3718,12 +3718,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>04812</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,51 +3733,51 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,35 +3787,35 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
@@ -3826,12 +3826,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06446</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3841,51 +3841,51 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="J67" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>04653</t>
+          <t>04812</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLION FIORENTINO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,35 +3895,35 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>33</v>
+        <v>131</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
@@ -3934,12 +3934,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3949,35 +3949,35 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
@@ -3988,12 +3988,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>34201</t>
+          <t>06446</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SANTA CROCE SULL'ARNO</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4003,35 +4003,35 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
@@ -4042,12 +4042,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04601</t>
+          <t>04653</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>CASTIGLION FIORENTINO</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4061,47 +4061,47 @@
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>MALALBERGO</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,32 +4111,32 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="M72" s="12" t="n">
         <v>3</v>
@@ -4150,12 +4150,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>55491</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SAN LAZZARO DI SAVENA</t>
+          <t>BORGO A MOZZANO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4165,51 +4165,51 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
         <v>30</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>05530</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SANTA CROCE SULL'ARNO</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4219,51 +4219,51 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>54101</t>
+          <t>04601</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>CECINA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4273,51 +4273,51 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>06259</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>MALALBERGO</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4331,31 +4331,31 @@
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H76" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="I76" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="J76" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K76" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L76" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="M76" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="I76" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="J76" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="K76" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L76" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="M76" s="12" t="n">
-        <v>11</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
@@ -4366,12 +4366,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>04978</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SCARLINO</t>
+          <t>SAN LAZZARO DI SAVENA</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4381,51 +4381,51 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="F77" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H77" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I77" s="12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J77" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K77" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L77" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="M77" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K77" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L77" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="M77" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>05099</t>
+          <t>05530</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4435,51 +4435,51 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G78" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="H78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="J78" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K78" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H78" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="I78" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="J78" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K78" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="L78" s="12" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>54479</t>
+          <t>05982</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>BENTIVOGLIO</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4489,51 +4489,51 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G79" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="H79" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="I79" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="J79" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="H79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="J79" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="K79" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>53490</t>
+          <t>54101</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SANT'ILARIO D'ENZA</t>
+          <t>CECINA</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4543,35 +4543,35 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
@@ -4582,12 +4582,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>04677</t>
+          <t>06259</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4597,35 +4597,35 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
@@ -4636,12 +4636,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>54066</t>
+          <t>04978</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>PIETRASANTA</t>
+          <t>SCARLINO</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4651,51 +4651,51 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05589</t>
+          <t>05099</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>ZOLA PREDOSA</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4705,51 +4705,51 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>25518</t>
+          <t>54479</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>CASALECCHIO DI RENO</t>
+          <t>BENTIVOGLIO</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4759,35 +4759,35 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>TODESCATO MARCO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="F84" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="G84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" s="12" t="n">
+      <c r="J84" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="M84" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="I84" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="J84" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="M84" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
@@ -4798,12 +4798,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>54593</t>
+          <t>53490</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>SANT'ILARIO D'ENZA</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4813,35 +4813,35 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
@@ -4852,12 +4852,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>05512</t>
+          <t>04677</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN PIETRO TERME</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4867,32 +4867,32 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J86" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K86" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K86" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="L86" s="12" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="M86" s="12" t="n">
         <v>1</v>
@@ -4906,12 +4906,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>05160</t>
+          <t>54066</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>BORGO A MOZZANO</t>
+          <t>PIETRASANTA</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4925,47 +4925,47 @@
         </is>
       </c>
       <c r="E87" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F87" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="G87" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F87" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="G87" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="H87" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="I87" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J87" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K87" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I87" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J87" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K87" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L87" s="12" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>05241</t>
+          <t>54044</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO TERME</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4975,35 +4975,35 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="F88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F88" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I88" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J88" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K88" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L88" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M88" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="J88" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K88" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="M88" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>01300</t>
+          <t>05055</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -5029,51 +5029,51 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E89" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J89" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>02945</t>
+          <t>05589</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>ZOLA PREDOSA</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5083,51 +5083,51 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J90" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K90" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M90" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>04840</t>
+          <t>25518</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>BARBERINO DI MUGELLO</t>
+          <t>CASALECCHIO DI RENO</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5137,46 +5137,46 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>TODESCATO MARCO</t>
         </is>
       </c>
       <c r="E91" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>128</v>
+        <v>13</v>
       </c>
       <c r="G91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H91" s="12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J91" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06353</t>
+          <t>54593</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -5195,31 +5195,31 @@
         </is>
       </c>
       <c r="E92" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="G92" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>116</v>
+        <v>5</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J92" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K92" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
@@ -5230,12 +5230,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06408</t>
+          <t>05512</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>CORREGGIO</t>
+          <t>CASTEL SAN PIETRO TERME</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5245,51 +5245,51 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E93" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="G93" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H93" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I93" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J93" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K93" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L93" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="M93" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I93" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>14730</t>
+          <t>06363</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>BOMPORTO</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5299,51 +5299,51 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E94" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>453</v>
+        <v>0</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J94" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K94" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>15552</t>
+          <t>05160</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>BORGO A MOZZANO</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5353,51 +5353,51 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E95" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I95" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J95" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L95" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>15572</t>
+          <t>22966</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>MOLINELLA</t>
+          <t>BERCETO</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5407,32 +5407,32 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>IACOPINI ALESSANDRA</t>
         </is>
       </c>
       <c r="E96" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J96" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K96" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I96" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L96" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M96" s="12" t="n">
         <v>0</v>
@@ -5446,52 +5446,538 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>11295</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>MONTIGNOSO</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>CASCIARI PAOLO</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J97" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K97" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L97" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M97" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>05241</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>SAN GIULIANO TERME</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>CIULLA VALERIO</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="M98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01300</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>COLLESALVETTI</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>CASCIARI PAOLO</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>04840</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>BARBERINO DI MUGELLO</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>CORSI PAOLA</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="12" t="n">
+        <v>128</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="I100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>06353</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>MODENA</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>PIETRANTONIO GIULIANO</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="12" t="n">
+        <v>116</v>
+      </c>
+      <c r="I101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>06408</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>CORREGGIO</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>CARCIONE PARIDE</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>14730</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>FIRENZE</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>CORSI PAOLA</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="12" t="n">
+        <v>288</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="12" t="n">
+        <v>453</v>
+      </c>
+      <c r="I103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>15552</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>IMOLA</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>MURGO LORENZO</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>15572</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>MOLINELLA</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>LIBANORI FEDERICO</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
           <t>53624</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>FOLLONICA</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>ANTONINI GABRIELE</t>
         </is>
       </c>
-      <c r="E97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="12" t="n">
+      <c r="E106" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="G97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="12" t="n">
+      <c r="G106" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" s="2" t="inlineStr">
+      <c r="I106" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>96</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>8613</v>
+        <v>9108</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6511</v>
+        <v>6863</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>4165</v>
+        <v>4412</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>1080</v>
+        <v>1126</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1004</v>
+        <v>1062</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>947</v>
+        <v>988</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>458</v>
+        <v>479</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>546</v>
+        <v>574</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>562</v>
+        <v>590</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>417</v>
+        <v>440</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>484</v>
+        <v>503</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>121</v>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>515</v>
+        <v>537</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>410</v>
+        <v>433</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>736</v>
+        <v>756</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,28 +983,28 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>393</v>
+        <v>426</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>546</v>
+        <v>565</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>394</v>
+        <v>419</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>626</v>
+        <v>658</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="J14" s="12" t="n">
+        <v>122</v>
+      </c>
+      <c r="K14" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="K14" s="12" t="n">
-        <v>95</v>
-      </c>
       <c r="L14" s="12" t="n">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>2</v>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>405</v>
+        <v>424</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1072,12 +1072,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>58414</t>
+          <t>05112</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>LUCCA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,51 +1087,51 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>186</v>
+        <v>333</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>141</v>
+        <v>208</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>289</v>
+        <v>212</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05112</t>
+          <t>58414</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>LUCCA</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,51 +1141,51 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>310</v>
+        <v>202</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>83</v>
+        <v>167</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>188</v>
+        <v>144</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>197</v>
+        <v>305</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04845</t>
+          <t>06334</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>FUCECCHIO</t>
+          <t>VIGNOLA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,51 +1195,51 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>249</v>
+        <v>199</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>12</v>
+        <v>168</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>48</v>
+        <v>183</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>126</v>
+        <v>211</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>06334</t>
+          <t>04845</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>VIGNOLA</t>
+          <t>FUCECCHIO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,51 +1249,51 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>150</v>
+        <v>13</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>164</v>
+        <v>51</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>198</v>
+        <v>132</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>05291</t>
+          <t>53815</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>PISA</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,35 +1303,35 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>268</v>
+        <v>327</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>189</v>
+        <v>229</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>16</v>
+        <v>146</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>13</v>
@@ -1373,16 +1373,16 @@
         <v>53</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>4</v>
@@ -1396,12 +1396,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>53815</t>
+          <t>05291</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>PISA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,35 +1411,35 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>77</v>
+        <v>212</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>137</v>
+        <v>180</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1469,31 +1469,31 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1523,35 +1523,35 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>67</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>20</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>32</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1577,19 +1577,19 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>38</v>
@@ -1598,7 +1598,7 @@
         <v>21</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>6</v>
@@ -1612,12 +1612,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>34710</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>FAENZA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,51 +1627,51 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>195</v>
+        <v>122</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>376</v>
+        <v>209</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>05349</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>FAENZA</t>
+          <t>PISTOIA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,39 +1681,39 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>121</v>
+        <v>259</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="J27" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="K27" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="L27" s="12" t="n">
+        <v>239</v>
+      </c>
+      <c r="M27" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="K27" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="L27" s="12" t="n">
-        <v>194</v>
-      </c>
-      <c r="M27" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1739,28 +1739,28 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>19</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>10</v>
@@ -1774,12 +1774,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06019</t>
+          <t>34710</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>MISANO ADRIATICO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,51 +1789,51 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>110</v>
+        <v>211</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>146</v>
+        <v>390</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05349</t>
+          <t>06019</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>PISTOIA</t>
+          <t>MISANO ADRIATICO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,39 +1843,39 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>249</v>
+        <v>117</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>224</v>
+        <v>152</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1901,35 +1901,35 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1955,28 +1955,28 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>4</v>
@@ -2009,28 +2009,28 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>32</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>2</v>
@@ -2044,12 +2044,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>06416</t>
+          <t>25554</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,35 +2059,35 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>93</v>
+        <v>230</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2098,12 +2098,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>55380</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MONTELUPO FIORENTINO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,51 +2113,51 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>220</v>
+        <v>119</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>55380</t>
+          <t>06416</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>MONTELUPO FIORENTINO</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,51 +2167,51 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>68</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>05915</t>
+          <t>04634</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>SAN GIOVANNI VALDARNO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,51 +2221,51 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>74</v>
+        <v>143</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>114</v>
+        <v>166</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>04892</t>
+          <t>05915</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,51 +2275,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>04634</t>
+          <t>04892</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI VALDARNO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,35 +2329,35 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="J39" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K39" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="K39" s="12" t="n">
-        <v>25</v>
-      </c>
       <c r="L39" s="12" t="n">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2368,12 +2368,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>53970</t>
+          <t>05239</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>SAN MINIATO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,51 +2383,51 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>05239</t>
+          <t>53970</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SAN MINIATO</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,39 +2437,39 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2495,31 +2495,31 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2549,31 +2549,31 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J43" s="12" t="n">
         <v>27</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2584,12 +2584,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>04516</t>
+          <t>05543</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CARRARA</t>
+          <t>SASSO MARCONI</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,35 +2599,35 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="G44" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="H44" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="J44" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="K44" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L44" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="M44" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="H44" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I44" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="J44" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="K44" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="L44" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="M44" s="12" t="n">
-        <v>13</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2657,19 +2657,19 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J45" s="12" t="n">
         <v>12</v>
@@ -2678,7 +2678,7 @@
         <v>34</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>2</v>
@@ -2692,12 +2692,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>05543</t>
+          <t>53676</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SASSO MARCONI</t>
+          <t>PIOMBINO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,35 +2707,35 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
@@ -2746,12 +2746,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>04516</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>PIOMBINO</t>
+          <t>CARRARA</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,35 +2761,35 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
@@ -2800,12 +2800,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>05514</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI IN PERSICETO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,35 +2815,35 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
@@ -2854,12 +2854,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>05514</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>SAN GIOVANNI IN PERSICETO</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,51 +2869,51 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F49" s="12" t="n">
         <v>71</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>05941</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>FORLÌ</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,51 +2923,51 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>56</v>
+        <v>119</v>
       </c>
       <c r="G50" s="12" t="n">
+        <v>99</v>
+      </c>
+      <c r="H50" s="12" t="n">
+        <v>340</v>
+      </c>
+      <c r="I50" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="J50" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K50" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="H50" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="I50" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="J50" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="K50" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="L50" s="12" t="n">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14735</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>BORGO SAN LORENZO</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,35 +2977,35 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3016,12 +3016,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>05941</t>
+          <t>14735</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>FORLÌ</t>
+          <t>BORGO SAN LORENZO</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3031,39 +3031,39 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>329</v>
+        <v>13</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3089,28 +3089,28 @@
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J53" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M53" s="12" t="n">
         <v>1</v>
@@ -3124,12 +3124,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>06403</t>
+          <t>55416</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>GUASTALLA</t>
+          <t>MONSUMMANO TERME</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>55420</t>
+          <t>06403</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>GUASTALLA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,51 +3193,51 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="G55" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>04951</t>
+          <t>55420</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>GROSSETO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,35 +3247,35 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
@@ -3286,12 +3286,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>55416</t>
+          <t>04951</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>MONSUMMANO TERME</t>
+          <t>GROSSETO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,39 +3301,39 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F58" s="12" t="n">
         <v>0</v>
@@ -3371,7 +3371,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J58" s="12" t="n">
         <v>15</v>
@@ -3380,7 +3380,7 @@
         <v>9</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="M58" s="12" t="n">
         <v>0</v>
@@ -3394,12 +3394,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05536</t>
+          <t>05290</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>PONTEDERA</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,51 +3409,51 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>05408</t>
+          <t>05536</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>CHIUSI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,39 +3463,39 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3521,28 +3521,28 @@
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K61" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M61" s="12" t="n">
         <v>19</v>
@@ -3556,12 +3556,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>05290</t>
+          <t>05408</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>PONTEDERA</t>
+          <t>CHIUSI</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,35 +3571,35 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G62" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H62" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="I62" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="J62" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="K62" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L62" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="M62" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="H62" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I62" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="J62" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K62" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="L62" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="M62" s="12" t="n">
-        <v>19</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
@@ -3610,12 +3610,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,51 +3625,51 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G63" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H63" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I63" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="J63" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H63" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I63" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="J63" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="K63" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>MONTECCHIO EMILIA</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3683,31 +3683,31 @@
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3718,12 +3718,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>55491</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>BORGO A MOZZANO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,35 +3733,35 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="H65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J65" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
@@ -3772,12 +3772,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,51 +3787,51 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="G66" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H66" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="J66" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="H66" s="12" t="n">
-        <v>109</v>
-      </c>
-      <c r="I66" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="J66" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="K66" s="12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MONTECCHIO EMILIA</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3841,35 +3841,35 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H67" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="I67" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="J67" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K67" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="L67" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="M67" s="12" t="n">
         <v>11</v>
-      </c>
-      <c r="I67" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J67" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K67" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="L67" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="M67" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
@@ -3880,12 +3880,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>04812</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,35 +3895,35 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
@@ -3934,12 +3934,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>06446</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3949,51 +3949,51 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="G69" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H69" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="J69" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H69" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="I69" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="J69" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="K69" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>06446</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4003,51 +4003,51 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04653</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLION FIORENTINO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4057,35 +4057,35 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="G71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I71" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H71" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="I71" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="J71" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
@@ -4096,12 +4096,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>04812</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,35 +4111,35 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
@@ -4150,12 +4150,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>55491</t>
+          <t>04653</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>BORGO A MOZZANO</t>
+          <t>CASTIGLION FIORENTINO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4165,51 +4165,51 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K73" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L73" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="M73" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L73" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="M73" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>34201</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SANTA CROCE SULL'ARNO</t>
+          <t>SAN LAZZARO DI SAVENA</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4219,51 +4219,51 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="I74" s="12" t="n">
         <v>23</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>04601</t>
+          <t>06259</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4273,51 +4273,51 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="G75" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="H75" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H75" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="I75" s="12" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>MALALBERGO</t>
+          <t>SANTA CROCE SULL'ARNO</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4327,35 +4327,35 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="G76" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="H76" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I76" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="H76" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="I76" s="12" t="n">
-        <v>20</v>
-      </c>
       <c r="J76" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
@@ -4366,12 +4366,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SAN LAZZARO DI SAVENA</t>
+          <t>MALALBERGO</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4381,35 +4381,35 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L77" s="12" t="n">
         <v>82</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
@@ -4420,12 +4420,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>05530</t>
+          <t>04601</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4435,51 +4435,51 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J78" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K78" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K78" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="L78" s="12" t="n">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>05982</t>
+          <t>05530</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4489,23 +4489,23 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J79" s="12" t="n">
         <v>10</v>
@@ -4514,26 +4514,26 @@
         <v>4</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>54101</t>
+          <t>05982</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>CECINA</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4543,35 +4543,35 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
         <v>27</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
@@ -4582,12 +4582,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06259</t>
+          <t>54101</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>CECINA</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4597,35 +4597,35 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
@@ -4676,14 +4676,14 @@
         <v>2</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4709,19 +4709,19 @@
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G83" s="12" t="n">
         <v>4</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J83" s="12" t="n">
         <v>3</v>
@@ -4730,10 +4730,10 @@
         <v>11</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
@@ -4784,26 +4784,26 @@
         <v>6</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M84" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>53490</t>
+          <t>04677</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>SANT'ILARIO D'ENZA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4813,35 +4813,35 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G85" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
@@ -4852,12 +4852,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>04677</t>
+          <t>53490</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>SANT'ILARIO D'ENZA</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4867,35 +4867,35 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J86" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
@@ -4928,13 +4928,13 @@
         <v>18</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G87" s="12" t="n">
         <v>8</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I87" s="12" t="n">
         <v>14</v>
@@ -4946,7 +4946,7 @@
         <v>4</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M87" s="12" t="n">
         <v>8</v>
@@ -4960,12 +4960,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>54044</t>
+          <t>05055</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4975,17 +4975,17 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="H88" s="12" t="n">
         <v>0</v>
@@ -4994,32 +4994,32 @@
         <v>14</v>
       </c>
       <c r="J88" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K88" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>05055</t>
+          <t>54044</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E89" s="12" t="n">
@@ -5039,29 +5039,29 @@
         <v>0</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J89" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5108,14 +5108,14 @@
         <v>0</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M90" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5141,19 +5141,19 @@
         </is>
       </c>
       <c r="E91" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J91" s="12" t="n">
         <v>3</v>
@@ -5162,7 +5162,7 @@
         <v>0</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="M91" s="12" t="n">
         <v>0</v>
@@ -5176,12 +5176,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>54593</t>
+          <t>06363</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>BOMPORTO</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5191,51 +5191,51 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E92" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J92" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K92" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L92" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="M92" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K92" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="L92" s="12" t="n">
-        <v>98</v>
-      </c>
-      <c r="M92" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>05512</t>
+          <t>54593</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN PIETRO TERME</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5245,32 +5245,32 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E93" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="G93" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H93" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I93" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J93" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="M93" s="12" t="n">
         <v>1</v>
@@ -5284,12 +5284,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>06363</t>
+          <t>05512</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>BOMPORTO</t>
+          <t>CASTEL SAN PIETRO TERME</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5299,51 +5299,51 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E94" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J94" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K94" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05160</t>
+          <t>22966</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>BORGO A MOZZANO</t>
+          <t>BERCETO</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5353,51 +5353,51 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>IACOPINI ALESSANDRA</t>
         </is>
       </c>
       <c r="E95" s="12" t="n">
         <v>8</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G95" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J95" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K95" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H95" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I95" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J95" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K95" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L95" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>22966</t>
+          <t>05160</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>BERCETO</t>
+          <t>BORGO A MOZZANO</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5407,35 +5407,35 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>IACOPINI ALESSANDRA</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E96" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J96" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M96" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="L96" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="M96" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="E97" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F97" s="12" t="n">
         <v>0</v>
@@ -5477,7 +5477,7 @@
         <v>0</v>
       </c>
       <c r="I97" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J97" s="12" t="n">
         <v>1</v>
@@ -5486,14 +5486,14 @@
         <v>2</v>
       </c>
       <c r="L97" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M97" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
         <v>0</v>
       </c>
       <c r="H99" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I99" s="12" t="n">
         <v>0</v>
@@ -5630,13 +5630,13 @@
         <v>0</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G100" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I100" s="12" t="n">
         <v>0</v>
@@ -5684,13 +5684,13 @@
         <v>0</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G101" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H101" s="12" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I101" s="12" t="n">
         <v>0</v>
@@ -5738,7 +5738,7 @@
         <v>0</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G102" s="12" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5792,13 +5792,13 @@
         <v>0</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="G103" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H103" s="12" t="n">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c r="I103" s="12" t="n">
         <v>0</v>
@@ -5846,7 +5846,7 @@
         <v>0</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G104" s="12" t="n">
         <v>0</v>
@@ -5900,7 +5900,7 @@
         <v>0</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G105" s="12" t="n">
         <v>0</v>
@@ -5954,7 +5954,7 @@
         <v>0</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G106" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>96</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>9108</v>
+        <v>9723</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6863</v>
+        <v>7367</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>4412</v>
+        <v>4663</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>1126</v>
+        <v>1177</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1062</v>
+        <v>1167</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>361</v>
+        <v>408</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>988</v>
+        <v>1037</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>479</v>
+        <v>512</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>574</v>
+        <v>606</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>590</v>
+        <v>639</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>503</v>
+        <v>535</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>537</v>
+        <v>562</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>433</v>
+        <v>459</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>756</v>
+        <v>806</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>646</v>
+        <v>678</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>426</v>
+        <v>450</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>565</v>
+        <v>619</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>419</v>
+        <v>444</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>658</v>
+        <v>723</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,28 +1091,28 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>333</v>
+        <v>365</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>1</v>
@@ -1126,12 +1126,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>58414</t>
+          <t>04845</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>FUCECCHIO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,39 +1141,39 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>202</v>
+        <v>293</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>167</v>
+        <v>65</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>144</v>
+        <v>195</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>305</v>
+        <v>140</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1199,47 +1199,47 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04845</t>
+          <t>58414</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>FUCECCHIO</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,39 +1249,39 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>260</v>
+        <v>211</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>51</v>
+        <v>184</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>181</v>
+        <v>148</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>132</v>
+        <v>327</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1307,31 +1307,31 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>78</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1361,35 +1361,35 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>4</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1415,16 +1415,16 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>180</v>
@@ -1433,10 +1433,10 @@
         <v>109</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>18</v>
@@ -1469,28 +1469,28 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>347</v>
+        <v>364</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>11</v>
@@ -1504,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>51840</t>
+          <t>05349</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>BAGNO A RIPOLI</t>
+          <t>PISTOIA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,39 +1519,39 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>126</v>
+        <v>272</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>56</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>187</v>
+        <v>246</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1577,31 +1577,31 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
+        <v>161</v>
+      </c>
+      <c r="F25" s="12" t="n">
         <v>152</v>
       </c>
-      <c r="F25" s="12" t="n">
-        <v>140</v>
-      </c>
       <c r="G25" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1612,12 +1612,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>FAENZA</t>
+          <t>BAGNO A RIPOLI</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,35 +1627,35 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1666,12 +1666,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>05349</t>
+          <t>05245</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>PISTOIA</t>
+          <t>VECCHIANO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,51 +1681,51 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>259</v>
+        <v>40</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>29</v>
+        <v>167</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>239</v>
+        <v>132</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>05245</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>VECCHIANO</t>
+          <t>FAENZA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,39 +1735,39 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>38</v>
+        <v>133</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>143</v>
+        <v>6</v>
       </c>
       <c r="H28" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="J28" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="K28" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="L28" s="12" t="n">
+        <v>226</v>
+      </c>
+      <c r="M28" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I28" s="12" t="n">
-        <v>113</v>
-      </c>
-      <c r="J28" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="K28" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="L28" s="12" t="n">
-        <v>115</v>
-      </c>
-      <c r="M28" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1793,28 +1793,28 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>4</v>
@@ -1828,12 +1828,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>06019</t>
+          <t>25554</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>MISANO ADRIATICO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,35 +1843,35 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>152</v>
+        <v>247</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>6</v>
+        <v>98</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1882,12 +1882,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>34723</t>
+          <t>06019</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>MISANO ADRIATICO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,39 +1897,39 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>306</v>
+        <v>164</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1955,28 +1955,28 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>4</v>
@@ -1990,12 +1990,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,51 +2005,51 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>246</v>
+        <v>3</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>253</v>
+        <v>317</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2063,47 +2063,47 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>25</v>
+        <v>246</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>32</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>230</v>
+        <v>264</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>55380</t>
+          <t>06416</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>MONTELUPO FIORENTINO</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,51 +2113,51 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>6</v>
+        <v>87</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="J35" s="12" t="n">
         <v>23</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>06416</t>
+          <t>04634</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>SAN GIOVANNI VALDARNO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,35 +2167,35 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>97</v>
+        <v>173</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2206,12 +2206,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04634</t>
+          <t>55380</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI VALDARNO</t>
+          <t>MONTELUPO FIORENTINO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,39 +2221,39 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>166</v>
+        <v>123</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2279,31 +2279,31 @@
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>36</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2314,12 +2314,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>04892</t>
+          <t>53970</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,35 +2329,35 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>163</v>
+        <v>127</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2368,12 +2368,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>05239</t>
+          <t>06210</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SAN MINIATO</t>
+          <t>CARPI</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,35 +2383,35 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2422,12 +2422,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>53970</t>
+          <t>05239</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>SAN MINIATO</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,51 +2437,51 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06210</t>
+          <t>04892</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>CARPI</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,51 +2491,51 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>77</v>
+        <v>173</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>34802</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>PRATO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2545,51 +2545,51 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
+        <v>93</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="H43" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="I43" s="12" t="n">
         <v>78</v>
       </c>
-      <c r="F43" s="12" t="n">
-        <v>99</v>
-      </c>
-      <c r="G43" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="H43" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="I43" s="12" t="n">
-        <v>66</v>
-      </c>
       <c r="J43" s="12" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>140</v>
+        <v>93</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05543</t>
+          <t>53676</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SASSO MARCONI</t>
+          <t>PIOMBINO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,35 +2599,35 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2638,12 +2638,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>34802</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>PRATO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2653,35 +2653,35 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2692,12 +2692,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>55416</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>PIOMBINO</t>
+          <t>MONSUMMANO TERME</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,51 +2707,51 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04516</t>
+          <t>05543</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>CARRARA</t>
+          <t>SASSO MARCONI</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,35 +2761,35 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="G47" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="H47" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I47" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="J47" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="K47" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L47" s="12" t="n">
+        <v>146</v>
+      </c>
+      <c r="M47" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="H47" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I47" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="J47" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="K47" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="L47" s="12" t="n">
-        <v>79</v>
-      </c>
-      <c r="M47" s="12" t="n">
-        <v>13</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2819,47 +2819,47 @@
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>60</v>
+        <v>127</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>05514</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI IN PERSICETO</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,51 +2869,51 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>05941</t>
+          <t>04516</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>FORLÌ</t>
+          <t>CARRARA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,51 +2923,51 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>340</v>
+        <v>2</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>05514</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>SAN GIOVANNI IN PERSICETO</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,51 +2977,51 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>14735</t>
+          <t>05941</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>BORGO SAN LORENZO</t>
+          <t>FORLÌ</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3031,51 +3031,51 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>13</v>
+        <v>363</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>58000</t>
+          <t>14735</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>MIRANDOLA</t>
+          <t>BORGO SAN LORENZO</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,51 +3085,51 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>55416</t>
+          <t>58000</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>MONSUMMANO TERME</t>
+          <t>MIRANDOLA</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M54" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>06403</t>
+          <t>55420</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>GUASTALLA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,51 +3193,51 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>55420</t>
+          <t>06403</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>GUASTALLA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,39 +3247,39 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3305,10 +3305,10 @@
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G57" s="12" t="n">
         <v>0</v>
@@ -3317,7 +3317,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J57" s="12" t="n">
         <v>10</v>
@@ -3326,10 +3326,10 @@
         <v>16</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F58" s="12" t="n">
         <v>0</v>
@@ -3377,17 +3377,17 @@
         <v>15</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M58" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G59" s="12" t="n">
         <v>2</v>
@@ -3425,19 +3425,19 @@
         <v>11</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J59" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
@@ -3470,13 +3470,13 @@
         <v>49</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="I60" s="12" t="n">
         <v>43</v>
@@ -3488,7 +3488,7 @@
         <v>6</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="M60" s="12" t="n">
         <v>40</v>
@@ -3502,12 +3502,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,51 +3517,51 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>05408</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>CHIUSI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,51 +3571,51 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="G62" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="H62" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="I62" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="J62" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H62" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="I62" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="J62" s="12" t="n">
-        <v>15</v>
-      </c>
       <c r="K62" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>05408</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>CHIUSI</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,35 +3625,35 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
@@ -3683,31 +3683,31 @@
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G64" s="12" t="n">
         <v>6</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K64" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3718,12 +3718,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>55491</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>BORGO A MOZZANO</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,51 +3733,51 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>24</v>
+        <v>124</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>55491</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>BORGO A MOZZANO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,51 +3787,51 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>04812</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>MONTECCHIO EMILIA</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3841,35 +3841,35 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>66</v>
+        <v>144</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>06259</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3895,51 +3895,51 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="G68" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="H68" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I68" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="J68" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K68" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L68" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="M68" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="H68" s="12" t="n">
-        <v>116</v>
-      </c>
-      <c r="I68" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="J68" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K68" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="L68" s="12" t="n">
-        <v>112</v>
-      </c>
-      <c r="M68" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>06446</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3949,51 +3949,51 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>MONTECCHIO EMILIA</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4003,35 +4003,35 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
@@ -4042,12 +4042,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4057,35 +4057,35 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>11</v>
+        <v>123</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
@@ -4096,12 +4096,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>04812</t>
+          <t>06446</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,39 +4111,39 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>139</v>
+        <v>46</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4169,28 +4169,28 @@
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J73" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M73" s="12" t="n">
         <v>1</v>
@@ -4204,12 +4204,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SAN LAZZARO DI SAVENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4223,31 +4223,31 @@
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
@@ -4258,12 +4258,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06259</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>MALALBERGO</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4277,31 +4277,31 @@
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
@@ -4312,12 +4312,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>34201</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SANTA CROCE SULL'ARNO</t>
+          <t>SAN LAZZARO DI SAVENA</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4327,35 +4327,35 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="I76" s="12" t="n">
         <v>24</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
@@ -4366,12 +4366,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>05530</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>MALALBERGO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4381,51 +4381,51 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="F77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="F77" s="12" t="n">
-        <v>80</v>
-      </c>
-      <c r="G77" s="12" t="n">
-        <v>25</v>
-      </c>
       <c r="H77" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J77" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K77" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K77" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="L77" s="12" t="n">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04601</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>SANTA CROCE SULL'ARNO</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4435,51 +4435,51 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>05530</t>
+          <t>04601</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4489,35 +4489,35 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J79" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K79" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K79" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="L79" s="12" t="n">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
@@ -4547,28 +4547,28 @@
         </is>
       </c>
       <c r="E80" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="F80" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="G80" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="H80" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="G80" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="H80" s="12" t="n">
-        <v>40</v>
-      </c>
       <c r="I80" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K80" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M80" s="12" t="n">
         <v>2</v>
@@ -4582,12 +4582,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>54101</t>
+          <t>04978</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>CECINA</t>
+          <t>SCARLINO</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4604,44 +4604,44 @@
         <v>27</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>04978</t>
+          <t>54101</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>SCARLINO</t>
+          <t>CECINA</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4655,35 +4655,35 @@
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4709,16 +4709,16 @@
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G83" s="12" t="n">
         <v>4</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I83" s="12" t="n">
         <v>14</v>
@@ -4727,13 +4727,13 @@
         <v>3</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
@@ -4744,12 +4744,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>54479</t>
+          <t>04677</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>BENTIVOGLIO</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4759,51 +4759,51 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G84" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H84" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="H84" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I84" s="12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J84" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K84" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K84" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="L84" s="12" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="M84" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04677</t>
+          <t>54479</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>BENTIVOGLIO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4813,39 +4813,39 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="M85" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4874,13 +4874,13 @@
         <v>22</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G86" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I86" s="12" t="n">
         <v>18</v>
@@ -4892,7 +4892,7 @@
         <v>4</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M86" s="12" t="n">
         <v>11</v>
@@ -4906,12 +4906,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>54066</t>
+          <t>05055</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>PIETRASANTA</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4921,51 +4921,51 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J87" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K87" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>05055</t>
+          <t>54066</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>PIETRASANTA</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4975,39 +4975,39 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I88" s="12" t="n">
         <v>14</v>
       </c>
       <c r="J88" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K88" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="E89" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F89" s="12" t="n">
         <v>0</v>
@@ -5045,7 +5045,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J89" s="12" t="n">
         <v>2</v>
@@ -5061,19 +5061,19 @@
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05589</t>
+          <t>06363</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>ZOLA PREDOSA</t>
+          <t>BOMPORTO</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5083,51 +5083,51 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F90" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H90" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J90" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K90" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>25518</t>
+          <t>05589</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>CASALECCHIO DI RENO</t>
+          <t>ZOLA PREDOSA</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5137,32 +5137,32 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>TODESCATO MARCO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E91" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H91" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J91" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="M91" s="12" t="n">
         <v>0</v>
@@ -5176,12 +5176,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06363</t>
+          <t>25518</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>BOMPORTO</t>
+          <t>CASALECCHIO DI RENO</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5191,39 +5191,39 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>TODESCATO MARCO</t>
         </is>
       </c>
       <c r="E92" s="12" t="n">
         <v>14</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J92" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K92" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5249,19 +5249,19 @@
         </is>
       </c>
       <c r="E93" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I93" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J93" s="12" t="n">
         <v>2</v>
@@ -5270,7 +5270,7 @@
         <v>6</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M93" s="12" t="n">
         <v>1</v>
@@ -5306,7 +5306,7 @@
         <v>11</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G94" s="12" t="n">
         <v>0</v>
@@ -5357,19 +5357,19 @@
         </is>
       </c>
       <c r="E95" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I95" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J95" s="12" t="n">
         <v>3</v>
@@ -5378,7 +5378,7 @@
         <v>1</v>
       </c>
       <c r="L95" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M95" s="12" t="n">
         <v>0</v>
@@ -5414,7 +5414,7 @@
         <v>8</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G96" s="12" t="n">
         <v>1</v>
@@ -5576,13 +5576,13 @@
         <v>0</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G99" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H99" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I99" s="12" t="n">
         <v>0</v>
@@ -5630,13 +5630,13 @@
         <v>0</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="G100" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I100" s="12" t="n">
         <v>0</v>
@@ -5684,13 +5684,13 @@
         <v>0</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G101" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H101" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="I101" s="12" t="n">
         <v>0</v>
@@ -5792,13 +5792,13 @@
         <v>0</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="G103" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H103" s="12" t="n">
-        <v>466</v>
+        <v>489</v>
       </c>
       <c r="I103" s="12" t="n">
         <v>0</v>
@@ -5846,7 +5846,7 @@
         <v>0</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G104" s="12" t="n">
         <v>0</v>
@@ -5900,7 +5900,7 @@
         <v>0</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G105" s="12" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
         <v>0</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G106" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>96</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>9723</v>
+        <v>10452</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>7367</v>
+        <v>7941</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>4663</v>
+        <v>4988</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>1177</v>
+        <v>1251</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1167</v>
+        <v>1245</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>282</v>
+        <v>311</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>408</v>
+        <v>440</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>1037</v>
+        <v>1105</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>455</v>
+        <v>486</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>512</v>
+        <v>544</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>606</v>
+        <v>651</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>639</v>
+        <v>661</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>433</v>
+        <v>455</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>466</v>
+        <v>497</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>535</v>
+        <v>567</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>562</v>
+        <v>579</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>806</v>
+        <v>869</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>678</v>
+        <v>726</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,28 +983,28 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>450</v>
+        <v>488</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>619</v>
+        <v>628</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>444</v>
+        <v>481</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>723</v>
+        <v>751</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>407</v>
+        <v>437</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>3</v>
@@ -1037,35 +1037,35 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>361</v>
+        <v>388</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>316</v>
+        <v>362</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>365</v>
+        <v>393</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>04845</t>
+          <t>06334</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>FUCECCHIO</t>
+          <t>VIGNOLA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,51 +1141,51 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>293</v>
+        <v>234</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>13</v>
+        <v>201</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>65</v>
+        <v>226</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>195</v>
+        <v>236</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>140</v>
+        <v>240</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>06334</t>
+          <t>04845</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VIGNOLA</t>
+          <t>FUCECCHIO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,39 +1195,39 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>220</v>
+        <v>312</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>181</v>
+        <v>16</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>195</v>
+        <v>76</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>221</v>
+        <v>147</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1253,28 +1253,28 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>44</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>327</v>
+        <v>365</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>6</v>
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>152</v>
@@ -1361,28 +1361,28 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>4</v>
@@ -1415,31 +1415,31 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>06249</t>
+          <t>05054</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SASSUOLO</t>
+          <t>ROSIGNANO MARITTIMO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,51 +1465,51 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>213</v>
+        <v>155</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>258</v>
+        <v>77</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>364</v>
+        <v>126</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>111</v>
+        <v>174</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>05349</t>
+          <t>06249</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>PISTOIA</t>
+          <t>SASSUOLO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,35 +1519,35 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>272</v>
+        <v>228</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>39</v>
+        <v>269</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>53</v>
+        <v>392</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1558,12 +1558,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>05054</t>
+          <t>05349</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>ROSIGNANO MARITTIMO</t>
+          <t>PISTOIA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,51 +1573,51 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>152</v>
+        <v>286</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>117</v>
+        <v>55</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>174</v>
+        <v>258</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>51840</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>BAGNO A RIPOLI</t>
+          <t>FAENZA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,35 +1627,35 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>140</v>
+        <v>93</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>191</v>
+        <v>240</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1685,47 +1685,47 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>23</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>FAENZA</t>
+          <t>BAGNO A RIPOLI</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,39 +1735,39 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>133</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>6</v>
+        <v>71</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1793,28 +1793,28 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>26</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>35</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>4</v>
@@ -1847,31 +1847,31 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>33</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1901,28 +1901,28 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>6</v>
@@ -1955,31 +1955,31 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>0</v>
@@ -2021,19 +2021,19 @@
         <v>0</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2044,12 +2044,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>04634</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>SAN GIOVANNI VALDARNO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,39 +2059,39 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>58</v>
+        <v>163</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>246</v>
+        <v>15</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>264</v>
+        <v>181</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2117,28 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
+        <v>126</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>174</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="H35" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="I35" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="J35" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="K35" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="L35" s="12" t="n">
         <v>112</v>
-      </c>
-      <c r="F35" s="12" t="n">
-        <v>164</v>
-      </c>
-      <c r="G35" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="H35" s="12" t="n">
-        <v>87</v>
-      </c>
-      <c r="I35" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="J35" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="K35" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="L35" s="12" t="n">
-        <v>102</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>8</v>
@@ -2152,12 +2152,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04634</t>
+          <t>53970</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI VALDARNO</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,51 +2167,51 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>55380</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>MONTELUPO FIORENTINO</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,51 +2221,51 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>132</v>
+        <v>63</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>3</v>
+        <v>254</v>
       </c>
       <c r="H37" s="12" t="n">
+        <v>224</v>
+      </c>
+      <c r="I37" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="J37" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="K37" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>275</v>
+      </c>
+      <c r="M37" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I37" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="J37" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="K37" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>123</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>05915</t>
+          <t>55380</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>MONTELUPO FIORENTINO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,51 +2275,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>53970</t>
+          <t>05915</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,39 +2329,39 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2387,31 +2387,31 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2441,28 +2441,28 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>5</v>
@@ -2476,12 +2476,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>04892</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,51 +2491,51 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>173</v>
+        <v>73</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>143</v>
+        <v>100</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>04892</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2545,51 +2545,51 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>67</v>
+        <v>182</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J43" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>93</v>
+        <v>149</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>34802</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>PIOMBINO</t>
+          <t>PRATO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,51 +2599,51 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="G44" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="H44" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="J44" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K44" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H44" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="I44" s="12" t="n">
+      <c r="L44" s="12" t="n">
+        <v>158</v>
+      </c>
+      <c r="M44" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="J44" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K44" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="L44" s="12" t="n">
-        <v>88</v>
-      </c>
-      <c r="M44" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>34802</t>
+          <t>55416</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>PRATO</t>
+          <t>MONSUMMANO TERME</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2657,47 +2657,47 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>55416</t>
+          <t>53676</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>MONSUMMANO TERME</t>
+          <t>PIOMBINO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,39 +2707,39 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="L46" s="12" t="n">
         <v>93</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2765,28 +2765,28 @@
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>1</v>
@@ -2819,28 +2819,28 @@
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J48" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>2</v>
@@ -2873,31 +2873,31 @@
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -2908,12 +2908,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>04516</t>
+          <t>14735</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>CARRARA</t>
+          <t>BORGO SAN LORENZO</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,51 +2923,51 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>05514</t>
+          <t>04516</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI IN PERSICETO</t>
+          <t>CARRARA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,39 +2977,39 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3035,28 +3035,28 @@
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="M52" s="12" t="n">
         <v>1</v>
@@ -3070,12 +3070,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>14735</t>
+          <t>05514</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>BORGO SAN LORENZO</t>
+          <t>SAN GIOVANNI IN PERSICETO</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,39 +3085,39 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3143,28 +3143,28 @@
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G54" s="12" t="n">
         <v>11</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J54" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M54" s="12" t="n">
         <v>1</v>
@@ -3197,35 +3197,35 @@
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G55" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H55" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I55" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="J55" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H55" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I55" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="J55" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="K55" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="M55" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3251,35 +3251,35 @@
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J56" s="12" t="n">
         <v>20</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M56" s="12" t="n">
         <v>41</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3305,47 +3305,47 @@
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J57" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05829</t>
+          <t>05290</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>FERRARA</t>
+          <t>PONTEDERA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,51 +3355,51 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05290</t>
+          <t>05829</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>PONTEDERA</t>
+          <t>FERRARA</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,46 +3409,46 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>05536</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3463,39 +3463,39 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3521,16 +3521,16 @@
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G61" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I61" s="12" t="n">
         <v>31</v>
@@ -3539,10 +3539,10 @@
         <v>7</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="M61" s="12" t="n">
         <v>1</v>
@@ -3556,12 +3556,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>55491</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>BORGO A MOZZANO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,51 +3571,51 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="G62" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="H62" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="J62" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="K62" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="H62" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="I62" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="J62" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="K62" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L62" s="12" t="n">
-        <v>107</v>
-      </c>
       <c r="M62" s="12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>05408</t>
+          <t>05536</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>CHIUSI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,51 +3625,51 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,35 +3679,35 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>39</v>
+        <v>138</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3718,12 +3718,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>05408</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>CHIUSI</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,32 +3733,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>119</v>
+        <v>47</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="M65" s="12" t="n">
         <v>2</v>
@@ -3772,12 +3772,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>55491</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>BORGO A MOZZANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,51 +3787,51 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="H66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>04812</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3841,35 +3841,35 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
@@ -3880,12 +3880,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>06259</t>
+          <t>04812</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,51 +3895,51 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>90</v>
+        <v>148</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>06446</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3949,17 +3949,17 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="H69" s="12" t="n">
         <v>0</v>
@@ -3968,20 +3968,20 @@
         <v>35</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4007,28 +4007,28 @@
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K70" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M70" s="12" t="n">
         <v>11</v>
@@ -4061,19 +4061,19 @@
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J71" s="12" t="n">
         <v>1</v>
@@ -4082,7 +4082,7 @@
         <v>21</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="M71" s="12" t="n">
         <v>4</v>
@@ -4096,12 +4096,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>06446</t>
+          <t>06259</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,39 +4111,39 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="F72" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="G72" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="H72" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I72" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="F72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="H72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="12" t="n">
-        <v>30</v>
-      </c>
       <c r="J72" s="12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K72" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4169,28 +4169,28 @@
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G73" s="12" t="n">
         <v>8</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I73" s="12" t="n">
         <v>23</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M73" s="12" t="n">
         <v>1</v>
@@ -4204,12 +4204,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SAN LAZZARO DI SAVENA</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4226,28 +4226,28 @@
         <v>36</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="J74" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K74" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L74" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="M74" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="K74" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="L74" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="M74" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
@@ -4258,12 +4258,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>MALALBERGO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4273,35 +4273,35 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
@@ -4312,12 +4312,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>05530</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SAN LAZZARO DI SAVENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4331,47 +4331,47 @@
         </is>
       </c>
       <c r="E76" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="F76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="H76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="F76" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="G76" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H76" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="I76" s="12" t="n">
-        <v>24</v>
-      </c>
       <c r="J76" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05530</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MALALBERGO</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4381,39 +4381,39 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J77" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K77" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K77" s="12" t="n">
+      <c r="L77" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="M77" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L77" s="12" t="n">
-        <v>66</v>
-      </c>
-      <c r="M77" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H78" s="12" t="n">
         <v>27</v>
@@ -4457,7 +4457,7 @@
         <v>7</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L78" s="12" t="n">
         <v>39</v>
@@ -4474,12 +4474,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04601</t>
+          <t>05982</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4489,51 +4489,51 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
         <v>30</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="G79" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="H79" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="I79" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="J79" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K79" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L79" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="M79" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H79" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I79" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="J79" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K79" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="L79" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="M79" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>05982</t>
+          <t>04601</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4543,39 +4543,39 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4601,28 +4601,28 @@
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K81" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M81" s="12" t="n">
         <v>0</v>
@@ -4658,13 +4658,13 @@
         <v>27</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G82" s="12" t="n">
         <v>11</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I82" s="12" t="n">
         <v>18</v>
@@ -4709,19 +4709,19 @@
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J83" s="12" t="n">
         <v>3</v>
@@ -4730,10 +4730,10 @@
         <v>12</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
@@ -4744,12 +4744,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04677</t>
+          <t>06363</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>BOMPORTO</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4759,51 +4759,51 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G84" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="M84" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H84" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="I84" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="J84" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="K84" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L84" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="M84" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>54479</t>
+          <t>04677</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>BENTIVOGLIO</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4813,51 +4813,51 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G85" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H85" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="H85" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I85" s="12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J85" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K85" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K85" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="L85" s="12" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="M85" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>53490</t>
+          <t>54479</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SANT'ILARIO D'ENZA</t>
+          <t>BENTIVOGLIO</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4867,51 +4867,51 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J86" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>05055</t>
+          <t>53490</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>SANT'ILARIO D'ENZA</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4921,23 +4921,23 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J87" s="12" t="n">
         <v>4</v>
@@ -4946,26 +4946,26 @@
         <v>4</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>54066</t>
+          <t>54044</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>PIETRASANTA</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4975,51 +4975,51 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="F88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="F88" s="12" t="n">
-        <v>83</v>
-      </c>
-      <c r="G88" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="H88" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="I88" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="J88" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K88" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>54044</t>
+          <t>54066</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>PIETRASANTA</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5029,51 +5029,51 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E89" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="G89" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H89" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="I89" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J89" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H89" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="J89" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="K89" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>06363</t>
+          <t>05055</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>BOMPORTO</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5083,39 +5083,39 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F90" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H90" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J90" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K90" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5198,13 +5198,13 @@
         <v>14</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G92" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I92" s="12" t="n">
         <v>13</v>
@@ -5216,14 +5216,14 @@
         <v>0</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M92" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G93" s="12" t="n">
         <v>1</v>
@@ -5270,7 +5270,7 @@
         <v>6</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="M93" s="12" t="n">
         <v>1</v>
@@ -5306,7 +5306,7 @@
         <v>11</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G94" s="12" t="n">
         <v>0</v>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5486,14 +5486,14 @@
         <v>2</v>
       </c>
       <c r="L97" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M97" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -5630,13 +5630,13 @@
         <v>0</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="G100" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="I100" s="12" t="n">
         <v>0</v>
@@ -5684,13 +5684,13 @@
         <v>0</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G101" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H101" s="12" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="I101" s="12" t="n">
         <v>0</v>
@@ -5738,7 +5738,7 @@
         <v>0</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G102" s="12" t="n">
         <v>0</v>
@@ -5792,13 +5792,13 @@
         <v>0</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="G103" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H103" s="12" t="n">
-        <v>489</v>
+        <v>509</v>
       </c>
       <c r="I103" s="12" t="n">
         <v>0</v>
@@ -5900,13 +5900,13 @@
         <v>0</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G105" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H105" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I105" s="12" t="n">
         <v>0</v>
@@ -5954,7 +5954,7 @@
         <v>0</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G106" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N106" headerRowCount="1">
-  <autoFilter ref="A10:N106"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N95" headerRowCount="1">
+  <autoFilter ref="A10:N95"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N106"/>
+  <dimension ref="A1:N95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,16 +673,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>10452</v>
+        <v>7940</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>7941</v>
+        <v>5923</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>4988</v>
+        <v>3926</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -802,12 +802,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>14728</t>
+          <t>05332</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>PRATO</t>
+          <t>PISTOIA</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>1251</v>
+        <v>651</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1245</v>
+        <v>661</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>311</v>
+        <v>258</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>1105</v>
+        <v>497</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>486</v>
+        <v>187</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>544</v>
+        <v>567</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>30</v>
+        <v>123</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -856,12 +856,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>05332</t>
+          <t>04739</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>PISTOIA</t>
+          <t>CALENZANO</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -871,51 +871,51 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>651</v>
+        <v>488</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>661</v>
+        <v>628</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>258</v>
+        <v>481</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>455</v>
+        <v>751</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>497</v>
+        <v>359</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>567</v>
+        <v>437</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>22960</t>
+          <t>25515</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -925,35 +925,35 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>579</v>
+        <v>388</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>479</v>
+        <v>362</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>869</v>
+        <v>156</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>434</v>
+        <v>323</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>204</v>
+        <v>165</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>131</v>
+        <v>50</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>726</v>
+        <v>298</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>189</v>
+        <v>34</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -964,12 +964,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>04739</t>
+          <t>05112</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CALENZANO</t>
+          <t>LUCCA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -979,32 +979,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>488</v>
+        <v>303</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>628</v>
+        <v>393</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>481</v>
+        <v>38</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>751</v>
+        <v>130</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>359</v>
+        <v>243</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>133</v>
+        <v>58</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>437</v>
+        <v>241</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>3</v>
@@ -1018,12 +1018,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>25515</t>
+          <t>06334</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>VIGNOLA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,35 +1033,35 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>388</v>
+        <v>270</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>362</v>
+        <v>234</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>466</v>
+        <v>201</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>156</v>
+        <v>226</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>323</v>
+        <v>236</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>298</v>
+        <v>240</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1072,12 +1072,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05112</t>
+          <t>04845</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>LUCCA</t>
+          <t>FUCECCHIO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,35 +1087,35 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>303</v>
+        <v>269</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>393</v>
+        <v>312</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>243</v>
+        <v>207</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>241</v>
+        <v>147</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>06334</t>
+          <t>53815</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>VIGNOLA</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,51 +1141,51 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>234</v>
+        <v>356</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>226</v>
+        <v>88</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>236</v>
+        <v>172</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04845</t>
+          <t>05918</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>FUCECCHIO</t>
+          <t>SANTARCANGELO DI ROMAGNA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,35 +1195,35 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>269</v>
+        <v>228</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>312</v>
+        <v>240</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>207</v>
+        <v>146</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1234,12 +1234,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>58414</t>
+          <t>05291</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>PISA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,51 +1249,51 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>226</v>
+        <v>312</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>25</v>
+        <v>225</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>200</v>
+        <v>102</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>150</v>
+        <v>198</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>365</v>
+        <v>212</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>53815</t>
+          <t>05054</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>ROSIGNANO MARITTIMO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,51 +1303,51 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>247</v>
+        <v>197</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>356</v>
+        <v>155</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>258</v>
+        <v>190</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>05918</t>
+          <t>06249</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SANTARCANGELO DI ROMAGNA</t>
+          <t>SASSUOLO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,35 +1357,35 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
+        <v>195</v>
+      </c>
+      <c r="F21" s="12" t="n">
         <v>228</v>
       </c>
-      <c r="F21" s="12" t="n">
-        <v>240</v>
-      </c>
       <c r="G21" s="12" t="n">
-        <v>15</v>
+        <v>269</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>63</v>
+        <v>392</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>158</v>
+        <v>233</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1396,12 +1396,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05291</t>
+          <t>05349</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>PISA</t>
+          <t>PISTOIA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,35 +1411,35 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>226</v>
+        <v>177</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>312</v>
+        <v>286</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>225</v>
+        <v>47</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>198</v>
+        <v>135</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>121</v>
+        <v>64</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>212</v>
+        <v>258</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05054</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ROSIGNANO MARITTIMO</t>
+          <t>FAENZA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>126</v>
+        <v>58</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>174</v>
+        <v>93</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>190</v>
+        <v>240</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1504,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>06249</t>
+          <t>05245</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SASSUOLO</t>
+          <t>VECCHIANO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,51 +1519,51 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>228</v>
+        <v>44</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>269</v>
+        <v>180</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>392</v>
+        <v>5</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>233</v>
+        <v>137</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>05349</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>PISTOIA</t>
+          <t>BAGNO A RIPOLI</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,51 +1573,51 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>286</v>
+        <v>133</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>258</v>
+        <v>200</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>34710</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>FAENZA</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,51 +1627,51 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>175</v>
+        <v>147</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>143</v>
+        <v>236</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>240</v>
+        <v>432</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>05245</t>
+          <t>25554</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>VECCHIANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,35 +1681,35 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>180</v>
+        <v>34</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>149</v>
+        <v>106</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>137</v>
+        <v>266</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>17</v>
+        <v>103</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>51840</t>
+          <t>06019</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>BAGNO A RIPOLI</t>
+          <t>MISANO ADRIATICO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,35 +1735,35 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1774,12 +1774,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>34710</t>
+          <t>05911</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,51 +1789,51 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>236</v>
+        <v>108</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>432</v>
+        <v>106</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,51 +1843,51 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="G30" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>103</v>
+      </c>
+      <c r="J30" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="H30" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="I30" s="12" t="n">
-        <v>106</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <v>55</v>
-      </c>
       <c r="K30" s="12" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>266</v>
+        <v>333</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>103</v>
+        <v>6</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>06019</t>
+          <t>04634</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>MISANO ADRIATICO</t>
+          <t>SAN GIOVANNI VALDARNO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,46 +1897,46 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>05911</t>
+          <t>53970</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1955,31 +1955,31 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>83</v>
+        <v>16</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -1990,12 +1990,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>34723</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,32 +2005,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>3</v>
+        <v>254</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>333</v>
+        <v>275</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>6</v>
@@ -2044,12 +2044,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>04634</t>
+          <t>55380</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI VALDARNO</t>
+          <t>MONTELUPO FIORENTINO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,35 +2059,35 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>181</v>
+        <v>131</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2098,12 +2098,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>06416</t>
+          <t>05915</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,23 +2113,23 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J35" s="12" t="n">
         <v>25</v>
@@ -2138,26 +2138,26 @@
         <v>36</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>53970</t>
+          <t>06210</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>CARPI</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,35 +2167,35 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>132</v>
+        <v>86</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>158</v>
+        <v>97</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2206,12 +2206,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>05239</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>SAN MINIATO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,51 +2221,51 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>254</v>
+        <v>19</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>224</v>
+        <v>20</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>275</v>
+        <v>128</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>55380</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>MONTELUPO FIORENTINO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,51 +2275,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>147</v>
+        <v>73</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>05915</t>
+          <t>04892</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,51 +2329,51 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>81</v>
+        <v>182</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>06210</t>
+          <t>34802</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>CARPI</t>
+          <t>PRATO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,51 +2383,51 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>97</v>
+        <v>158</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>05239</t>
+          <t>55416</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SAN MINIATO</t>
+          <t>MONSUMMANO TERME</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,35 +2437,35 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2476,12 +2476,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>53676</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>PIOMBINO</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,35 +2491,35 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2530,12 +2530,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>04892</t>
+          <t>05543</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>SASSO MARCONI</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2545,51 +2545,51 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>182</v>
+        <v>76</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>34802</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>PRATO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,35 +2599,35 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2638,12 +2638,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>55416</t>
+          <t>14735</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>MONSUMMANO TERME</t>
+          <t>BORGO SAN LORENZO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2653,51 +2653,51 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="G45" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="I45" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="H45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="12" t="n">
-        <v>87</v>
-      </c>
       <c r="J45" s="12" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>04516</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>PIOMBINO</t>
+          <t>CARRARA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,35 +2707,35 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="J46" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="K46" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="L46" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="F46" s="12" t="n">
-        <v>84</v>
-      </c>
-      <c r="G46" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="H46" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="I46" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="J46" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K46" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="L46" s="12" t="n">
-        <v>93</v>
-      </c>
       <c r="M46" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
@@ -2746,12 +2746,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>05543</t>
+          <t>05941</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>SASSO MARCONI</t>
+          <t>FORLÌ</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,51 +2761,51 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>64</v>
+        <v>393</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>05514</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SAN GIOVANNI IN PERSICETO</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,51 +2815,51 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="F48" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="H48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="J48" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K48" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L48" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="G48" s="12" t="n">
-        <v>89</v>
-      </c>
-      <c r="H48" s="12" t="n">
-        <v>133</v>
-      </c>
-      <c r="I48" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="J48" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="K48" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="L48" s="12" t="n">
-        <v>189</v>
-      </c>
       <c r="M48" s="12" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>58000</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>MIRANDOLA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,51 +2869,51 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>137</v>
+        <v>91</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14735</t>
+          <t>55420</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>BORGO SAN LORENZO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,51 +2923,51 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>04516</t>
+          <t>04951</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>CARRARA</t>
+          <t>GROSSETO</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,51 +2977,51 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="G51" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>05941</t>
+          <t>05290</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>FORLÌ</t>
+          <t>PONTEDERA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3031,35 +3031,35 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>393</v>
+        <v>13</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>145</v>
+        <v>91</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -3070,12 +3070,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>05514</t>
+          <t>05829</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI IN PERSICETO</t>
+          <t>FERRARA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,51 +3085,51 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="H53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>58000</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>MIRANDOLA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G54" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="H54" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="I54" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="J54" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="K54" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="H54" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="I54" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="J54" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K54" s="12" t="n">
-        <v>34</v>
-      </c>
       <c r="L54" s="12" t="n">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>55420</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,51 +3193,51 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H55" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I55" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="J55" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I55" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="J55" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="K55" s="12" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06403</t>
+          <t>55491</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>GUASTALLA</t>
+          <t>BORGO A MOZZANO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,51 +3247,51 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>04951</t>
+          <t>05536</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>GROSSETO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,51 +3301,51 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I57" s="12" t="n">
         <v>44</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05290</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>PONTEDERA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,35 +3355,35 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
@@ -3394,12 +3394,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05829</t>
+          <t>05408</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>FERRARA</t>
+          <t>CHIUSI</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,46 +3409,46 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3467,31 +3467,31 @@
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
@@ -3502,12 +3502,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>04812</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,35 +3517,35 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>71</v>
+        <v>148</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
@@ -3556,12 +3556,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>55491</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>BORGO A MOZZANO</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,51 +3571,51 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>30</v>
+        <v>117</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>05536</t>
+          <t>06259</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,51 +3625,51 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K63" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>04653</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>CASTIGLION FIORENTINO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,35 +3679,35 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>138</v>
+        <v>39</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3718,12 +3718,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>05408</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>CHIUSI</t>
+          <t>SAN LAZZARO DI SAVENA</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,32 +3733,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="M65" s="12" t="n">
         <v>2</v>
@@ -3772,7 +3772,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3791,47 +3791,47 @@
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="M66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>05530</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3841,51 +3841,51 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J67" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>04812</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>MALALBERGO</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,35 +3895,35 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="H68" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="I68" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="J68" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K68" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I68" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="J68" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="K68" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="L68" s="12" t="n">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
@@ -3934,12 +3934,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>06446</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>SANTA CROCE SULL'ARNO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3949,51 +3949,51 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>05982</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>MONTECCHIO EMILIA</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4003,35 +4003,35 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="F70" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="F70" s="12" t="n">
-        <v>81</v>
-      </c>
       <c r="G70" s="12" t="n">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J70" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K70" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K70" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="L70" s="12" t="n">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
@@ -4042,12 +4042,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>04601</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4057,51 +4057,51 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>133</v>
+        <v>9</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>06259</t>
+          <t>04978</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>SCARLINO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,51 +4111,51 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>04653</t>
+          <t>54101</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLION FIORENTINO</t>
+          <t>CECINA</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4165,35 +4165,35 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
@@ -4204,12 +4204,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>05099</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SAN LAZZARO DI SAVENA</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4219,35 +4219,35 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G74" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H74" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="I74" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J74" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H74" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="I74" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="J74" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="K74" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
@@ -4258,12 +4258,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>06363</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>BOMPORTO</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4273,51 +4273,51 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J75" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K75" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L75" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="M75" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K75" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="L75" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="M75" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05530</t>
+          <t>04677</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4327,51 +4327,51 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K76" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>54479</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>MALALBERGO</t>
+          <t>BENTIVOGLIO</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4381,51 +4381,51 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="J77" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>34201</t>
+          <t>54044</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SANTA CROCE SULL'ARNO</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4435,51 +4435,51 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G78" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H78" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="I78" s="12" t="n">
-        <v>24</v>
-      </c>
       <c r="J78" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>05982</t>
+          <t>54066</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>PIETRASANTA</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4489,35 +4489,35 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
@@ -4528,12 +4528,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>04601</t>
+          <t>05055</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4543,35 +4543,35 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
@@ -4582,12 +4582,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>04978</t>
+          <t>05589</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>SCARLINO</t>
+          <t>ZOLA PREDOSA</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4597,32 +4597,32 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M81" s="12" t="n">
         <v>0</v>
@@ -4636,12 +4636,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>54101</t>
+          <t>25518</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>CECINA</t>
+          <t>CASALECCHIO DI RENO</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4651,51 +4651,51 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>TODESCATO MARCO</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05099</t>
+          <t>54593</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4705,35 +4705,35 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>51</v>
+        <v>112</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
@@ -4744,12 +4744,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>06363</t>
+          <t>05512</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>BOMPORTO</t>
+          <t>CASTEL SAN PIETRO TERME</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4759,51 +4759,51 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04677</t>
+          <t>05160</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>BORGO A MOZZANO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4813,51 +4813,51 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="M85" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>54479</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>BENTIVOGLIO</t>
+          <t>MONTIGNOSO</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4867,32 +4867,32 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J86" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="M86" s="12" t="n">
         <v>1</v>
@@ -4906,12 +4906,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>53490</t>
+          <t>05241</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SANT'ILARIO D'ENZA</t>
+          <t>SAN GIULIANO TERME</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4921,51 +4921,51 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J87" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>54044</t>
+          <t>01300</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4975,51 +4975,51 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J88" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K88" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>54066</t>
+          <t>04840</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>PIETRASANTA</t>
+          <t>BARBERINO DI MUGELLO</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5029,35 +5029,35 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E89" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>86</v>
+        <v>181</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J89" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
@@ -5068,12 +5068,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05055</t>
+          <t>06353</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5083,51 +5083,51 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J90" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K90" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05589</t>
+          <t>06408</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>ZOLA PREDOSA</t>
+          <t>CORREGGIO</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5137,51 +5137,51 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E91" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H91" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J91" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>25518</t>
+          <t>14730</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>CASALECCHIO DI RENO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5191,51 +5191,51 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>TODESCATO MARCO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E92" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>21</v>
+        <v>312</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>2</v>
+        <v>509</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J92" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K92" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="M92" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>54593</t>
+          <t>15552</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5245,35 +5245,35 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E93" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I93" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J93" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
@@ -5284,12 +5284,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05512</t>
+          <t>15572</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN PIETRO TERME</t>
+          <t>MOLINELLA</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5299,14 +5299,14 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E94" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="G94" s="12" t="n">
         <v>0</v>
@@ -5315,19 +5315,19 @@
         <v>3</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J94" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K94" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
@@ -5338,12 +5338,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>22966</t>
+          <t>53624</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>BERCETO</t>
+          <t>FOLLONICA</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5353,631 +5353,37 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>IACOPINI ALESSANDRA</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="E95" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H95" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I95" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J95" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N95" s="2" t="inlineStr">
-        <is>
-          <t>Da seguire</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>05160</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>BORGO A MOZZANO</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>CASCIARI PAOLO</t>
-        </is>
-      </c>
-      <c r="E96" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F96" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="G96" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H96" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I96" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J96" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K96" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M96" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N96" s="2" t="inlineStr">
-        <is>
-          <t>Da seguire</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>11295</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>MONTIGNOSO</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>CASCIARI PAOLO</t>
-        </is>
-      </c>
-      <c r="E97" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="F97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="H97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J97" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K97" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L97" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="M97" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>05241</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>SAN GIULIANO TERME</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>CIULLA VALERIO</t>
-        </is>
-      </c>
-      <c r="E98" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="F98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J98" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="M98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>01300</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>COLLESALVETTI</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>CASCIARI PAOLO</t>
-        </is>
-      </c>
-      <c r="E99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="G99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="I99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>04840</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>BARBERINO DI MUGELLO</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>CORSI PAOLA</t>
-        </is>
-      </c>
-      <c r="E100" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" s="12" t="n">
-        <v>181</v>
-      </c>
-      <c r="G100" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="I100" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>06353</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>MODENA</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>PIETRANTONIO GIULIANO</t>
-        </is>
-      </c>
-      <c r="E101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" s="12" t="n">
-        <v>87</v>
-      </c>
-      <c r="G101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="12" t="n">
-        <v>130</v>
-      </c>
-      <c r="I101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>06408</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>CORREGGIO</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>CARCIONE PARIDE</t>
-        </is>
-      </c>
-      <c r="E102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="G102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>14730</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>FIRENZE</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>CORSI PAOLA</t>
-        </is>
-      </c>
-      <c r="E103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" s="12" t="n">
-        <v>312</v>
-      </c>
-      <c r="G103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" s="12" t="n">
-        <v>509</v>
-      </c>
-      <c r="I103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>15552</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>IMOLA</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>MURGO LORENZO</t>
-        </is>
-      </c>
-      <c r="E104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="G104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="I104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>15572</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>MOLINELLA</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>LIBANORI FEDERICO</t>
-        </is>
-      </c>
-      <c r="E105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="G105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>53624</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>FOLLONICA</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>ANTONINI GABRIELE</t>
-        </is>
-      </c>
-      <c r="E106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="G106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N95" headerRowCount="1">
-  <autoFilter ref="A10:N95"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N94" headerRowCount="1">
+  <autoFilter ref="A10:N94"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N95"/>
+  <dimension ref="A1:N94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,16 +673,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>7940</v>
+        <v>7886</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5923</v>
+        <v>5875</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3926</v>
+        <v>3925</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -3070,12 +3070,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>05829</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>FERRARA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,35 +3085,35 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
@@ -3124,12 +3124,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>55491</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>BORGO A MOZZANO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,51 +3193,51 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>55491</t>
+          <t>05536</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>BORGO A MOZZANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,51 +3247,51 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>05536</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3308,44 +3308,44 @@
         <v>50</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>05408</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>CHIUSI</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,32 +3355,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J58" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="K58" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K58" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="L58" s="12" t="n">
-        <v>138</v>
+        <v>88</v>
       </c>
       <c r="M58" s="12" t="n">
         <v>2</v>
@@ -3394,12 +3394,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05408</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>CHIUSI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,51 +3409,51 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J59" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>04812</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,51 +3463,51 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K60" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04812</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,35 +3517,35 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>11</v>
+        <v>133</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
@@ -3556,12 +3556,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>06259</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,35 +3571,35 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>133</v>
+        <v>3</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
@@ -3610,12 +3610,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>06259</t>
+          <t>04653</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>CASTIGLION FIORENTINO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,35 +3625,35 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
@@ -3664,12 +3664,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>04653</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLION FIORENTINO</t>
+          <t>SAN LAZZARO DI SAVENA</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,35 +3679,35 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3718,12 +3718,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SAN LAZZARO DI SAVENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3740,28 +3740,28 @@
         <v>36</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>05530</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3791,47 +3791,47 @@
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>05530</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MALALBERGO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3841,51 +3841,51 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
         <v>35</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K67" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L67" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="M67" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L67" s="12" t="n">
-        <v>67</v>
-      </c>
-      <c r="M67" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>MALALBERGO</t>
+          <t>SANTA CROCE SULL'ARNO</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,35 +3895,35 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="I68" s="12" t="n">
         <v>24</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
@@ -3934,12 +3934,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>34201</t>
+          <t>05982</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SANTA CROCE SULL'ARNO</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3949,35 +3949,35 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H69" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="I69" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="I69" s="12" t="n">
-        <v>24</v>
-      </c>
       <c r="J69" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
@@ -3988,12 +3988,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>05982</t>
+          <t>04601</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4003,51 +4003,51 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
         <v>30</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04601</t>
+          <t>04978</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>SCARLINO</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4057,51 +4057,51 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>04978</t>
+          <t>54101</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SCARLINO</t>
+          <t>CECINA</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4115,47 +4115,47 @@
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>54101</t>
+          <t>05099</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>CECINA</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4165,32 +4165,32 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
         <v>27</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="M73" s="12" t="n">
         <v>7</v>
@@ -4204,12 +4204,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>05099</t>
+          <t>06363</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>BOMPORTO</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4219,51 +4219,51 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06363</t>
+          <t>04677</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>BOMPORTO</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4273,51 +4273,51 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G75" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I75" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="H75" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="J75" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>04677</t>
+          <t>54479</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>BENTIVOGLIO</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4327,51 +4327,51 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="M76" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>54479</t>
+          <t>54044</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>BENTIVOGLIO</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G77" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="J77" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K77" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L77" s="12" t="n">
         <v>10</v>
-      </c>
-      <c r="H77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="J77" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K77" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="L77" s="12" t="n">
-        <v>60</v>
       </c>
       <c r="M77" s="12" t="n">
         <v>1</v>
@@ -4420,12 +4420,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>54044</t>
+          <t>54066</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>PIETRASANTA</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4435,51 +4435,51 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="G78" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H78" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="I78" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J78" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K78" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="J78" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K78" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="L78" s="12" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>54066</t>
+          <t>05055</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>PIETRASANTA</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4489,51 +4489,51 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F79" s="12" t="n">
-        <v>86</v>
-      </c>
-      <c r="G79" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="H79" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>05055</t>
+          <t>05589</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>ZOLA PREDOSA</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4543,51 +4543,51 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>05589</t>
+          <t>25518</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>ZOLA PREDOSA</t>
+          <t>CASALECCHIO DI RENO</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4597,32 +4597,32 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>TODESCATO MARCO</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="M81" s="12" t="n">
         <v>0</v>
@@ -4636,12 +4636,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>25518</t>
+          <t>54593</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>CASALECCHIO DI RENO</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4651,51 +4651,51 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>TODESCATO MARCO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
         <v>14</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="G82" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H82" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I82" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J82" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I82" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="K82" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>54593</t>
+          <t>05512</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>CASTEL SAN PIETRO TERME</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4705,32 +4705,32 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I83" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="M83" s="12" t="n">
         <v>1</v>
@@ -4744,12 +4744,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>05512</t>
+          <t>05160</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN PIETRO TERME</t>
+          <t>BORGO A MOZZANO</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4759,51 +4759,51 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="M84" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>05160</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>BORGO A MOZZANO</t>
+          <t>MONTIGNOSO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4817,47 +4817,47 @@
         </is>
       </c>
       <c r="E85" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J85" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M85" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11295</t>
+          <t>05241</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>MONTIGNOSO</t>
+          <t>SAN GIULIANO TERME</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4867,35 +4867,35 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J86" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
@@ -4906,12 +4906,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>05241</t>
+          <t>01300</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO TERME</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4921,51 +4921,51 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>01300</t>
+          <t>04840</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>BARBERINO DI MUGELLO</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4975,20 +4975,20 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>54</v>
+        <v>181</v>
       </c>
       <c r="G88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I88" s="12" t="n">
         <v>0</v>
@@ -5014,12 +5014,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>04840</t>
+          <t>06353</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>BARBERINO DI MUGELLO</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5029,20 +5029,20 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="E89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>181</v>
+        <v>87</v>
       </c>
       <c r="G89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="I89" s="12" t="n">
         <v>0</v>
@@ -5068,12 +5068,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>06353</t>
+          <t>06408</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>CORREGGIO</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5083,20 +5083,20 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="G90" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="I90" s="12" t="n">
         <v>0</v>
@@ -5122,12 +5122,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>06408</t>
+          <t>14730</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>CORREGGIO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5137,20 +5137,20 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="E91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>34</v>
+        <v>312</v>
       </c>
       <c r="G91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H91" s="12" t="n">
-        <v>1</v>
+        <v>509</v>
       </c>
       <c r="I91" s="12" t="n">
         <v>0</v>
@@ -5176,12 +5176,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>14730</t>
+          <t>15552</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5191,20 +5191,20 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="E92" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>312</v>
+        <v>72</v>
       </c>
       <c r="G92" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>509</v>
+        <v>7</v>
       </c>
       <c r="I92" s="12" t="n">
         <v>0</v>
@@ -5230,12 +5230,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>15552</t>
+          <t>15572</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>MOLINELLA</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5245,20 +5245,20 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="E93" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="G93" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H93" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I93" s="12" t="n">
         <v>0</v>
@@ -5284,12 +5284,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>15572</t>
+          <t>53624</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>MOLINELLA</t>
+          <t>FOLLONICA</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5299,14 +5299,14 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="E94" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G94" s="12" t="n">
         <v>0</v>
@@ -5330,60 +5330,6 @@
         <v>0</v>
       </c>
       <c r="N94" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>53624</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>FOLLONICA</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>ANTONINI GABRIELE</t>
-        </is>
-      </c>
-      <c r="E95" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="G95" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I95" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N94" headerRowCount="1">
-  <autoFilter ref="A10:N94"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N95" headerRowCount="1">
+  <autoFilter ref="A10:N95"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N94"/>
+  <dimension ref="A1:N95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,7 +673,7 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>7886</v>
@@ -5335,6 +5335,56 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>05920</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>FORLI'</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr"/>
+      <c r="E95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>

--- a/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N95" headerRowCount="1">
-  <autoFilter ref="A10:N95"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O95" headerRowCount="1">
+  <autoFilter ref="A10:O95"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N95"/>
+  <dimension ref="A1:O95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>R.A. FI-MARE / VIA NICCOLO' MACCHIAVELLI 287</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>DE LUCA ANTONIO</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>651</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>661</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>258</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>455</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>497</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>187</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>144</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>567</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>123</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA VITTORIO EMANUELE SNC - LOC.SPAZZAVENTO</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>CORSI PAOLA</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>488</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>628</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>481</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>751</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>359</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>133</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>437</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA M.E.LEPIDO 206</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>388</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>362</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>466</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>156</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>323</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>165</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>298</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -974,42 +1005,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>FRAZ-S-VITO STR-PROV</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>CASCIARI PAOLO</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>303</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>393</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>130</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>243</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>241</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1028,42 +1064,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA PER SPILAMBERTO 1015</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>LIBANORI FEDERICO</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>270</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>234</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>201</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>226</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>236</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>240</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1082,42 +1123,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIALE BUOZZI 122/124</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>269</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>312</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>207</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1136,42 +1182,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA CONSOLARE SAN MARINO 7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>247</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>356</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>172</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>258</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>152</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1190,42 +1241,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA EMILIA, 1837</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>CALIO' ANTONELLA</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>228</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>240</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="I18" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="J18" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="L18" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="M18" s="12" t="n">
         <v>158</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="N18" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1244,42 +1300,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA CISANELLO 170</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>226</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>312</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>225</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="J19" s="12" t="n">
         <v>198</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>121</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="L19" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="M19" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="N19" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1298,42 +1359,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA AURELIA, 340</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>MUFFATO LORENZO</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>197</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>155</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="I20" s="12" t="n">
         <v>126</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>174</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="L20" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="M20" s="12" t="n">
         <v>190</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="N20" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1352,42 +1418,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA PIA</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>195</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>228</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>269</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="I21" s="12" t="n">
         <v>392</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="J21" s="12" t="n">
         <v>127</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="K21" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="L21" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="M21" s="12" t="n">
         <v>233</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="N21" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1406,42 +1477,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>MACALLE', 26</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>DE LUCA ANTONIO</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>286</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="I22" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="J22" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="K22" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="L22" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="M22" s="12" t="n">
         <v>258</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="N22" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1460,42 +1536,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>GRANAROLO, 177</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>CALIO' ANTONELLA</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>175</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>143</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="H23" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="I23" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="J23" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="K23" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="L23" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="M23" s="12" t="n">
         <v>240</v>
       </c>
-      <c r="M23" s="12" t="n">
+      <c r="N23" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1514,42 +1595,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA PROV.LE VECCHIANESE 38</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>CIULLA VALERIO</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>171</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>180</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="I24" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="J24" s="12" t="n">
         <v>149</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="K24" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="L24" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L24" s="12" t="n">
+      <c r="M24" s="12" t="n">
         <v>137</v>
       </c>
-      <c r="M24" s="12" t="n">
+      <c r="N24" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1568,42 +1654,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>SS 222 KM 2+340 PONTE A EMA</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>CORSI PAOLA</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>170</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>133</v>
-      </c>
-      <c r="G25" s="12" t="n">
-        <v>71</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>71</v>
       </c>
       <c r="I25" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="J25" s="12" t="n">
         <v>149</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="K25" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="K25" s="12" t="n">
+      <c r="L25" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L25" s="12" t="n">
+      <c r="M25" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="N25" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1622,42 +1713,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA ENRICO DE NICOLA 47/A - 47/B</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>CORSI PAOLA</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>236</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="H26" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="H26" s="12" t="n">
+      <c r="I26" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="J26" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="K26" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="K26" s="12" t="n">
+      <c r="L26" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="L26" s="12" t="n">
+      <c r="M26" s="12" t="n">
         <v>432</v>
       </c>
-      <c r="M26" s="12" t="n">
+      <c r="N26" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1676,42 +1772,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA NUOVA BAZZANESE 8</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>MURGO LORENZO</t>
         </is>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>138</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>138</v>
       </c>
       <c r="G27" s="12" t="n">
+        <v>138</v>
+      </c>
+      <c r="H27" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="I27" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="I27" s="12" t="n">
+      <c r="J27" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="K27" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="K27" s="12" t="n">
+      <c r="L27" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="M27" s="12" t="n">
         <v>266</v>
       </c>
-      <c r="M27" s="12" t="n">
+      <c r="N27" s="12" t="n">
         <v>103</v>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1730,42 +1831,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA NAZIONALE ADRIATICA 148</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>138</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="H28" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="H28" s="12" t="n">
+      <c r="I28" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="I28" s="12" t="n">
+      <c r="J28" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="K28" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="K28" s="12" t="n">
+      <c r="L28" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="L28" s="12" t="n">
+      <c r="M28" s="12" t="n">
         <v>174</v>
       </c>
-      <c r="M28" s="12" t="n">
+      <c r="N28" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1784,42 +1890,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA ROMEA 1498</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
           <t>CELLINI LUCA</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H29" s="12" t="n">
+      <c r="I29" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="J29" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="K29" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K29" s="12" t="n">
+      <c r="L29" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="M29" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="M29" s="12" t="n">
+      <c r="N29" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1838,42 +1949,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIALE NENNI 19 -21</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>130</v>
       </c>
-      <c r="F30" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H30" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="12" t="n">
         <v>103</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="K30" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="K30" s="12" t="n">
+      <c r="L30" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="L30" s="12" t="n">
+      <c r="M30" s="12" t="n">
         <v>333</v>
       </c>
-      <c r="M30" s="12" t="n">
+      <c r="N30" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1892,42 +2008,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA UBALDINO PERUZZI</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>PETRELLI DANIELE</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>128</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>163</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H31" s="12" t="n">
+      <c r="I31" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="I31" s="12" t="n">
+      <c r="J31" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="J31" s="12" t="n">
+      <c r="K31" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="K31" s="12" t="n">
+      <c r="L31" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="L31" s="12" t="n">
+      <c r="M31" s="12" t="n">
         <v>181</v>
       </c>
-      <c r="M31" s="12" t="n">
+      <c r="N31" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1946,42 +2067,47 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA CALCINARO 2460</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>CELLINI LUCA</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>126</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>132</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="H32" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="H32" s="12" t="n">
+      <c r="I32" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="I32" s="12" t="n">
+      <c r="J32" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="J32" s="12" t="n">
+      <c r="K32" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="K32" s="12" t="n">
+      <c r="L32" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="L32" s="12" t="n">
+      <c r="M32" s="12" t="n">
         <v>158</v>
       </c>
-      <c r="M32" s="12" t="n">
+      <c r="N32" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2000,42 +2126,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA SELICE KM. 2</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>121</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="H33" s="12" t="n">
         <v>254</v>
       </c>
-      <c r="H33" s="12" t="n">
+      <c r="I33" s="12" t="n">
         <v>224</v>
       </c>
-      <c r="I33" s="12" t="n">
+      <c r="J33" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="J33" s="12" t="n">
+      <c r="K33" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="K33" s="12" t="n">
+      <c r="L33" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="M33" s="12" t="n">
         <v>275</v>
       </c>
-      <c r="M33" s="12" t="n">
+      <c r="N33" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2054,42 +2185,47 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA TOSCO ROMAGNOLO SUD 36 - LOC. FIBBIANA</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>115</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="H34" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="12" t="n">
+      <c r="I34" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I34" s="12" t="n">
+      <c r="J34" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="J34" s="12" t="n">
+      <c r="K34" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="K34" s="12" t="n">
+      <c r="L34" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="L34" s="12" t="n">
+      <c r="M34" s="12" t="n">
         <v>131</v>
       </c>
-      <c r="M34" s="12" t="n">
+      <c r="N34" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2108,42 +2244,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA FLAMINIA 3</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="H35" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="H35" s="12" t="n">
+      <c r="I35" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I35" s="12" t="n">
+      <c r="J35" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="J35" s="12" t="n">
+      <c r="K35" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K35" s="12" t="n">
+      <c r="L35" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="L35" s="12" t="n">
+      <c r="M35" s="12" t="n">
         <v>136</v>
       </c>
-      <c r="M35" s="12" t="n">
+      <c r="N35" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2162,42 +2303,47 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA MANZONI</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>LIBANORI FEDERICO</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>105</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="H36" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H36" s="12" t="n">
+      <c r="I36" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="I36" s="12" t="n">
+      <c r="J36" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="J36" s="12" t="n">
+      <c r="K36" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="K36" s="12" t="n">
+      <c r="L36" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L36" s="12" t="n">
+      <c r="M36" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="M36" s="12" t="n">
+      <c r="N36" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2216,42 +2362,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA PANNOCCHIA 90 - LOC. PONTE A EGOLA</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>CIULLA VALERIO</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>131</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="H37" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H37" s="12" t="n">
+      <c r="I37" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="I37" s="12" t="n">
+      <c r="J37" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="J37" s="12" t="n">
+      <c r="K37" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="K37" s="12" t="n">
+      <c r="L37" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="L37" s="12" t="n">
+      <c r="M37" s="12" t="n">
         <v>128</v>
       </c>
-      <c r="M37" s="12" t="n">
+      <c r="N37" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2270,42 +2421,47 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA FERRARESE 166</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="H38" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="H38" s="12" t="n">
+      <c r="I38" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="I38" s="12" t="n">
+      <c r="J38" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="J38" s="12" t="n">
+      <c r="K38" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="K38" s="12" t="n">
+      <c r="L38" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L38" s="12" t="n">
+      <c r="M38" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="M38" s="12" t="n">
+      <c r="N38" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2324,42 +2480,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA SESTESE, 97/99</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>CORSI PAOLA</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>182</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="H39" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H39" s="12" t="n">
+      <c r="I39" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="I39" s="12" t="n">
+      <c r="J39" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="J39" s="12" t="n">
+      <c r="K39" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="K39" s="12" t="n">
+      <c r="L39" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="L39" s="12" t="n">
+      <c r="M39" s="12" t="n">
         <v>149</v>
       </c>
-      <c r="M39" s="12" t="n">
+      <c r="N39" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2378,42 +2539,47 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>XVI APRILE</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
           <t>DE LUCA ANTONIO</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="H40" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="H40" s="12" t="n">
+      <c r="I40" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="I40" s="12" t="n">
+      <c r="J40" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="J40" s="12" t="n">
+      <c r="K40" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="K40" s="12" t="n">
+      <c r="L40" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L40" s="12" t="n">
+      <c r="M40" s="12" t="n">
         <v>158</v>
       </c>
-      <c r="M40" s="12" t="n">
+      <c r="N40" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2432,42 +2598,47 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>DELLA COSTITUZIONE, 138</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
           <t>DE LUCA ANTONIO</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="F41" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="H41" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="J41" s="12" t="n">
+      <c r="K41" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="K41" s="12" t="n">
+      <c r="L41" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L41" s="12" t="n">
+      <c r="M41" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="M41" s="12" t="n">
+      <c r="N41" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2486,42 +2657,47 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIALE UNITA' D'ITALIA 121</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>MUFFATO LORENZO</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="H42" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H42" s="12" t="n">
+      <c r="I42" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="I42" s="12" t="n">
+      <c r="J42" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="J42" s="12" t="n">
+      <c r="K42" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="K42" s="12" t="n">
+      <c r="L42" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="L42" s="12" t="n">
+      <c r="M42" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="M42" s="12" t="n">
+      <c r="N42" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2540,42 +2716,47 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA KENNEDY 7</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
           <t>CARCIONE PARIDE</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="H43" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="H43" s="12" t="n">
+      <c r="I43" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="I43" s="12" t="n">
+      <c r="J43" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="J43" s="12" t="n">
+      <c r="K43" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="K43" s="12" t="n">
+      <c r="L43" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L43" s="12" t="n">
+      <c r="M43" s="12" t="n">
         <v>158</v>
       </c>
-      <c r="M43" s="12" t="n">
+      <c r="N43" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2594,42 +2775,47 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIALE DELL'INDUSTRIA 44</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="G44" s="12" t="n">
+      <c r="H44" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="H44" s="12" t="n">
+      <c r="I44" s="12" t="n">
         <v>133</v>
       </c>
-      <c r="I44" s="12" t="n">
+      <c r="J44" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="J44" s="12" t="n">
+      <c r="K44" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K44" s="12" t="n">
+      <c r="L44" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="L44" s="12" t="n">
+      <c r="M44" s="12" t="n">
         <v>189</v>
       </c>
-      <c r="M44" s="12" t="n">
+      <c r="N44" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2648,42 +2834,47 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA DELLA RESISTENZA</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
           <t>CORSI PAOLA</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>113</v>
       </c>
-      <c r="G45" s="12" t="n">
+      <c r="H45" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H45" s="12" t="n">
+      <c r="I45" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I45" s="12" t="n">
+      <c r="J45" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="J45" s="12" t="n">
+      <c r="K45" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K45" s="12" t="n">
+      <c r="L45" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="L45" s="12" t="n">
+      <c r="M45" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="M45" s="12" t="n">
+      <c r="N45" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2702,42 +2893,47 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA GALILEO GALILEI</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
           <t>CASCIARI PAOLO</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="F46" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="G46" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="G46" s="12" t="n">
+      <c r="H46" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="12" t="n">
+      <c r="I46" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I46" s="12" t="n">
+      <c r="J46" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="J46" s="12" t="n">
+      <c r="K46" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="K46" s="12" t="n">
+      <c r="L46" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="L46" s="12" t="n">
+      <c r="M46" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="M46" s="12" t="n">
+      <c r="N46" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2756,42 +2952,47 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA EUGENIO BERTINI</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
           <t>CELLINI LUCA</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="F47" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="G47" s="12" t="n">
         <v>131</v>
       </c>
-      <c r="G47" s="12" t="n">
+      <c r="H47" s="12" t="n">
         <v>103</v>
       </c>
-      <c r="H47" s="12" t="n">
+      <c r="I47" s="12" t="n">
         <v>393</v>
       </c>
-      <c r="I47" s="12" t="n">
+      <c r="J47" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="J47" s="12" t="n">
+      <c r="K47" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K47" s="12" t="n">
+      <c r="L47" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="L47" s="12" t="n">
+      <c r="M47" s="12" t="n">
         <v>145</v>
       </c>
-      <c r="M47" s="12" t="n">
+      <c r="N47" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N47" s="2" t="inlineStr">
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2810,42 +3011,47 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA BOLOGNA 13</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
           <t>LIBANORI FEDERICO</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="G48" s="12" t="n">
+      <c r="H48" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="H48" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="J48" s="12" t="n">
+      <c r="K48" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="K48" s="12" t="n">
+      <c r="L48" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L48" s="12" t="n">
+      <c r="M48" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="M48" s="12" t="n">
+      <c r="N48" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2864,42 +3070,47 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>SS. SUD</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
           <t>LIBANORI FEDERICO</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="G49" s="12" t="n">
+      <c r="H49" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="H49" s="12" t="n">
+      <c r="I49" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="I49" s="12" t="n">
+      <c r="J49" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="J49" s="12" t="n">
+      <c r="K49" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K49" s="12" t="n">
+      <c r="L49" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="L49" s="12" t="n">
+      <c r="M49" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="M49" s="12" t="n">
+      <c r="N49" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N49" s="2" t="inlineStr">
+      <c r="O49" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2918,42 +3129,47 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA SHAKESPEARE SNC</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="G50" s="12" t="n">
+      <c r="H50" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H50" s="12" t="n">
+      <c r="I50" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I50" s="12" t="n">
+      <c r="J50" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="J50" s="12" t="n">
+      <c r="K50" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="K50" s="12" t="n">
+      <c r="L50" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="L50" s="12" t="n">
+      <c r="M50" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="M50" s="12" t="n">
+      <c r="N50" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2972,42 +3188,47 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA AURELIA NORD 162</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
           <t>ANTONINI GABRIELE</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="G51" s="12" t="n">
+      <c r="H51" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H51" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="J51" s="12" t="n">
+      <c r="K51" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K51" s="12" t="n">
+      <c r="L51" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="L51" s="12" t="n">
+      <c r="M51" s="12" t="n">
         <v>119</v>
       </c>
-      <c r="M51" s="12" t="n">
+      <c r="N51" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="N51" s="2" t="inlineStr">
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -3026,42 +3247,47 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>S.G.C. FIPILI KM 52,800 - LOC. CURIGLIANO</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
           <t>DE LUCA ANTONIO</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="F52" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="G52" s="12" t="n">
+      <c r="H52" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H52" s="12" t="n">
+      <c r="I52" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I52" s="12" t="n">
+      <c r="J52" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="J52" s="12" t="n">
+      <c r="K52" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K52" s="12" t="n">
+      <c r="L52" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="L52" s="12" t="n">
+      <c r="M52" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="M52" s="12" t="n">
+      <c r="N52" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="N52" s="2" t="inlineStr">
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3080,42 +3306,47 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA STALINGRADO 59/4</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="F53" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="G53" s="12" t="n">
+      <c r="H53" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="H53" s="12" t="n">
+      <c r="I53" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="I53" s="12" t="n">
+      <c r="J53" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="J53" s="12" t="n">
+      <c r="K53" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="K53" s="12" t="n">
+      <c r="L53" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L53" s="12" t="n">
+      <c r="M53" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="M53" s="12" t="n">
+      <c r="N53" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="N53" s="2" t="inlineStr">
+      <c r="O53" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -3134,42 +3365,47 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
           <t>PETRELLI DANIELE</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="F54" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="G54" s="12" t="n">
+      <c r="H54" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H54" s="12" t="n">
+      <c r="I54" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="I54" s="12" t="n">
+      <c r="J54" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="J54" s="12" t="n">
+      <c r="K54" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K54" s="12" t="n">
+      <c r="L54" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L54" s="12" t="n">
+      <c r="M54" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="M54" s="12" t="n">
+      <c r="N54" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N54" s="2" t="inlineStr">
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3188,42 +3424,47 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA LUDOVICA</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
           <t>CASCIARI PAOLO</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="F55" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="F55" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="H55" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="J55" s="12" t="n">
+      <c r="K55" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="K55" s="12" t="n">
+      <c r="L55" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L55" s="12" t="n">
+      <c r="M55" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="M55" s="12" t="n">
+      <c r="N55" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N55" s="2" t="inlineStr">
+      <c r="O55" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -3242,42 +3483,47 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA ALDINI 186</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
           <t>PIETRANTONIO GIULIANO</t>
         </is>
-      </c>
-      <c r="E56" s="12" t="n">
-        <v>50</v>
       </c>
       <c r="F56" s="12" t="n">
         <v>50</v>
       </c>
       <c r="G56" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="H56" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="H56" s="12" t="n">
+      <c r="I56" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="I56" s="12" t="n">
+      <c r="J56" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="J56" s="12" t="n">
+      <c r="K56" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="K56" s="12" t="n">
+      <c r="L56" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L56" s="12" t="n">
+      <c r="M56" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="M56" s="12" t="n">
+      <c r="N56" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="N56" s="2" t="inlineStr">
+      <c r="O56" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3296,42 +3542,47 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA VIGNOLESE 1030</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
           <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
-      <c r="E57" s="12" t="n">
+      <c r="F57" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="F57" s="12" t="n">
+      <c r="G57" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="G57" s="12" t="n">
+      <c r="H57" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="H57" s="12" t="n">
+      <c r="I57" s="12" t="n">
         <v>122</v>
       </c>
-      <c r="I57" s="12" t="n">
+      <c r="J57" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="J57" s="12" t="n">
+      <c r="K57" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K57" s="12" t="n">
+      <c r="L57" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L57" s="12" t="n">
+      <c r="M57" s="12" t="n">
         <v>138</v>
       </c>
-      <c r="M57" s="12" t="n">
+      <c r="N57" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N57" s="2" t="inlineStr">
+      <c r="O57" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3350,42 +3601,47 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>S.S. 146 - KM. 2+180 SNC</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
-      <c r="E58" s="12" t="n">
+      <c r="F58" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="F58" s="12" t="n">
+      <c r="G58" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="G58" s="12" t="n">
+      <c r="H58" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H58" s="12" t="n">
+      <c r="I58" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="I58" s="12" t="n">
+      <c r="J58" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="J58" s="12" t="n">
+      <c r="K58" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K58" s="12" t="n">
+      <c r="L58" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L58" s="12" t="n">
+      <c r="M58" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="M58" s="12" t="n">
+      <c r="N58" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N58" s="2" t="inlineStr">
+      <c r="O58" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3404,42 +3660,47 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA G. DOZZA, 33</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E59" s="12" t="n">
+      <c r="F59" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="F59" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H59" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="J59" s="12" t="n">
+      <c r="K59" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K59" s="12" t="n">
+      <c r="L59" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L59" s="12" t="n">
+      <c r="M59" s="12" t="n">
         <v>107</v>
       </c>
-      <c r="M59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
+      <c r="N59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -3458,42 +3719,47 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA DEL ROMITO</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
           <t>CORSI PAOLA</t>
         </is>
       </c>
-      <c r="E60" s="12" t="n">
+      <c r="F60" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="F60" s="12" t="n">
+      <c r="G60" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="G60" s="12" t="n">
+      <c r="H60" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="H60" s="12" t="n">
+      <c r="I60" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I60" s="12" t="n">
+      <c r="J60" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="J60" s="12" t="n">
+      <c r="K60" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="K60" s="12" t="n">
+      <c r="L60" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L60" s="12" t="n">
+      <c r="M60" s="12" t="n">
         <v>148</v>
       </c>
-      <c r="M60" s="12" t="n">
+      <c r="N60" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="N60" s="2" t="inlineStr">
+      <c r="O60" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3512,42 +3778,47 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>TANGENZIALE OVEST KM. 5,287</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
           <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
-      <c r="E61" s="12" t="n">
+      <c r="F61" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="F61" s="12" t="n">
+      <c r="G61" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="G61" s="12" t="n">
+      <c r="H61" s="12" t="n">
         <v>78</v>
       </c>
-      <c r="H61" s="12" t="n">
+      <c r="I61" s="12" t="n">
         <v>133</v>
       </c>
-      <c r="I61" s="12" t="n">
+      <c r="J61" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="J61" s="12" t="n">
+      <c r="K61" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K61" s="12" t="n">
+      <c r="L61" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L61" s="12" t="n">
+      <c r="M61" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="M61" s="12" t="n">
+      <c r="N61" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N61" s="2" t="inlineStr">
+      <c r="O61" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3566,42 +3837,47 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA CANALETTO, 62</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
           <t>LIBANORI FEDERICO</t>
         </is>
       </c>
-      <c r="E62" s="12" t="n">
+      <c r="F62" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="F62" s="12" t="n">
+      <c r="G62" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="G62" s="12" t="n">
+      <c r="H62" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="H62" s="12" t="n">
+      <c r="I62" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I62" s="12" t="n">
+      <c r="J62" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="J62" s="12" t="n">
+      <c r="K62" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="K62" s="12" t="n">
+      <c r="L62" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L62" s="12" t="n">
+      <c r="M62" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="M62" s="12" t="n">
+      <c r="N62" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="N62" s="2" t="inlineStr">
+      <c r="O62" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3620,42 +3896,47 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>SS 71 KM.131+073</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
           <t>PETRELLI DANIELE</t>
         </is>
       </c>
-      <c r="E63" s="12" t="n">
+      <c r="F63" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="F63" s="12" t="n">
+      <c r="G63" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="G63" s="12" t="n">
+      <c r="H63" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H63" s="12" t="n">
+      <c r="I63" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="I63" s="12" t="n">
+      <c r="J63" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="J63" s="12" t="n">
+      <c r="K63" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K63" s="12" t="n">
+      <c r="L63" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L63" s="12" t="n">
+      <c r="M63" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="M63" s="12" t="n">
+      <c r="N63" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N63" s="2" t="inlineStr">
+      <c r="O63" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3674,42 +3955,47 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>COMPLANARE S. LAZZARO SNC</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E64" s="12" t="n">
+      <c r="F64" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="F64" s="12" t="n">
+      <c r="G64" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="G64" s="12" t="n">
+      <c r="H64" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H64" s="12" t="n">
+      <c r="I64" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="I64" s="12" t="n">
+      <c r="J64" s="12" t="n">
         <v>26</v>
-      </c>
-      <c r="J64" s="12" t="n">
-        <v>9</v>
       </c>
       <c r="K64" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L64" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M64" s="12" t="n">
         <v>94</v>
       </c>
-      <c r="M64" s="12" t="n">
+      <c r="N64" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N64" s="2" t="inlineStr">
+      <c r="O64" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3728,42 +4014,47 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA CRISTOFORO COLOMBO 36</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E65" s="12" t="n">
+      <c r="F65" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="F65" s="12" t="n">
+      <c r="G65" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="G65" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H65" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I65" s="12" t="n">
+      <c r="J65" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="J65" s="12" t="n">
+      <c r="K65" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K65" s="12" t="n">
+      <c r="L65" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L65" s="12" t="n">
+      <c r="M65" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="M65" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" s="2" t="inlineStr">
+      <c r="N65" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3782,42 +4073,47 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA MASSARENTI, 221/3</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E66" s="12" t="n">
+      <c r="F66" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F66" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G66" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="H66" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I66" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="J66" s="12" t="n">
+      <c r="K66" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K66" s="12" t="n">
+      <c r="L66" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L66" s="12" t="n">
+      <c r="M66" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="M66" s="12" t="n">
+      <c r="N66" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="N66" s="2" t="inlineStr">
+      <c r="O66" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3836,42 +4132,47 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>S.S. 64 LOCALITA' ALTEDO</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>LIBANORI FEDERICO</t>
         </is>
       </c>
-      <c r="E67" s="12" t="n">
+      <c r="F67" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F67" s="12" t="n">
+      <c r="G67" s="12" t="n">
         <v>99</v>
       </c>
-      <c r="G67" s="12" t="n">
+      <c r="H67" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="H67" s="12" t="n">
+      <c r="I67" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="I67" s="12" t="n">
+      <c r="J67" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="J67" s="12" t="n">
+      <c r="K67" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K67" s="12" t="n">
+      <c r="L67" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L67" s="12" t="n">
+      <c r="M67" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="M67" s="12" t="n">
+      <c r="N67" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N67" s="2" t="inlineStr">
+      <c r="O67" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3890,42 +4191,47 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA PROVINCIALE NUOVA FRANCESCA KM 8,000 SNC</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
           <t>CIULLA VALERIO</t>
         </is>
       </c>
-      <c r="E68" s="12" t="n">
+      <c r="F68" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="F68" s="12" t="n">
+      <c r="G68" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="G68" s="12" t="n">
+      <c r="H68" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H68" s="12" t="n">
+      <c r="I68" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="I68" s="12" t="n">
+      <c r="J68" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="J68" s="12" t="n">
+      <c r="K68" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K68" s="12" t="n">
+      <c r="L68" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L68" s="12" t="n">
+      <c r="M68" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="M68" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" s="2" t="inlineStr">
+      <c r="N68" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3944,42 +4250,47 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>MARECCHIESE LOC SPAD</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
           <t>CELLINI LUCA</t>
         </is>
       </c>
-      <c r="E69" s="12" t="n">
+      <c r="F69" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="F69" s="12" t="n">
+      <c r="G69" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="G69" s="12" t="n">
+      <c r="H69" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="H69" s="12" t="n">
+      <c r="I69" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="I69" s="12" t="n">
+      <c r="J69" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="J69" s="12" t="n">
+      <c r="K69" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="K69" s="12" t="n">
+      <c r="L69" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L69" s="12" t="n">
+      <c r="M69" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="M69" s="12" t="n">
+      <c r="N69" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N69" s="2" t="inlineStr">
+      <c r="O69" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3998,42 +4309,47 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>SS71 KM141+597 S.ANASTASIO LOC.OLMO</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
           <t>PETRELLI DANIELE</t>
         </is>
       </c>
-      <c r="E70" s="12" t="n">
+      <c r="F70" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="F70" s="12" t="n">
+      <c r="G70" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="G70" s="12" t="n">
+      <c r="H70" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H70" s="12" t="n">
+      <c r="I70" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I70" s="12" t="n">
+      <c r="J70" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="J70" s="12" t="n">
+      <c r="K70" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K70" s="12" t="n">
+      <c r="L70" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L70" s="12" t="n">
+      <c r="M70" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="M70" s="12" t="n">
+      <c r="N70" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="N70" s="2" t="inlineStr">
+      <c r="O70" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4052,42 +4368,47 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>SS 1 VAR.AURELIA KM.223,2</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
           <t>ANTONINI GABRIELE</t>
         </is>
       </c>
-      <c r="E71" s="12" t="n">
+      <c r="F71" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="F71" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H71" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="J71" s="12" t="n">
+      <c r="K71" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K71" s="12" t="n">
+      <c r="L71" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L71" s="12" t="n">
+      <c r="M71" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="M71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" s="2" t="inlineStr">
+      <c r="N71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -4106,42 +4427,47 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA VARIANTE AURELIA KM273</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>ANTONINI GABRIELE</t>
         </is>
       </c>
-      <c r="E72" s="12" t="n">
+      <c r="F72" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="F72" s="12" t="n">
+      <c r="G72" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="G72" s="12" t="n">
+      <c r="H72" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="H72" s="12" t="n">
+      <c r="I72" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="I72" s="12" t="n">
+      <c r="J72" s="12" t="n">
         <v>18</v>
-      </c>
-      <c r="J72" s="12" t="n">
-        <v>7</v>
       </c>
       <c r="K72" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L72" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M72" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="M72" s="12" t="n">
+      <c r="N72" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N72" s="2" t="inlineStr">
+      <c r="O72" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4160,42 +4486,47 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>S.G.C. FI/PI/LI LOC.GRECCIANO SUD 64</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>DE LUCA ANTONIO</t>
         </is>
       </c>
-      <c r="E73" s="12" t="n">
+      <c r="F73" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="F73" s="12" t="n">
+      <c r="G73" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="G73" s="12" t="n">
+      <c r="H73" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H73" s="12" t="n">
+      <c r="I73" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="I73" s="12" t="n">
+      <c r="J73" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="J73" s="12" t="n">
+      <c r="K73" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K73" s="12" t="n">
+      <c r="L73" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L73" s="12" t="n">
+      <c r="M73" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="M73" s="12" t="n">
+      <c r="N73" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N73" s="2" t="inlineStr">
+      <c r="O73" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4214,42 +4545,47 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA GORGHETTO, 2</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
           <t>LIBANORI FEDERICO</t>
         </is>
       </c>
-      <c r="E74" s="12" t="n">
+      <c r="F74" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="F74" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G74" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="H74" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I74" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="J74" s="12" t="n">
+      <c r="K74" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K74" s="12" t="n">
+      <c r="L74" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L74" s="12" t="n">
+      <c r="M74" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="M74" s="12" t="n">
+      <c r="N74" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N74" s="2" t="inlineStr">
+      <c r="O74" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -4268,42 +4604,47 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>S.S. 71, KM. 151 LOC.CECILIANO</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
           <t>PETRELLI DANIELE</t>
         </is>
       </c>
-      <c r="E75" s="12" t="n">
+      <c r="F75" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F75" s="12" t="n">
+      <c r="G75" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="G75" s="12" t="n">
+      <c r="H75" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H75" s="12" t="n">
+      <c r="I75" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="I75" s="12" t="n">
+      <c r="J75" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="J75" s="12" t="n">
+      <c r="K75" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K75" s="12" t="n">
+      <c r="L75" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L75" s="12" t="n">
+      <c r="M75" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="M75" s="12" t="n">
+      <c r="N75" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N75" s="2" t="inlineStr">
+      <c r="O75" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4322,42 +4663,47 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>TRASVERSALE DI PIANURA</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
           <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
-      <c r="E76" s="12" t="n">
+      <c r="F76" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="F76" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="H76" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="J76" s="12" t="n">
+      <c r="K76" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K76" s="12" t="n">
+      <c r="L76" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L76" s="12" t="n">
+      <c r="M76" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="M76" s="12" t="n">
+      <c r="N76" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N76" s="2" t="inlineStr">
+      <c r="O76" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -4376,42 +4722,47 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIALE BRACCI SNC</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
           <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
-      <c r="E77" s="12" t="n">
+      <c r="F77" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="F77" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H77" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="J77" s="12" t="n">
+      <c r="K77" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K77" s="12" t="n">
+      <c r="L77" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L77" s="12" t="n">
+      <c r="M77" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="M77" s="12" t="n">
+      <c r="N77" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N77" s="2" t="inlineStr">
+      <c r="O77" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -4430,42 +4781,47 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>UNITA' D'ITALIA 9</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
           <t>CASCIARI PAOLO</t>
         </is>
       </c>
-      <c r="E78" s="12" t="n">
+      <c r="F78" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F78" s="12" t="n">
+      <c r="G78" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="G78" s="12" t="n">
+      <c r="H78" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H78" s="12" t="n">
+      <c r="I78" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="I78" s="12" t="n">
+      <c r="J78" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="J78" s="12" t="n">
+      <c r="K78" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K78" s="12" t="n">
+      <c r="L78" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L78" s="12" t="n">
+      <c r="M78" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="M78" s="12" t="n">
+      <c r="N78" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="N78" s="2" t="inlineStr">
+      <c r="O78" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4484,42 +4840,47 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>FRAZ-STAGNO SS-1</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
           <t>MUFFATO LORENZO</t>
         </is>
       </c>
-      <c r="E79" s="12" t="n">
+      <c r="F79" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="F79" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="H79" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="12" t="n">
         <v>15</v>
-      </c>
-      <c r="J79" s="12" t="n">
-        <v>4</v>
       </c>
       <c r="K79" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L79" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M79" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="M79" s="12" t="n">
+      <c r="N79" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N79" s="2" t="inlineStr">
+      <c r="O79" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4538,42 +4899,47 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA RISORGIMENTO 77</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="F80" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="F80" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H80" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="K80" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K80" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="M80" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" s="2" t="inlineStr">
+      <c r="N80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -4592,42 +4958,47 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>AUTOSTRADA A1 - DIR. BOLOGNA</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
           <t>TODESCATO MARCO</t>
         </is>
       </c>
-      <c r="E81" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F81" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G81" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H81" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I81" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="J81" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K81" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="M81" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" s="2" t="inlineStr">
+      <c r="N81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -4646,42 +5017,47 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>SS MO/SASSUOLO LOC. BAGGIOVARA SNC</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
-      <c r="E82" s="12" t="n">
+      <c r="F82" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F82" s="12" t="n">
+      <c r="G82" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="G82" s="12" t="n">
+      <c r="H82" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H82" s="12" t="n">
+      <c r="I82" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I82" s="12" t="n">
+      <c r="J82" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="J82" s="12" t="n">
+      <c r="K82" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K82" s="12" t="n">
+      <c r="L82" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L82" s="12" t="n">
+      <c r="M82" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="M82" s="12" t="n">
+      <c r="N82" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N82" s="2" t="inlineStr">
+      <c r="O82" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4700,42 +5076,47 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA EMILIA PONENTE 210</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E83" s="12" t="n">
+      <c r="F83" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="F83" s="12" t="n">
+      <c r="G83" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="G83" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I83" s="12" t="n">
+      <c r="J83" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="J83" s="12" t="n">
+      <c r="K83" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K83" s="12" t="n">
+      <c r="L83" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L83" s="12" t="n">
+      <c r="M83" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="M83" s="12" t="n">
+      <c r="N83" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N83" s="2" t="inlineStr">
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4754,42 +5135,47 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA DELLA FONTANA 4/5</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
           <t>CASCIARI PAOLO</t>
         </is>
       </c>
-      <c r="E84" s="12" t="n">
+      <c r="F84" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F84" s="12" t="n">
+      <c r="G84" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="G84" s="12" t="n">
+      <c r="H84" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="H84" s="12" t="n">
-        <v>4</v>
       </c>
       <c r="I84" s="12" t="n">
         <v>4</v>
       </c>
       <c r="J84" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K84" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K84" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="M84" s="12" t="n">
+      <c r="N84" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N84" s="2" t="inlineStr">
+      <c r="O84" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4808,42 +5194,47 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA AURELIA KM 376 LOC. DEBBIA</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
           <t>CASCIARI PAOLO</t>
         </is>
       </c>
-      <c r="E85" s="12" t="n">
+      <c r="F85" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F85" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H85" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="J85" s="12" t="n">
+      <c r="K85" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K85" s="12" t="n">
+      <c r="L85" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L85" s="12" t="n">
+      <c r="M85" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="M85" s="12" t="n">
+      <c r="N85" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N85" s="2" t="inlineStr">
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -4862,20 +5253,22 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>LOC. MADONNA DELL'ACQUA - SS AURELIA KM 339 + 79</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
           <t>CIULLA VALERIO</t>
         </is>
       </c>
-      <c r="E86" s="12" t="n">
+      <c r="F86" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F86" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G86" s="12" t="n">
         <v>0</v>
       </c>
@@ -4883,21 +5276,24 @@
         <v>0</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="M86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" s="2" t="inlineStr">
+      <c r="N86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -4916,29 +5312,31 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>P.TA FIORENTINA</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
           <t>CASCIARI PAOLO</t>
         </is>
       </c>
-      <c r="E87" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="G87" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I87" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J87" s="12" t="n">
         <v>0</v>
       </c>
@@ -4951,7 +5349,10 @@
       <c r="M87" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N87" s="2" t="inlineStr">
+      <c r="N87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4970,29 +5371,31 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIALE GRAMSCI 25</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
           <t>CORSI PAOLA</t>
         </is>
       </c>
-      <c r="E88" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="12" t="n">
         <v>181</v>
       </c>
-      <c r="G88" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="I88" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J88" s="12" t="n">
         <v>0</v>
       </c>
@@ -5005,7 +5408,10 @@
       <c r="M88" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N88" s="2" t="inlineStr">
+      <c r="N88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -5024,29 +5430,31 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>TANGENZIALE NORD LUIGI PIRANDELLO 49/51</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
           <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
-      <c r="E89" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="G89" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="12" t="n">
         <v>130</v>
       </c>
-      <c r="I89" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J89" s="12" t="n">
         <v>0</v>
       </c>
@@ -5059,7 +5467,10 @@
       <c r="M89" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N89" s="2" t="inlineStr">
+      <c r="N89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -5078,29 +5489,31 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>REPUBBLICA 12</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
           <t>CARCIONE PARIDE</t>
         </is>
       </c>
-      <c r="E90" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="G90" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I90" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J90" s="12" t="n">
         <v>0</v>
       </c>
@@ -5113,7 +5526,10 @@
       <c r="M90" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N90" s="2" t="inlineStr">
+      <c r="N90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -5132,29 +5548,31 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIALE ETRURIA, 403</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
           <t>CORSI PAOLA</t>
         </is>
       </c>
-      <c r="E91" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="12" t="n">
         <v>312</v>
       </c>
-      <c r="G91" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="12" t="n">
         <v>509</v>
       </c>
-      <c r="I91" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J91" s="12" t="n">
         <v>0</v>
       </c>
@@ -5167,7 +5585,10 @@
       <c r="M91" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N91" s="2" t="inlineStr">
+      <c r="N91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -5186,29 +5607,31 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIALE D AGOSTINO 141</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E92" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="G92" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I92" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J92" s="12" t="n">
         <v>0</v>
       </c>
@@ -5221,7 +5644,10 @@
       <c r="M92" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N92" s="2" t="inlineStr">
+      <c r="N92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -5240,29 +5666,31 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>VIA PROVINCIALE SUPERIORE</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
           <t>LIBANORI FEDERICO</t>
         </is>
       </c>
-      <c r="E93" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="G93" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I93" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J93" s="12" t="n">
         <v>0</v>
       </c>
@@ -5275,7 +5703,10 @@
       <c r="M93" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N93" s="2" t="inlineStr">
+      <c r="N93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -5294,29 +5725,31 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>AURELIA LOCALITA RONDELLI</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
           <t>ANTONINI GABRIELE</t>
         </is>
       </c>
-      <c r="E94" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="G94" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I94" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J94" s="12" t="n">
         <v>0</v>
       </c>
@@ -5329,7 +5762,10 @@
       <c r="M94" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N94" s="2" t="inlineStr">
+      <c r="N94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -5348,13 +5784,15 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr"/>
-      <c r="E95" s="12" t="n">
-        <v>0</v>
-      </c>
+          <t>S.S. 9 KM 46</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="12" t="n">
         <v>0</v>
       </c>
@@ -5379,7 +5817,10 @@
       <c r="M95" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N95" s="2" t="inlineStr">
+      <c r="N95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>85</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>7886</v>
+        <v>8226</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5875</v>
+        <v>6117</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3925</v>
+        <v>4108</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>651</v>
+        <v>681</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>661</v>
+        <v>707</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>455</v>
+        <v>494</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>567</v>
+        <v>597</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>488</v>
+        <v>510</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>628</v>
+        <v>657</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>481</v>
+        <v>502</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>751</v>
+        <v>800</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>437</v>
+        <v>464</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>3</v>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I16" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>213</v>
+      </c>
+      <c r="K16" s="12" t="n">
         <v>76</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>207</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>73</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>56</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1231,17 +1231,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>05918</t>
+          <t>05291</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SANTARCANGELO DI ROMAGNA</t>
+          <t>PISA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VIA EMILIA, 1837</t>
+          <t>VIA CISANELLO 170</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,35 +1251,35 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>15</v>
+        <v>238</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>63</v>
+        <v>110</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>146</v>
+        <v>215</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>158</v>
+        <v>222</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>05291</t>
+          <t>05918</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>PISA</t>
+          <t>SANTARCANGELO DI ROMAGNA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA CISANELLO 170</t>
+          <t>VIA EMILIA, 1837</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,35 +1310,35 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>312</v>
+        <v>246</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>225</v>
+        <v>15</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>198</v>
+        <v>146</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>212</v>
+        <v>158</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>05054</t>
+          <t>06249</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ROSIGNANO MARITTIMO</t>
+          <t>SASSUOLO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA AURELIA, 340</t>
+          <t>VIA PIA</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,56 +1369,56 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>155</v>
+        <v>240</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>77</v>
+        <v>278</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>126</v>
+        <v>419</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>190</v>
+        <v>242</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06249</t>
+          <t>05054</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SASSUOLO</t>
+          <t>ROSIGNANO MARITTIMO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA PIA</t>
+          <t>VIA AURELIA, 340</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,56 +1428,56 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>228</v>
+        <v>167</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>269</v>
+        <v>79</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>392</v>
+        <v>134</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>127</v>
+        <v>177</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05349</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>PISTOIA</t>
+          <t>FAENZA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>MACALLE', 26</t>
+          <t>GRANAROLO, 177</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,56 +1487,56 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>286</v>
+        <v>147</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>135</v>
+        <v>98</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>05349</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>FAENZA</t>
+          <t>PISTOIA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>GRANAROLO, 177</t>
+          <t>MACALLE', 26</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,56 +1546,56 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>143</v>
+        <v>305</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>240</v>
+        <v>273</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>05245</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>VECCHIANO</t>
+          <t>BAGNO A RIPOLI</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA PROV.LE VECCHIANESE 38</t>
+          <t>SS 222 KM 2+340 PONTE A EMA</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,35 +1605,35 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1644,17 +1644,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>51840</t>
+          <t>05245</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>BAGNO A RIPOLI</t>
+          <t>VECCHIANO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>SS 222 KM 2+340 PONTE A EMA</t>
+          <t>VIA PROV.LE VECCHIANESE 38</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,39 +1664,39 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>133</v>
+        <v>45</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>71</v>
+        <v>184</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>23</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>200</v>
+        <v>141</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>432</v>
+        <v>455</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1762,17 +1762,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>06019</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MISANO ADRIATICO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA NUOVA BAZZANESE 8</t>
+          <t>VIA NAZIONALE ADRIATICA 148</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,56 +1782,56 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>266</v>
+        <v>179</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>103</v>
+        <v>6</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06019</t>
+          <t>25554</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>MISANO ADRIATICO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE ADRIATICA 148</t>
+          <t>VIA NUOVA BAZZANESE 8</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,56 +1841,56 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>174</v>
+        <v>274</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>05911</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMEA 1498</t>
+          <t>VIALE NENNI 19 -21</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,56 +1900,56 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>106</v>
+        <v>355</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>34723</t>
+          <t>04634</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>SAN GIOVANNI VALDARNO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIALE NENNI 19 -21</t>
+          <t>VIA UBALDINO PERUZZI</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,56 +1959,56 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>38</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>333</v>
+        <v>195</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>04634</t>
+          <t>05911</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI VALDARNO</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIA UBALDINO PERUZZI</t>
+          <t>VIA ROMEA 1498</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,39 +2018,39 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>163</v>
+        <v>114</v>
       </c>
       <c r="H31" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>93</v>
+      </c>
+      <c r="J31" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="K31" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I31" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="J31" s="12" t="n">
-        <v>93</v>
-      </c>
-      <c r="K31" s="12" t="n">
-        <v>31</v>
-      </c>
       <c r="L31" s="12" t="n">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>181</v>
+        <v>110</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2081,28 +2081,28 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>41</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>32</v>
@@ -2140,52 +2140,52 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>55380</t>
+          <t>05915</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MONTELUPO FIORENTINO</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA TOSCO ROMAGNOLO SUD 36 - LOC. FIBBIANA</t>
+          <t>VIA FLAMINIA 3</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,56 +2195,56 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05915</t>
+          <t>55380</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>MONTELUPO FIORENTINO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA FLAMINIA 3</t>
+          <t>VIA TOSCO ROMAGNOLO SUD 36 - LOC. FIBBIANA</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,56 +2254,56 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>81</v>
+        <v>155</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>25</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>06210</t>
+          <t>05239</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CARPI</t>
+          <t>SAN MINIATO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA MANZONI</t>
+          <t>VIA PANNOCCHIA 90 - LOC. PONTE A EGOLA</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,35 +2313,35 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2352,17 +2352,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>05239</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SAN MINIATO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VIA PANNOCCHIA 90 - LOC. PONTE A EGOLA</t>
+          <t>VIA FERRARESE 166</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,35 +2372,35 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
+        <v>106</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="I37" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="J37" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="K37" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="M37" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="G37" s="12" t="n">
-        <v>131</v>
-      </c>
-      <c r="H37" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="I37" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="J37" s="12" t="n">
-        <v>74</v>
-      </c>
-      <c r="K37" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <v>128</v>
-      </c>
       <c r="N37" s="12" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2411,17 +2411,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>06210</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>CARPI</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA FERRARESE 166</t>
+          <t>VIA MANZONI</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,35 +2431,35 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
+        <v>105</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="H38" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I38" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="J38" s="12" t="n">
+        <v>93</v>
+      </c>
+      <c r="K38" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="L38" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M38" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="G38" s="12" t="n">
-        <v>73</v>
-      </c>
-      <c r="H38" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="I38" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="J38" s="12" t="n">
-        <v>81</v>
-      </c>
-      <c r="K38" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="L38" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="M38" s="12" t="n">
-        <v>100</v>
-      </c>
       <c r="N38" s="12" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2494,31 +2494,31 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>34</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2553,28 +2553,28 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>62</v>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L41" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>1</v>
@@ -2647,17 +2647,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>05543</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>PIOMBINO</t>
+          <t>SASSO MARCONI</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIALE UNITA' D'ITALIA 121</t>
+          <t>VIA KENNEDY 7</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2667,35 +2667,35 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>93</v>
+        <v>169</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2706,17 +2706,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>05543</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SASSO MARCONI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIA KENNEDY 7</t>
+          <t>VIALE DELL'INDUSTRIA 44</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2726,56 +2726,56 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>64</v>
+        <v>159</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>158</v>
+        <v>194</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>53676</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>PIOMBINO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIALE DELL'INDUSTRIA 44</t>
+          <t>VIALE UNITA' D'ITALIA 121</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2785,56 +2785,56 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>133</v>
+        <v>27</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>189</v>
+        <v>96</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>14735</t>
+          <t>05941</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>BORGO SAN LORENZO</t>
+          <t>FORLÌ</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA RESISTENZA</t>
+          <t>VIA EUGENIO BERTINI</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,35 +2844,35 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>15</v>
+        <v>418</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2883,17 +2883,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04516</t>
+          <t>05514</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>CARRARA</t>
+          <t>SAN GIOVANNI IN PERSICETO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>VIA GALILEO GALILEI</t>
+          <t>VIA BOLOGNA 13</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2903,56 +2903,56 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>86</v>
+        <v>145</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>05941</t>
+          <t>14735</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>FORLÌ</t>
+          <t>BORGO SAN LORENZO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>VIA EUGENIO BERTINI</t>
+          <t>VIA DELLA RESISTENZA</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2962,35 +2962,35 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>393</v>
+        <v>15</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -3001,17 +3001,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>05514</t>
+          <t>04516</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI IN PERSICETO</t>
+          <t>CARRARA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>VIA BOLOGNA 13</t>
+          <t>VIA GALILEO GALILEI</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3021,35 +3021,35 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3084,16 +3084,16 @@
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="J49" s="12" t="n">
         <v>35</v>
@@ -3102,13 +3102,13 @@
         <v>9</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J50" s="12" t="n">
         <v>45</v>
@@ -3161,13 +3161,13 @@
         <v>13</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3202,35 +3202,35 @@
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H52" s="12" t="n">
         <v>3</v>
@@ -3279,13 +3279,13 @@
         <v>5</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3320,19 +3320,19 @@
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="H53" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K53" s="12" t="n">
         <v>14</v>
@@ -3341,31 +3341,31 @@
         <v>11</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="N53" s="12" t="n">
         <v>20</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>05536</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
+          <t>VIA ALDINI 186</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3375,56 +3375,56 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>55491</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>BORGO A MOZZANO</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>VIA LUDOVICA</t>
+          <t>VIA VIGNOLESE 1030</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3434,56 +3434,56 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>30</v>
+        <v>151</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>05536</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>VIA ALDINI 186</t>
+          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3493,56 +3493,56 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="K56" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L56" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L56" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="M56" s="12" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>55491</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>BORGO A MOZZANO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>VIA VIGNOLESE 1030</t>
+          <t>VIA LUDOVICA</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3552,56 +3552,56 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="G57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="I57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="G57" s="12" t="n">
-        <v>82</v>
-      </c>
-      <c r="H57" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="I57" s="12" t="n">
-        <v>122</v>
-      </c>
-      <c r="J57" s="12" t="n">
-        <v>37</v>
-      </c>
       <c r="K57" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>138</v>
+        <v>32</v>
       </c>
       <c r="N57" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05408</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>CHIUSI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>S.S. 146 - KM. 2+180 SNC</t>
+          <t>VIA G. DOZZA, 33</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3611,56 +3611,56 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
         <v>48</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>05408</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>CHIUSI</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>VIA G. DOZZA, 33</t>
+          <t>S.S. 146 - KM. 2+180 SNC</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3670,39 +3670,39 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K59" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3736,7 +3736,7 @@
         <v>43</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H60" s="12" t="n">
         <v>10</v>
@@ -3754,7 +3754,7 @@
         <v>9</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="N60" s="12" t="n">
         <v>9</v>
@@ -3792,19 +3792,19 @@
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K61" s="12" t="n">
         <v>1</v>
@@ -3813,7 +3813,7 @@
         <v>21</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N61" s="12" t="n">
         <v>4</v>
@@ -3851,19 +3851,19 @@
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G62" s="12" t="n">
         <v>71</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K62" s="12" t="n">
         <v>13</v>
@@ -3872,7 +3872,7 @@
         <v>6</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N62" s="12" t="n">
         <v>13</v>
@@ -3910,19 +3910,19 @@
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I63" s="12" t="n">
         <v>34</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K63" s="12" t="n">
         <v>8</v>
@@ -3931,10 +3931,10 @@
         <v>11</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3945,17 +3945,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>05530</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SAN LAZZARO DI SAVENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COMPLANARE S. LAZZARO SNC</t>
+          <t>VIA MASSARENTI, 221/3</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3969,52 +3969,52 @@
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="N64" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MALALBERGO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>VIA CRISTOFORO COLOMBO 36</t>
+          <t>S.S. 64 LOCALITA' ALTEDO</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4024,35 +4024,35 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -4063,17 +4063,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>05530</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SAN LAZZARO DI SAVENA</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>VIA MASSARENTI, 221/3</t>
+          <t>COMPLANARE S. LAZZARO SNC</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4087,52 +4087,52 @@
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>MALALBERGO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>S.S. 64 LOCALITA' ALTEDO</t>
+          <t>VIA CRISTOFORO COLOMBO 36</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4142,35 +4142,35 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="N67" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4208,13 +4208,13 @@
         <v>34</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H68" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J68" s="12" t="n">
         <v>24</v>
@@ -4226,7 +4226,7 @@
         <v>9</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N68" s="12" t="n">
         <v>0</v>
@@ -4264,31 +4264,31 @@
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L69" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="N69" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4323,22 +4323,22 @@
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H70" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L70" s="12" t="n">
         <v>10</v>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G71" s="12" t="n">
         <v>0</v>
@@ -4394,7 +4394,7 @@
         <v>0</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K71" s="12" t="n">
         <v>4</v>
@@ -4410,24 +4410,24 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>54101</t>
+          <t>04677</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>CECINA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>VIA VARIANTE AURELIA KM273</t>
+          <t>S.S. 71, KM. 151 LOC.CECILIANO</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4437,35 +4437,35 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="N72" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4500,19 +4500,19 @@
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I73" s="12" t="n">
         <v>29</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K73" s="12" t="n">
         <v>3</v>
@@ -4521,10 +4521,10 @@
         <v>12</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4535,17 +4535,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06363</t>
+          <t>54101</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>BOMPORTO</t>
+          <t>CECINA</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>VIA GORGHETTO, 2</t>
+          <t>VIA VARIANTE AURELIA KM273</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4555,56 +4555,56 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="N74" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>04677</t>
+          <t>06363</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>BOMPORTO</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>S.S. 71, KM. 151 LOC.CECILIANO</t>
+          <t>VIA GORGHETTO, 2</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4614,39 +4614,39 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="H75" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I75" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="K75" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L75" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M75" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="N75" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I75" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J75" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="K75" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L75" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="M75" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="N75" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4698,10 +4698,10 @@
         <v>6</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="N76" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4712,17 +4712,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>54044</t>
+          <t>54066</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>PIETRASANTA</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>VIALE BRACCI SNC</t>
+          <t>UNITA' D'ITALIA 9</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4732,56 +4732,56 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H77" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I77" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="J77" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="K77" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K77" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="L77" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="N77" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>54066</t>
+          <t>54044</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>PIETRASANTA</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>UNITA' D'ITALIA 9</t>
+          <t>VIALE BRACCI SNC</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4791,39 +4791,39 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="N78" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4854,22 +4854,22 @@
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L79" s="12" t="n">
         <v>4</v>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
         <v>0</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N80" s="12" t="n">
         <v>0</v>
@@ -4975,7 +4975,7 @@
         <v>14</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H81" s="12" t="n">
         <v>1</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="N81" s="12" t="n">
         <v>0</v>
@@ -5034,7 +5034,7 @@
         <v>14</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H82" s="12" t="n">
         <v>1</v>
@@ -5052,10 +5052,10 @@
         <v>6</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="N82" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>11</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H83" s="12" t="n">
         <v>0</v>
@@ -5152,13 +5152,13 @@
         <v>8</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H84" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J84" s="12" t="n">
         <v>4</v>
@@ -5329,13 +5329,13 @@
         <v>0</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J87" s="12" t="n">
         <v>0</v>
@@ -5388,13 +5388,13 @@
         <v>0</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="H88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="J88" s="12" t="n">
         <v>0</v>
@@ -5447,13 +5447,13 @@
         <v>0</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="J89" s="12" t="n">
         <v>0</v>
@@ -5565,13 +5565,13 @@
         <v>0</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>312</v>
+        <v>351</v>
       </c>
       <c r="H91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>509</v>
+        <v>547</v>
       </c>
       <c r="J91" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>85</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>8226</v>
+        <v>8646</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6117</v>
+        <v>6410</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>4108</v>
+        <v>4317</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>681</v>
+        <v>720</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>707</v>
+        <v>765</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>494</v>
+        <v>545</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>516</v>
+        <v>546</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>597</v>
+        <v>632</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>510</v>
+        <v>559</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>657</v>
+        <v>686</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>800</v>
+        <v>845</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>464</v>
+        <v>481</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>373</v>
+        <v>398</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>482</v>
+        <v>504</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>5</v>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>45</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>105</v>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I16" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>227</v>
+      </c>
+      <c r="K16" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="J16" s="12" t="n">
-        <v>213</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>76</v>
-      </c>
       <c r="L16" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>61</v>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1317,13 +1317,13 @@
         <v>229</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>146</v>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>419</v>
+        <v>450</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>05349</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>FAENZA</t>
+          <t>PISTOIA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>GRANAROLO, 177</t>
+          <t>MACALLE', 26</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,56 +1487,56 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>147</v>
+        <v>316</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>98</v>
+        <v>151</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>253</v>
+        <v>301</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05349</t>
+          <t>05245</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>PISTOIA</t>
+          <t>VECCHIANO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>MACALLE', 26</t>
+          <t>VIA PROV.LE VECCHIANESE 38</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,56 +1546,56 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>305</v>
+        <v>45</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>49</v>
+        <v>194</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>273</v>
+        <v>146</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>51840</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>BAGNO A RIPOLI</t>
+          <t>FAENZA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>SS 222 KM 2+340 PONTE A EMA</t>
+          <t>GRANAROLO, 177</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,35 +1605,35 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>211</v>
+        <v>269</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1644,17 +1644,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>05245</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>VECCHIANO</t>
+          <t>BAGNO A RIPOLI</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA PROV.LE VECCHIANESE 38</t>
+          <t>SS 222 KM 2+340 PONTE A EMA</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,35 +1664,35 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>45</v>
+        <v>148</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>184</v>
+        <v>78</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>141</v>
+        <v>221</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>27</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>455</v>
+        <v>484</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,35 +1786,35 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>54</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1845,35 +1845,35 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>56</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1904,35 +1904,35 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>42</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2022,31 +2022,31 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2081,31 +2081,31 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>18</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>40</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2140,31 +2140,31 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2175,17 +2175,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05915</t>
+          <t>55380</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>MONTELUPO FIORENTINO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA FLAMINIA 3</t>
+          <t>VIA TOSCO ROMAGNOLO SUD 36 - LOC. FIBBIANA</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,56 +2195,56 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="G34" s="12" t="n">
+        <v>159</v>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J34" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="H34" s="12" t="n">
-        <v>74</v>
-      </c>
-      <c r="I34" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="J34" s="12" t="n">
-        <v>82</v>
-      </c>
       <c r="K34" s="12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>55380</t>
+          <t>05915</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>MONTELUPO FIORENTINO</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA TOSCO ROMAGNOLO SUD 36 - LOC. FIBBIANA</t>
+          <t>VIA FLAMINIA 3</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,39 +2254,39 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>155</v>
+        <v>85</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2317,28 +2317,28 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>20</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>6</v>
@@ -2352,17 +2352,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>04892</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VIA FERRARESE 166</t>
+          <t>VIA SESTESE, 97/99</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,39 +2372,39 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2435,16 +2435,16 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>16</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>93</v>
@@ -2453,13 +2453,13 @@
         <v>43</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2470,17 +2470,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>04892</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA SESTESE, 97/99</t>
+          <t>VIA FERRARESE 166</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2490,39 +2490,39 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>189</v>
+        <v>86</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>84</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2553,28 +2553,28 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L40" s="12" t="n">
         <v>18</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>62</v>
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>59</v>
@@ -2624,16 +2624,16 @@
         <v>0</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L41" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>1</v>
@@ -2647,17 +2647,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>05543</t>
+          <t>05514</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SASSO MARCONI</t>
+          <t>SAN GIOVANNI IN PERSICETO</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIA KENNEDY 7</t>
+          <t>VIA BOLOGNA 13</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2667,56 +2667,56 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="L42" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>05543</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SASSO MARCONI</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIALE DELL'INDUSTRIA 44</t>
+          <t>VIA KENNEDY 7</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2726,39 +2726,39 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>159</v>
+        <v>84</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="K43" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="L43" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L43" s="12" t="n">
-        <v>42</v>
-      </c>
       <c r="M43" s="12" t="n">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2789,28 +2789,28 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I44" s="12" t="n">
         <v>27</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L44" s="12" t="n">
         <v>22</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>11</v>
@@ -2824,17 +2824,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05941</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>FORLÌ</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>VIA EUGENIO BERTINI</t>
+          <t>VIALE DELL'INDUSTRIA 44</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,32 +2844,32 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>418</v>
+        <v>176</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>162</v>
+        <v>205</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>2</v>
@@ -2883,17 +2883,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>05514</t>
+          <t>05941</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI IN PERSICETO</t>
+          <t>FORLÌ</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>VIA BOLOGNA 13</t>
+          <t>VIA EUGENIO BERTINI</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2903,39 +2903,39 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>71</v>
+        <v>144</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>54</v>
+        <v>111</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>0</v>
+        <v>437</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2966,31 +2966,31 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -3025,10 +3025,10 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>1</v>
@@ -3037,16 +3037,16 @@
         <v>2</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>14</v>
@@ -3060,17 +3060,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>58000</t>
+          <t>55420</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>MIRANDOLA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>SS. SUD</t>
+          <t>VIA SHAKESPEARE SNC</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3080,56 +3080,56 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="H49" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="N49" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>55420</t>
+          <t>58000</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MIRANDOLA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>VIA SHAKESPEARE SNC</t>
+          <t>SS. SUD</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3139,32 +3139,32 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="N50" s="12" t="n">
         <v>3</v>
@@ -3202,19 +3202,19 @@
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>10</v>
@@ -3223,10 +3223,10 @@
         <v>20</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H52" s="12" t="n">
         <v>3</v>
@@ -3273,19 +3273,19 @@
         <v>13</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K52" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3320,10 +3320,10 @@
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H53" s="12" t="n">
         <v>30</v>
@@ -3338,10 +3338,10 @@
         <v>14</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="N53" s="12" t="n">
         <v>20</v>
@@ -3355,17 +3355,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>05536</t>
+          <t>55491</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>BORGO A MOZZANO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>VIA ALDINI 186</t>
+          <t>VIA LUDOVICA</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3375,56 +3375,56 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="I54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="G54" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="H54" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="I54" s="12" t="n">
-        <v>95</v>
-      </c>
-      <c r="J54" s="12" t="n">
-        <v>47</v>
-      </c>
       <c r="K54" s="12" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L54" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="N54" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="M54" s="12" t="n">
-        <v>89</v>
-      </c>
-      <c r="N54" s="12" t="n">
-        <v>41</v>
-      </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>05536</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>VIA VIGNOLESE 1030</t>
+          <t>VIA ALDINI 186</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3438,31 +3438,31 @@
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3473,17 +3473,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>05408</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>CHIUSI</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
+          <t>S.S. 146 - KM. 2+180 SNC</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3493,35 +3493,35 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
         <v>52</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3532,17 +3532,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>55491</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>BORGO A MOZZANO</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>VIA LUDOVICA</t>
+          <t>VIA VIGNOLESE 1030</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3552,56 +3552,56 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>32</v>
+        <v>155</v>
       </c>
       <c r="N57" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>VIA G. DOZZA, 33</t>
+          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3611,56 +3611,56 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05408</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>CHIUSI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>S.S. 146 - KM. 2+180 SNC</t>
+          <t>VIA G. DOZZA, 33</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3670,56 +3670,56 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L59" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>04812</t>
+          <t>05530</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>VIA DEL ROMITO</t>
+          <t>VIA MASSARENTI, 221/3</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3729,56 +3729,56 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>154</v>
+        <v>72</v>
       </c>
       <c r="N60" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>04812</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>TANGENZIALE OVEST KM. 5,287</t>
+          <t>VIA DEL ROMITO</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3788,35 +3788,35 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G61" s="12" t="n">
         <v>90</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>138</v>
+        <v>11</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3851,19 +3851,19 @@
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I62" s="12" t="n">
         <v>4</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K62" s="12" t="n">
         <v>13</v>
@@ -3872,7 +3872,7 @@
         <v>6</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="N62" s="12" t="n">
         <v>13</v>
@@ -3910,19 +3910,19 @@
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K63" s="12" t="n">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>11</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N63" s="12" t="n">
         <v>2</v>
@@ -3945,17 +3945,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>05530</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>VIA MASSARENTI, 221/3</t>
+          <t>TANGENZIALE OVEST KM. 5,287</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3965,39 +3965,39 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>67</v>
+        <v>125</v>
       </c>
       <c r="N64" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4028,31 +4028,31 @@
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -4087,28 +4087,28 @@
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H66" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L66" s="12" t="n">
         <v>9</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N66" s="12" t="n">
         <v>2</v>
@@ -4149,7 +4149,7 @@
         <v>37</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H67" s="12" t="n">
         <v>1</v>
@@ -4167,7 +4167,7 @@
         <v>16</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="N67" s="12" t="n">
         <v>0</v>
@@ -4181,17 +4181,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>34201</t>
+          <t>04978</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SANTA CROCE SULL'ARNO</t>
+          <t>SCARLINO</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>VIA PROVINCIALE NUOVA FRANCESCA KM 8,000 SNC</t>
+          <t>SS 1 VAR.AURELIA KM.223,2</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4201,56 +4201,56 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="N68" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05982</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>SANTA CROCE SULL'ARNO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>MARECCHIESE LOC SPAD</t>
+          <t>VIA PROVINCIALE NUOVA FRANCESCA KM 8,000 SNC</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4260,35 +4260,35 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G69" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="H69" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I69" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="J69" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="K69" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L69" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M69" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="H69" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="I69" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="J69" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="K69" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="L69" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="M69" s="12" t="n">
-        <v>36</v>
-      </c>
       <c r="N69" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4323,28 +4323,28 @@
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I70" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J70" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="K70" s="12" t="n">
         <v>11</v>
-      </c>
-      <c r="J70" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="K70" s="12" t="n">
-        <v>10</v>
       </c>
       <c r="L70" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N70" s="12" t="n">
         <v>10</v>
@@ -4358,17 +4358,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04978</t>
+          <t>05982</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SCARLINO</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>SS 1 VAR.AURELIA KM.223,2</t>
+          <t>MARECCHIESE LOC SPAD</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4378,39 +4378,39 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="G71" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="H71" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="I71" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="J71" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="12" t="n">
-        <v>26</v>
-      </c>
       <c r="K71" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L71" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L71" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="M71" s="12" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N71" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H72" s="12" t="n">
         <v>2</v>
@@ -4453,19 +4453,19 @@
         <v>10</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K72" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="N72" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4500,31 +4500,31 @@
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I73" s="12" t="n">
         <v>29</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L73" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4535,17 +4535,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>54101</t>
+          <t>06363</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>CECINA</t>
+          <t>BOMPORTO</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>VIA VARIANTE AURELIA KM273</t>
+          <t>VIA GORGHETTO, 2</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4555,56 +4555,56 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="N74" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06363</t>
+          <t>54479</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>BOMPORTO</t>
+          <t>BENTIVOGLIO</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>VIA GORGHETTO, 2</t>
+          <t>TRASVERSALE DI PIANURA</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4614,56 +4614,56 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K75" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L75" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L75" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="M75" s="12" t="n">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="N75" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>54479</t>
+          <t>54101</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>BENTIVOGLIO</t>
+          <t>CECINA</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>TRASVERSALE DI PIANURA</t>
+          <t>VIA VARIANTE AURELIA KM273</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -4673,39 +4673,39 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N76" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4736,31 +4736,31 @@
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L77" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="N77" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4816,14 +4816,14 @@
         <v>2</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N78" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4875,14 +4875,14 @@
         <v>4</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N79" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4913,19 +4913,19 @@
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K80" s="12" t="n">
         <v>6</v>
@@ -4934,7 +4934,7 @@
         <v>0</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N80" s="12" t="n">
         <v>0</v>
@@ -4975,7 +4975,7 @@
         <v>14</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H81" s="12" t="n">
         <v>1</v>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
         <v>14</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H82" s="12" t="n">
         <v>1</v>
@@ -5052,7 +5052,7 @@
         <v>6</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="N82" s="12" t="n">
         <v>3</v>
@@ -5152,7 +5152,7 @@
         <v>8</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H84" s="12" t="n">
         <v>1</v>
@@ -5229,7 +5229,7 @@
         <v>2</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N85" s="12" t="n">
         <v>1</v>
@@ -5329,13 +5329,13 @@
         <v>0</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J87" s="12" t="n">
         <v>0</v>
@@ -5388,13 +5388,13 @@
         <v>0</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="H88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="J88" s="12" t="n">
         <v>0</v>
@@ -5447,13 +5447,13 @@
         <v>0</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="J89" s="12" t="n">
         <v>0</v>
@@ -5565,13 +5565,13 @@
         <v>0</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>351</v>
+        <v>394</v>
       </c>
       <c r="H91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>547</v>
+        <v>588</v>
       </c>
       <c r="J91" s="12" t="n">
         <v>0</v>
@@ -5624,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H92" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>85</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>8646</v>
+        <v>9071</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6410</v>
+        <v>6730</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>4317</v>
+        <v>4571</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>720</v>
+        <v>752</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>765</v>
+        <v>845</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>545</v>
+        <v>591</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>546</v>
+        <v>567</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>632</v>
+        <v>664</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>559</v>
+        <v>589</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>686</v>
+        <v>725</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>526</v>
+        <v>549</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>845</v>
+        <v>901</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>481</v>
+        <v>528</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>398</v>
+        <v>449</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>504</v>
+        <v>524</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>428</v>
+        <v>467</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>300</v>
+        <v>328</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>229</v>
+        <v>259</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>263</v>
+        <v>312</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>387</v>
+        <v>404</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>90</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>75</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>05918</t>
+          <t>06249</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SANTARCANGELO DI ROMAGNA</t>
+          <t>SASSUOLO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA EMILIA, 1837</t>
+          <t>VIA PIA</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,35 +1310,35 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>258</v>
+        <v>287</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>15</v>
+        <v>315</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>68</v>
+        <v>480</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>158</v>
+        <v>277</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06249</t>
+          <t>05918</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SASSUOLO</t>
+          <t>SANTARCANGELO DI ROMAGNA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA PIA</t>
+          <t>VIA EMILIA, 1837</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,35 +1369,35 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>294</v>
+        <v>15</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>450</v>
+        <v>73</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>80</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>256</v>
+        <v>158</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,28 +1432,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>56</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>8</v>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05349</t>
+          <t>05245</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>PISTOIA</t>
+          <t>VECCHIANO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>MACALLE', 26</t>
+          <t>VIA PROV.LE VECCHIANESE 38</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,56 +1487,56 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>316</v>
+        <v>47</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>52</v>
+        <v>207</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>301</v>
+        <v>156</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05245</t>
+          <t>05349</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>VECCHIANO</t>
+          <t>PISTOIA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA PROV.LE VECCHIANESE 38</t>
+          <t>MACALLE', 26</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,39 +1546,39 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>45</v>
+        <v>334</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>194</v>
+        <v>53</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>146</v>
+        <v>331</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1609,28 +1609,28 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>7</v>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>25</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>33</v>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>484</v>
+        <v>519</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>6</v>
@@ -1845,31 +1845,31 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>56</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>34723</t>
+          <t>04634</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>SAN GIOVANNI VALDARNO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIALE NENNI 19 -21</t>
+          <t>VIA UBALDINO PERUZZI</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,56 +1900,56 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>366</v>
+        <v>211</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>04634</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI VALDARNO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIA UBALDINO PERUZZI</t>
+          <t>VIALE NENNI 19 -21</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,39 +1959,39 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>201</v>
+        <v>394</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2022,16 +2022,16 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>45</v>
@@ -2040,13 +2040,13 @@
         <v>15</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2081,52 +2081,52 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>55380</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>MONTELUPO FIORENTINO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA SELICE KM. 2</t>
+          <t>VIA TOSCO ROMAGNOLO SUD 36 - LOC. FIBBIANA</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,56 +2136,56 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>72</v>
+        <v>164</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>257</v>
+        <v>6</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>250</v>
+        <v>7</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>289</v>
+        <v>170</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>55380</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MONTELUPO FIORENTINO</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA TOSCO ROMAGNOLO SUD 36 - LOC. FIBBIANA</t>
+          <t>VIA SELICE KM. 2</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,39 +2195,39 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>5</v>
+        <v>259</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>7</v>
+        <v>261</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>153</v>
+        <v>298</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2258,35 +2258,35 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>37</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>22</v>
@@ -2329,40 +2329,40 @@
         <v>20</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>35</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04892</t>
+          <t>06210</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>CARPI</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VIA SESTESE, 97/99</t>
+          <t>VIA MANZONI</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,56 +2372,56 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>209</v>
+        <v>102</v>
       </c>
       <c r="H37" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="I37" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="J37" s="12" t="n">
+        <v>98</v>
+      </c>
+      <c r="K37" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="L37" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I37" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="J37" s="12" t="n">
-        <v>89</v>
-      </c>
-      <c r="K37" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>24</v>
-      </c>
       <c r="M37" s="12" t="n">
-        <v>169</v>
+        <v>116</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>06210</t>
+          <t>04892</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>CARPI</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA MANZONI</t>
+          <t>VIA SESTESE, 97/99</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,39 +2431,39 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>93</v>
+        <v>236</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>109</v>
+        <v>186</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2494,31 +2494,31 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G39" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="J39" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="H39" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="I39" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <v>84</v>
-      </c>
       <c r="K39" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L39" s="12" t="n">
         <v>22</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2553,28 +2553,28 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>62</v>
@@ -2612,35 +2612,35 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L41" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G42" s="12" t="n">
         <v>71</v>
@@ -2683,40 +2683,40 @@
         <v>0</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L42" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>05543</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SASSO MARCONI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIA KENNEDY 7</t>
+          <t>VIALE DELL'INDUSTRIA 44</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2726,56 +2726,56 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>90</v>
+        <v>169</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>84</v>
+        <v>189</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>05941</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>PIOMBINO</t>
+          <t>FORLÌ</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIALE UNITA' D'ITALIA 121</t>
+          <t>VIA EUGENIO BERTINI</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2785,56 +2785,56 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>91</v>
+        <v>154</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>27</v>
+        <v>468</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>05543</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SASSO MARCONI</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>VIALE DELL'INDUSTRIA 44</t>
+          <t>VIA KENNEDY 7</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,56 +2844,56 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>152</v>
+        <v>103</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>176</v>
+        <v>97</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="K45" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="L45" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L45" s="12" t="n">
-        <v>42</v>
-      </c>
       <c r="M45" s="12" t="n">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>05941</t>
+          <t>53676</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>FORLÌ</t>
+          <t>PIOMBINO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>VIA EUGENIO BERTINI</t>
+          <t>VIALE UNITA' D'ITALIA 121</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2903,39 +2903,39 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>111</v>
+        <v>22</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>437</v>
+        <v>30</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2966,31 +2966,31 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="H47" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I47" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="I47" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="J47" s="12" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -3028,13 +3028,13 @@
         <v>80</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J48" s="12" t="n">
         <v>54</v>
@@ -3046,14 +3046,14 @@
         <v>29</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>14</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3087,13 +3087,13 @@
         <v>77</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H49" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J49" s="12" t="n">
         <v>47</v>
@@ -3105,14 +3105,14 @@
         <v>30</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="N49" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K50" s="12" t="n">
         <v>9</v>
@@ -3164,7 +3164,7 @@
         <v>38</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N50" s="12" t="n">
         <v>3</v>
@@ -3202,35 +3202,35 @@
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="N51" s="12" t="n">
         <v>12</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3261,19 +3261,19 @@
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H52" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K52" s="12" t="n">
         <v>5</v>
@@ -3282,10 +3282,10 @@
         <v>30</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3296,17 +3296,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>55491</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>BORGO A MOZZANO</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>VIA STALINGRADO 59/4</t>
+          <t>VIA LUDOVICA</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3316,56 +3316,56 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>128</v>
+        <v>37</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>55491</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>BORGO A MOZZANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>VIA LUDOVICA</t>
+          <t>VIA G. DOZZA, 33</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3375,35 +3375,35 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="I54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3438,28 +3438,28 @@
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L55" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="N55" s="12" t="n">
         <v>41</v>
@@ -3473,17 +3473,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>05408</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>CHIUSI</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>S.S. 146 - KM. 2+180 SNC</t>
+          <t>VIA VIGNOLESE 1030</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3493,32 +3493,32 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>51</v>
+        <v>149</v>
       </c>
       <c r="J56" s="12" t="n">
         <v>39</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>96</v>
+        <v>169</v>
       </c>
       <c r="N56" s="12" t="n">
         <v>2</v>
@@ -3532,17 +3532,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>VIA VIGNOLESE 1030</t>
+          <t>VIA STALINGRADO 59/4</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3552,35 +3552,35 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H57" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="I57" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="J57" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="K57" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L57" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="M57" s="12" t="n">
+        <v>130</v>
+      </c>
+      <c r="N57" s="12" t="n">
         <v>20</v>
-      </c>
-      <c r="I57" s="12" t="n">
-        <v>134</v>
-      </c>
-      <c r="J57" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="K57" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L57" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="M57" s="12" t="n">
-        <v>155</v>
-      </c>
-      <c r="N57" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3591,17 +3591,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>05408</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>CHIUSI</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
+          <t>S.S. 146 - KM. 2+180 SNC</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3611,35 +3611,35 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3650,17 +3650,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>VIA G. DOZZA, 33</t>
+          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3670,56 +3670,56 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>05530</t>
+          <t>04812</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>VIA MASSARENTI, 221/3</t>
+          <t>VIA DEL ROMITO</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3729,56 +3729,56 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>72</v>
+        <v>168</v>
       </c>
       <c r="N60" s="12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04812</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>VIA DEL ROMITO</t>
+          <t>TANGENZIALE OVEST KM. 5,287</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3788,35 +3788,35 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>11</v>
+        <v>154</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3827,17 +3827,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>06259</t>
+          <t>05530</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>VIA CANALETTO, 62</t>
+          <t>VIA MASSARENTI, 221/3</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3847,39 +3847,39 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3910,28 +3910,28 @@
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H63" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I63" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="J63" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="K63" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L63" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="I63" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="J63" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="K63" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L63" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="M63" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N63" s="12" t="n">
         <v>2</v>
@@ -3945,17 +3945,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>06259</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>TANGENZIALE OVEST KM. 5,287</t>
+          <t>VIA CANALETTO, 62</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3965,35 +3965,35 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="N64" s="12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -4004,17 +4004,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>05982</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>MALALBERGO</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>S.S. 64 LOCALITA' ALTEDO</t>
+          <t>MARECCHIESE LOC SPAD</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4024,35 +4024,35 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>115</v>
+        <v>54</v>
       </c>
       <c r="H65" s="12" t="n">
         <v>33</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K65" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="L65" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M65" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="N65" s="12" t="n">
         <v>6</v>
-      </c>
-      <c r="L65" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="M65" s="12" t="n">
-        <v>104</v>
-      </c>
-      <c r="N65" s="12" t="n">
-        <v>7</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -4063,17 +4063,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SAN LAZZARO DI SAVENA</t>
+          <t>MALALBERGO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COMPLANARE S. LAZZARO SNC</t>
+          <t>S.S. 64 LOCALITA' ALTEDO</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4083,35 +4083,35 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -4122,17 +4122,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>04978</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SCARLINO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>VIA CRISTOFORO COLOMBO 36</t>
+          <t>SS 1 VAR.AURELIA KM.223,2</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4142,56 +4142,56 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="G67" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I67" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="K67" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L67" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M67" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="G67" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="H67" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I67" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="J67" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="K67" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L67" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="M67" s="12" t="n">
-        <v>69</v>
-      </c>
       <c r="N67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>04978</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SCARLINO</t>
+          <t>SAN LAZZARO DI SAVENA</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>SS 1 VAR.AURELIA KM.223,2</t>
+          <t>COMPLANARE S. LAZZARO SNC</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4201,56 +4201,56 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L68" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="M68" s="12" t="n">
+        <v>116</v>
+      </c>
+      <c r="N68" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="M68" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="N68" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>34201</t>
+          <t>04601</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SANTA CROCE SULL'ARNO</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>VIA PROVINCIALE NUOVA FRANCESCA KM 8,000 SNC</t>
+          <t>SS71 KM141+597 S.ANASTASIO LOC.OLMO</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4260,56 +4260,56 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="N69" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04601</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>SS71 KM141+597 S.ANASTASIO LOC.OLMO</t>
+          <t>VIA CRISTOFORO COLOMBO 36</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4319,56 +4319,56 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="N70" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>05982</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>SANTA CROCE SULL'ARNO</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>MARECCHIESE LOC SPAD</t>
+          <t>VIA PROVINCIALE NUOVA FRANCESCA KM 8,000 SNC</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4378,35 +4378,35 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="N71" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H72" s="12" t="n">
         <v>2</v>
@@ -4453,7 +4453,7 @@
         <v>10</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K72" s="12" t="n">
         <v>9</v>
@@ -4462,7 +4462,7 @@
         <v>6</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N72" s="12" t="n">
         <v>4</v>
@@ -4476,17 +4476,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>05099</t>
+          <t>54066</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>PIETRASANTA</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>S.G.C. FI/PI/LI LOC.GRECCIANO SUD 64</t>
+          <t>UNITA' D'ITALIA 9</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4496,35 +4496,35 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4559,22 +4559,22 @@
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G74" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L74" s="12" t="n">
         <v>4</v>
@@ -4594,17 +4594,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>54479</t>
+          <t>05099</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>BENTIVOGLIO</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>TRASVERSALE DI PIANURA</t>
+          <t>S.G.C. FI/PI/LI LOC.GRECCIANO SUD 64</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4614,56 +4614,56 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="H75" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I75" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J75" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="K75" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L75" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="M75" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="N75" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I75" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="K75" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L75" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M75" s="12" t="n">
-        <v>69</v>
-      </c>
-      <c r="N75" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>54101</t>
+          <t>54479</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>CECINA</t>
+          <t>BENTIVOGLIO</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>VIA VARIANTE AURELIA KM273</t>
+          <t>TRASVERSALE DI PIANURA</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -4673,56 +4673,56 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K76" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N76" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>54066</t>
+          <t>54101</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>PIETRASANTA</t>
+          <t>CECINA</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>UNITA' D'ITALIA 9</t>
+          <t>VIA VARIANTE AURELIA KM273</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4732,35 +4732,35 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="J77" s="12" t="n">
         <v>18</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="N77" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4771,17 +4771,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>54044</t>
+          <t>05055</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>VIALE BRACCI SNC</t>
+          <t>FRAZ-STAGNO SS-1</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4791,35 +4791,35 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="G78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="K78" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="N78" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4830,17 +4830,17 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>05055</t>
+          <t>54044</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>FRAZ-STAGNO SS-1</t>
+          <t>VIALE BRACCI SNC</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F79" s="12" t="n">
@@ -4860,46 +4860,46 @@
         <v>0</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="I79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="N79" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>05589</t>
+          <t>54593</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>ZOLA PREDOSA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>VIA RISORGIMENTO 77</t>
+          <t>SS MO/SASSUOLO LOC. BAGGIOVARA SNC</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4909,56 +4909,56 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="N80" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>25518</t>
+          <t>05589</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>CASALECCHIO DI RENO</t>
+          <t>ZOLA PREDOSA</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>AUTOSTRADA A1 - DIR. BOLOGNA</t>
+          <t>VIA RISORGIMENTO 77</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4968,32 +4968,32 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>TODESCATO MARCO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="N81" s="12" t="n">
         <v>0</v>
@@ -5007,17 +5007,17 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>54593</t>
+          <t>25518</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>CASALECCHIO DI RENO</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>SS MO/SASSUOLO LOC. BAGGIOVARA SNC</t>
+          <t>AUTOSTRADA A1 - DIR. BOLOGNA</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -5027,39 +5027,39 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>TODESCATO MARCO</t>
         </is>
       </c>
       <c r="F82" s="12" t="n">
         <v>14</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="H82" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="N82" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5093,7 @@
         <v>11</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H83" s="12" t="n">
         <v>0</v>
@@ -5125,17 +5125,17 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>05160</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>BORGO A MOZZANO</t>
+          <t>MONTIGNOSO</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA FONTANA 4/5</t>
+          <t>VIA AURELIA KM 376 LOC. DEBBIA</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -5149,25 +5149,25 @@
         </is>
       </c>
       <c r="F84" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K84" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M84" s="12" t="n">
         <v>9</v>
@@ -5177,24 +5177,24 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11295</t>
+          <t>05160</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>MONTIGNOSO</t>
+          <t>BORGO A MOZZANO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>VIA AURELIA KM 376 LOC. DEBBIA</t>
+          <t>VIA DELLA FONTANA 4/5</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5208,35 +5208,35 @@
         </is>
       </c>
       <c r="F85" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H85" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J85" s="12" t="n">
         <v>4</v>
-      </c>
-      <c r="I85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="12" t="n">
-        <v>5</v>
       </c>
       <c r="K85" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N85" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5329,7 @@
         <v>0</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H87" s="12" t="n">
         <v>0</v>
@@ -5388,13 +5388,13 @@
         <v>0</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>231</v>
+        <v>260</v>
       </c>
       <c r="H88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="J88" s="12" t="n">
         <v>0</v>
@@ -5447,13 +5447,13 @@
         <v>0</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="J89" s="12" t="n">
         <v>0</v>
@@ -5565,13 +5565,13 @@
         <v>0</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>394</v>
+        <v>456</v>
       </c>
       <c r="H91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>588</v>
+        <v>650</v>
       </c>
       <c r="J91" s="12" t="n">
         <v>0</v>
@@ -5624,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H92" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>85</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>9071</v>
+        <v>9385</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6730</v>
+        <v>6993</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>4571</v>
+        <v>4724</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>752</v>
+        <v>775</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>845</v>
+        <v>886</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>591</v>
+        <v>622</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>174</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>664</v>
+        <v>705</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>589</v>
+        <v>619</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>725</v>
+        <v>745</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>901</v>
+        <v>947</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>420</v>
+        <v>447</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>528</v>
+        <v>555</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>5</v>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>467</v>
+        <v>494</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>6</v>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>49</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>62</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>62</v>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>157</v>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1376,13 +1376,13 @@
         <v>229</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>146</v>
@@ -1435,13 +1435,13 @@
         <v>226</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>86</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="J21" s="12" t="n">
         <v>187</v>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05245</t>
+          <t>05349</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>VECCHIANO</t>
+          <t>PISTOIA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA PROV.LE VECCHIANESE 38</t>
+          <t>MACALLE', 26</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,56 +1487,56 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>47</v>
+        <v>348</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>207</v>
+        <v>55</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>156</v>
+        <v>353</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05349</t>
+          <t>05245</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>PISTOIA</t>
+          <t>VECCHIANO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>MACALLE', 26</t>
+          <t>VIA PROV.LE VECCHIANESE 38</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,39 +1546,39 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>334</v>
+        <v>51</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>53</v>
+        <v>208</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>331</v>
+        <v>162</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>95</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1668,35 +1668,35 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>25</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I26" s="12" t="n">
         <v>48</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>59</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>519</v>
+        <v>545</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>60</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>59</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>6</v>
@@ -1845,31 +1845,31 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>40</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>56</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1904,28 +1904,28 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>2</v>
@@ -1963,35 +1963,35 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>42</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>9</v>
@@ -2081,28 +2081,28 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>44</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>34</v>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>6</v>
@@ -2152,16 +2152,16 @@
         <v>7</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>27</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>2</v>
@@ -2175,17 +2175,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>05915</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA SELICE KM. 2</t>
+          <t>VIA FLAMINIA 3</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,56 +2195,56 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>259</v>
+        <v>81</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>261</v>
+        <v>19</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>93</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>298</v>
+        <v>169</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05915</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA FLAMINIA 3</t>
+          <t>VIA SELICE KM. 2</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,35 +2254,35 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>79</v>
+        <v>260</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>19</v>
+        <v>274</v>
       </c>
       <c r="J35" s="12" t="n">
         <v>93</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>162</v>
+        <v>307</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2317,28 +2317,28 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>20</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L36" s="12" t="n">
         <v>34</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>7</v>
@@ -2376,31 +2376,31 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G37" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="I37" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="J37" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="H37" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="I37" s="12" t="n">
-        <v>79</v>
-      </c>
-      <c r="J37" s="12" t="n">
-        <v>98</v>
-      </c>
       <c r="K37" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L37" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2435,31 +2435,31 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L38" s="12" t="n">
         <v>26</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2494,16 +2494,16 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>86</v>
@@ -2512,13 +2512,13 @@
         <v>38</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2553,31 +2553,31 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2588,17 +2588,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>55416</t>
+          <t>05514</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>MONSUMMANO TERME</t>
+          <t>SAN GIOVANNI IN PERSICETO</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>DELLA COSTITUZIONE, 138</t>
+          <t>VIA BOLOGNA 13</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2608,35 +2608,35 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>122</v>
+        <v>180</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2647,17 +2647,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>05514</t>
+          <t>05941</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI IN PERSICETO</t>
+          <t>FORLÌ</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIA BOLOGNA 13</t>
+          <t>VIA EUGENIO BERTINI</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2667,56 +2667,56 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>71</v>
+        <v>159</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>0</v>
+        <v>494</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>55416</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MONSUMMANO TERME</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIALE DELL'INDUSTRIA 44</t>
+          <t>DELLA COSTITUZIONE, 138</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2726,56 +2726,56 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
+        <v>102</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="I43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="G43" s="12" t="n">
-        <v>169</v>
-      </c>
-      <c r="H43" s="12" t="n">
-        <v>99</v>
-      </c>
-      <c r="I43" s="12" t="n">
-        <v>189</v>
-      </c>
-      <c r="J43" s="12" t="n">
-        <v>57</v>
-      </c>
       <c r="K43" s="12" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>211</v>
+        <v>123</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05941</t>
+          <t>05543</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>FORLÌ</t>
+          <t>SASSO MARCONI</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA EUGENIO BERTINI</t>
+          <t>VIA KENNEDY 7</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2785,35 +2785,35 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>117</v>
+        <v>33</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>468</v>
+        <v>108</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2824,17 +2824,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05543</t>
+          <t>53676</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SASSO MARCONI</t>
+          <t>PIOMBINO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>VIA KENNEDY 7</t>
+          <t>VIALE UNITA' D'ITALIA 121</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,35 +2844,35 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>187</v>
+        <v>112</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2883,17 +2883,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>PIOMBINO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>VIALE UNITA' D'ITALIA 121</t>
+          <t>VIALE DELL'INDUSTRIA 44</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2903,39 +2903,39 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>100</v>
+        <v>176</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>30</v>
+        <v>209</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>103</v>
+        <v>217</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2966,28 +2966,28 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L47" s="12" t="n">
         <v>22</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>8</v>
@@ -3025,28 +3025,28 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>14</v>
@@ -3060,17 +3060,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>55420</t>
+          <t>04951</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>GROSSETO</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>VIA SHAKESPEARE SNC</t>
+          <t>VIA AURELIA NORD 162</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3080,56 +3080,56 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="H49" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="K49" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L49" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="M49" s="12" t="n">
+        <v>147</v>
+      </c>
+      <c r="N49" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I49" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J49" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="K49" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L49" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="M49" s="12" t="n">
-        <v>97</v>
-      </c>
-      <c r="N49" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>58000</t>
+          <t>55420</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>MIRANDOLA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>SS. SUD</t>
+          <t>VIA SHAKESPEARE SNC</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3139,56 +3139,56 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N50" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>04951</t>
+          <t>58000</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>GROSSETO</t>
+          <t>MIRANDOLA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>VIA AURELIA NORD 162</t>
+          <t>SS. SUD</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3198,56 +3198,56 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>05290</t>
+          <t>55491</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>PONTEDERA</t>
+          <t>BORGO A MOZZANO</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>S.G.C. FIPILI KM 52,800 - LOC. CURIGLIANO</t>
+          <t>VIA LUDOVICA</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3257,56 +3257,56 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="I52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="G52" s="12" t="n">
-        <v>92</v>
-      </c>
-      <c r="H52" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I52" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="J52" s="12" t="n">
-        <v>32</v>
-      </c>
       <c r="K52" s="12" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>55491</t>
+          <t>05290</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>BORGO A MOZZANO</t>
+          <t>PONTEDERA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>VIA LUDOVICA</t>
+          <t>S.G.C. FIPILI KM 52,800 - LOC. CURIGLIANO</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3316,39 +3316,39 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3379,52 +3379,52 @@
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L54" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="N54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>05536</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>VIA ALDINI 186</t>
+          <t>VIA VIGNOLESE 1030</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3438,31 +3438,31 @@
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>97</v>
+        <v>182</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3473,17 +3473,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>05536</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>VIA VIGNOLESE 1030</t>
+          <t>VIA ALDINI 186</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3497,31 +3497,31 @@
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>169</v>
+        <v>99</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3556,16 +3556,16 @@
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H57" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J57" s="12" t="n">
         <v>43</v>
@@ -3574,10 +3574,10 @@
         <v>14</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="N57" s="12" t="n">
         <v>20</v>
@@ -3618,13 +3618,13 @@
         <v>54</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H58" s="12" t="n">
         <v>17</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J58" s="12" t="n">
         <v>41</v>
@@ -3636,7 +3636,7 @@
         <v>13</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="N58" s="12" t="n">
         <v>2</v>
@@ -3650,17 +3650,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
+          <t>TANGENZIALE OVEST KM. 5,287</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3670,35 +3670,35 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>3</v>
+        <v>97</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>23</v>
+        <v>157</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L59" s="12" t="n">
         <v>21</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3733,28 +3733,28 @@
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I60" s="12" t="n">
         <v>13</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L60" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="N60" s="12" t="n">
         <v>11</v>
@@ -3768,17 +3768,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>TANGENZIALE OVEST KM. 5,287</t>
+          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3788,35 +3788,35 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L61" s="12" t="n">
         <v>21</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3851,19 +3851,19 @@
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H62" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="I62" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="12" t="n">
         <v>45</v>
-      </c>
-      <c r="I62" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="12" t="n">
-        <v>43</v>
       </c>
       <c r="K62" s="12" t="n">
         <v>15</v>
@@ -3872,31 +3872,31 @@
         <v>7</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>04653</t>
+          <t>05982</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLION FIORENTINO</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>SS 71 KM.131+073</t>
+          <t>MARECCHIESE LOC SPAD</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3906,35 +3906,35 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M63" s="12" t="n">
         <v>47</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3945,17 +3945,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>06259</t>
+          <t>04653</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>CASTIGLION FIORENTINO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>VIA CANALETTO, 62</t>
+          <t>SS 71 KM.131+073</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3965,35 +3965,35 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="N64" s="12" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -4004,17 +4004,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>05982</t>
+          <t>04978</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>SCARLINO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>MARECCHIESE LOC SPAD</t>
+          <t>SS 1 VAR.AURELIA KM.223,2</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4024,56 +4024,56 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>06259</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>MALALBERGO</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>S.S. 64 LOCALITA' ALTEDO</t>
+          <t>VIA CANALETTO, 62</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4090,28 +4090,28 @@
         <v>43</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -4122,17 +4122,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>04978</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SCARLINO</t>
+          <t>MALALBERGO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>SS 1 VAR.AURELIA KM.223,2</t>
+          <t>S.S. 64 LOCALITA' ALTEDO</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4142,39 +4142,39 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K67" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="N67" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4205,19 +4205,19 @@
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H68" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K68" s="12" t="n">
         <v>10</v>
@@ -4226,7 +4226,7 @@
         <v>10</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="N68" s="12" t="n">
         <v>4</v>
@@ -4267,7 +4267,7 @@
         <v>38</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H69" s="12" t="n">
         <v>6</v>
@@ -4285,10 +4285,10 @@
         <v>10</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N69" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4299,17 +4299,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SANTA CROCE SULL'ARNO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>VIA CRISTOFORO COLOMBO 36</t>
+          <t>VIA PROVINCIALE NUOVA FRANCESCA KM 8,000 SNC</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4319,32 +4319,32 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="N70" s="12" t="n">
         <v>0</v>
@@ -4358,17 +4358,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>34201</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SANTA CROCE SULL'ARNO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>VIA PROVINCIALE NUOVA FRANCESCA KM 8,000 SNC</t>
+          <t>VIA CRISTOFORO COLOMBO 36</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4378,32 +4378,32 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="N71" s="12" t="n">
         <v>0</v>
@@ -4417,17 +4417,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>04677</t>
+          <t>54066</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>PIETRASANTA</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>S.S. 71, KM. 151 LOC.CECILIANO</t>
+          <t>UNITA' D'ITALIA 9</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4437,35 +4437,35 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L72" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="N72" s="12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4476,17 +4476,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>54066</t>
+          <t>04677</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>PIETRASANTA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>UNITA' D'ITALIA 9</t>
+          <t>S.S. 71, KM. 151 LOC.CECILIANO</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4496,35 +4496,35 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L73" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4535,17 +4535,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06363</t>
+          <t>05099</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>BOMPORTO</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>VIA GORGHETTO, 2</t>
+          <t>S.G.C. FI/PI/LI LOC.GRECCIANO SUD 64</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4555,56 +4555,56 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="N74" s="12" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>05099</t>
+          <t>06363</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>BOMPORTO</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>S.G.C. FI/PI/LI LOC.GRECCIANO SUD 64</t>
+          <t>VIA GORGHETTO, 2</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4614,56 +4614,56 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
         <v>30</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K75" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L75" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L75" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="M75" s="12" t="n">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="N75" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>54479</t>
+          <t>05055</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>BENTIVOGLIO</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>TRASVERSALE DI PIANURA</t>
+          <t>FRAZ-STAGNO SS-1</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -4673,56 +4673,56 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="I76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="N76" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>54101</t>
+          <t>54479</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>CECINA</t>
+          <t>BENTIVOGLIO</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>VIA VARIANTE AURELIA KM273</t>
+          <t>TRASVERSALE DI PIANURA</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4732,56 +4732,56 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K77" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N77" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>05055</t>
+          <t>54101</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>CECINA</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>FRAZ-STAGNO SS-1</t>
+          <t>VIA VARIANTE AURELIA KM273</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4791,39 +4791,39 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K78" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="N78" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4875,7 +4875,7 @@
         <v>2</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N79" s="12" t="n">
         <v>1</v>
@@ -4916,7 +4916,7 @@
         <v>17</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H80" s="12" t="n">
         <v>1</v>
@@ -4934,7 +4934,7 @@
         <v>7</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="N80" s="12" t="n">
         <v>4</v>
@@ -4993,14 +4993,14 @@
         <v>0</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="N81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5093,7 @@
         <v>11</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H83" s="12" t="n">
         <v>0</v>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5211,13 +5211,13 @@
         <v>8</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H85" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J85" s="12" t="n">
         <v>4</v>
@@ -5329,13 +5329,13 @@
         <v>0</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J87" s="12" t="n">
         <v>0</v>
@@ -5388,7 +5388,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H88" s="12" t="n">
         <v>0</v>
@@ -5447,13 +5447,13 @@
         <v>0</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="J89" s="12" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H90" s="12" t="n">
         <v>0</v>
@@ -5565,13 +5565,13 @@
         <v>0</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="H91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>650</v>
+        <v>682</v>
       </c>
       <c r="J91" s="12" t="n">
         <v>0</v>
@@ -5624,13 +5624,13 @@
         <v>0</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H92" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J92" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>85</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>9385</v>
+        <v>9901</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6993</v>
+        <v>7392</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>4724</v>
+        <v>5019</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>775</v>
+        <v>815</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>886</v>
+        <v>941</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="I11" s="12" t="n">
+        <v>663</v>
+      </c>
+      <c r="J11" s="12" t="n">
         <v>622</v>
       </c>
-      <c r="J11" s="12" t="n">
-        <v>590</v>
-      </c>
       <c r="K11" s="12" t="n">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>705</v>
+        <v>739</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>128</v>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>619</v>
+        <v>655</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>745</v>
+        <v>774</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>567</v>
+        <v>592</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>947</v>
+        <v>985</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>447</v>
+        <v>482</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>555</v>
+        <v>582</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>5</v>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>461</v>
+        <v>485</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>462</v>
+        <v>496</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="I13" s="12" t="n">
+        <v>219</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>399</v>
+      </c>
+      <c r="K13" s="12" t="n">
         <v>201</v>
       </c>
-      <c r="J13" s="12" t="n">
-        <v>381</v>
-      </c>
-      <c r="K13" s="12" t="n">
-        <v>194</v>
-      </c>
       <c r="L13" s="12" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>494</v>
+        <v>522</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>6</v>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>339</v>
+        <v>364</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>62</v>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>157</v>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>277</v>
+        <v>306</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>328</v>
+        <v>347</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>05918</t>
+          <t>05054</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SANTARCANGELO DI ROMAGNA</t>
+          <t>ROSIGNANO MARITTIMO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA EMILIA, 1837</t>
+          <t>VIA AURELIA, 340</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,56 +1369,56 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>283</v>
+        <v>203</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>75</v>
+        <v>172</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>146</v>
+        <v>194</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>60</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>158</v>
+        <v>231</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>05054</t>
+          <t>05918</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ROSIGNANO MARITTIMO</t>
+          <t>SANTARCANGELO DI ROMAGNA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA AURELIA, 340</t>
+          <t>VIA EMILIA, 1837</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,39 +1428,39 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>191</v>
+        <v>297</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="I21" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>146</v>
+      </c>
+      <c r="K21" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="L21" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="M21" s="12" t="n">
         <v>158</v>
       </c>
-      <c r="J21" s="12" t="n">
-        <v>187</v>
-      </c>
-      <c r="K21" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="L21" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="M21" s="12" t="n">
-        <v>225</v>
-      </c>
       <c r="N21" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>64</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>40</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>26</v>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05245</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>VECCHIANO</t>
+          <t>FAENZA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA PROV.LE VECCHIANESE 38</t>
+          <t>GRANAROLO, 177</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,35 +1546,35 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>51</v>
+        <v>202</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>208</v>
+        <v>15</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>183</v>
+        <v>117</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>162</v>
+        <v>318</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>FAENZA</t>
+          <t>BAGNO A RIPOLI</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>GRANAROLO, 177</t>
+          <t>SS 222 KM 2+340 PONTE A EMA</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,56 +1605,56 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>297</v>
+        <v>264</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>51840</t>
+          <t>05245</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>BAGNO A RIPOLI</t>
+          <t>VECCHIANO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>SS 222 KM 2+340 PONTE A EMA</t>
+          <t>VIA PROV.LE VECCHIANESE 38</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,35 +1664,35 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>169</v>
+        <v>57</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>87</v>
+        <v>211</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>25</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>255</v>
+        <v>165</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>545</v>
+        <v>574</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,35 +1786,35 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1845,31 +1845,31 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>04634</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI VALDARNO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA UBALDINO PERUZZI</t>
+          <t>VIALE NENNI 19 -21</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,56 +1900,56 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>214</v>
+        <v>433</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>34723</t>
+          <t>04634</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>SAN GIOVANNI VALDARNO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIALE NENNI 19 -21</t>
+          <t>VIA UBALDINO PERUZZI</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,39 +1959,39 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1</v>
+        <v>207</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>413</v>
+        <v>226</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>9</v>
@@ -2057,17 +2057,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>53970</t>
+          <t>05915</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VIA CALCINARO 2460</t>
+          <t>VIA FLAMINIA 3</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,56 +2077,56 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>55380</t>
+          <t>53970</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>MONTELUPO FIORENTINO</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA TOSCO ROMAGNOLO SUD 36 - LOC. FIBBIANA</t>
+          <t>VIA CALCINARO 2460</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,35 +2136,35 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2175,17 +2175,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05915</t>
+          <t>55380</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>MONTELUPO FIORENTINO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA FLAMINIA 3</t>
+          <t>VIA TOSCO ROMAGNOLO SUD 36 - LOC. FIBBIANA</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,56 +2195,56 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>95</v>
+        <v>182</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>05239</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>SAN MINIATO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA SELICE KM. 2</t>
+          <t>VIA PANNOCCHIA 90 - LOC. PONTE A EGOLA</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,56 +2254,56 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>84</v>
+        <v>171</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>260</v>
+        <v>30</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>274</v>
+        <v>21</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>307</v>
+        <v>174</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>05239</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SAN MINIATO</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA PANNOCCHIA 90 - LOC. PONTE A EGOLA</t>
+          <t>VIA SELICE KM. 2</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,39 +2313,39 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>166</v>
+        <v>93</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>23</v>
+        <v>266</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>20</v>
+        <v>290</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>167</v>
+        <v>317</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2376,31 +2376,31 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2435,31 +2435,31 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="L38" s="12" t="n">
         <v>26</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2494,31 +2494,31 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L39" s="12" t="n">
         <v>23</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2529,17 +2529,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>34802</t>
+          <t>05514</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>PRATO</t>
+          <t>SAN GIOVANNI IN PERSICETO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>XVI APRILE</t>
+          <t>VIA BOLOGNA 13</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2549,56 +2549,56 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>133</v>
+        <v>71</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>05514</t>
+          <t>05941</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI IN PERSICETO</t>
+          <t>FORLÌ</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>VIA BOLOGNA 13</t>
+          <t>VIA EUGENIO BERTINI</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2608,56 +2608,56 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>71</v>
+        <v>170</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>67</v>
+        <v>125</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>05941</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>FORLÌ</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIA EUGENIO BERTINI</t>
+          <t>VIALE DELL'INDUSTRIA 44</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2667,35 +2667,35 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>494</v>
+        <v>214</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>177</v>
+        <v>232</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2706,17 +2706,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>55416</t>
+          <t>34802</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>MONSUMMANO TERME</t>
+          <t>PRATO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>DELLA COSTITUZIONE, 138</t>
+          <t>XVI APRILE</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2730,52 +2730,52 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>2</v>
+        <v>135</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>123</v>
+        <v>208</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05543</t>
+          <t>53676</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SASSO MARCONI</t>
+          <t>PIOMBINO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA KENNEDY 7</t>
+          <t>VIALE UNITA' D'ITALIA 121</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2785,56 +2785,56 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>193</v>
+        <v>119</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>55416</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>PIOMBINO</t>
+          <t>MONSUMMANO TERME</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>VIALE UNITA' D'ITALIA 121</t>
+          <t>DELLA COSTITUZIONE, 138</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,35 +2844,35 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2883,17 +2883,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>05543</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SASSO MARCONI</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>VIALE DELL'INDUSTRIA 44</t>
+          <t>VIA KENNEDY 7</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2903,35 +2903,35 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>176</v>
+        <v>114</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>209</v>
+        <v>118</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2966,28 +2966,28 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H47" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="I47" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="J47" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="K47" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L47" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="I47" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="J47" s="12" t="n">
-        <v>73</v>
-      </c>
-      <c r="K47" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L47" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="M47" s="12" t="n">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>8</v>
@@ -3025,31 +3025,31 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>18</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3060,17 +3060,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>04951</t>
+          <t>58000</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>GROSSETO</t>
+          <t>MIRANDOLA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>VIA AURELIA NORD 162</t>
+          <t>SS. SUD</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3080,39 +3080,39 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J50" s="12" t="n">
         <v>48</v>
@@ -3161,34 +3161,34 @@
         <v>13</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>58000</t>
+          <t>04951</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>MIRANDOLA</t>
+          <t>GROSSETO</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>SS. SUD</t>
+          <t>VIA AURELIA NORD 162</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3198,56 +3198,56 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>55491</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>BORGO A MOZZANO</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>VIA LUDOVICA</t>
+          <t>VIA VIGNOLESE 1030</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3257,56 +3257,56 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="K52" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L52" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L52" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="M52" s="12" t="n">
-        <v>38</v>
+        <v>206</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>05290</t>
+          <t>55491</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>PONTEDERA</t>
+          <t>BORGO A MOZZANO</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>S.G.C. FIPILI KM 52,800 - LOC. CURIGLIANO</t>
+          <t>VIA LUDOVICA</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3316,56 +3316,56 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>105</v>
+        <v>39</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>05290</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>PONTEDERA</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>VIA G. DOZZA, 33</t>
+          <t>S.G.C. FIPILI KM 52,800 - LOC. CURIGLIANO</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3375,56 +3375,56 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>VIA VIGNOLESE 1030</t>
+          <t>VIA G. DOZZA, 33</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3434,39 +3434,39 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="K55" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L55" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L55" s="12" t="n">
-        <v>18</v>
-      </c>
       <c r="M55" s="12" t="n">
-        <v>182</v>
+        <v>141</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3497,28 +3497,28 @@
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L56" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="N56" s="12" t="n">
         <v>41</v>
@@ -3556,31 +3556,31 @@
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K57" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="L57" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L57" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="M57" s="12" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="N57" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3591,17 +3591,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05408</t>
+          <t>04812</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>CHIUSI</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>S.S. 146 - KM. 2+180 SNC</t>
+          <t>VIA DEL ROMITO</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3611,35 +3611,35 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L58" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="M58" s="12" t="n">
+        <v>185</v>
+      </c>
+      <c r="N58" s="12" t="n">
         <v>13</v>
-      </c>
-      <c r="M58" s="12" t="n">
-        <v>104</v>
-      </c>
-      <c r="N58" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3650,17 +3650,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>05408</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>CHIUSI</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>TANGENZIALE OVEST KM. 5,287</t>
+          <t>S.S. 146 - KM. 2+180 SNC</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3670,35 +3670,35 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>157</v>
+        <v>57</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3709,17 +3709,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>04812</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>VIA DEL ROMITO</t>
+          <t>TANGENZIALE OVEST KM. 5,287</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3729,35 +3729,35 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>13</v>
+        <v>165</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>175</v>
+        <v>141</v>
       </c>
       <c r="N60" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3768,17 +3768,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>05530</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
+          <t>VIA MASSARENTI, 221/3</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3788,56 +3788,56 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>05530</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>VIA MASSARENTI, 221/3</t>
+          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3847,56 +3847,56 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>05982</t>
+          <t>04978</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>SCARLINO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>MARECCHIESE LOC SPAD</t>
+          <t>SS 1 VAR.AURELIA KM.223,2</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3906,56 +3906,56 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>04653</t>
+          <t>05982</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLION FIORENTINO</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>SS 71 KM.131+073</t>
+          <t>MARECCHIESE LOC SPAD</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3965,35 +3965,35 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H64" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="I64" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="J64" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="K64" s="12" t="n">
         <v>18</v>
-      </c>
-      <c r="I64" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="J64" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="K64" s="12" t="n">
-        <v>9</v>
       </c>
       <c r="L64" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N64" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -4004,17 +4004,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>04978</t>
+          <t>04653</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SCARLINO</t>
+          <t>CASTIGLION FIORENTINO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>SS 1 VAR.AURELIA KM.223,2</t>
+          <t>SS 71 KM.131+073</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4024,56 +4024,56 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06259</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>MALALBERGO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>VIA CANALETTO, 62</t>
+          <t>S.S. 64 LOCALITA' ALTEDO</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4087,31 +4087,31 @@
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I66" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="J66" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="K66" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L66" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="M66" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="N66" s="12" t="n">
         <v>7</v>
-      </c>
-      <c r="J66" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="K66" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L66" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="M66" s="12" t="n">
-        <v>115</v>
-      </c>
-      <c r="N66" s="12" t="n">
-        <v>14</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -4122,17 +4122,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>06259</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>MALALBERGO</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>S.S. 64 LOCALITA' ALTEDO</t>
+          <t>VIA CANALETTO, 62</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4149,28 +4149,28 @@
         <v>43</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N67" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4205,16 +4205,16 @@
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H68" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J68" s="12" t="n">
         <v>29</v>
@@ -4223,10 +4223,10 @@
         <v>10</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="N68" s="12" t="n">
         <v>4</v>
@@ -4264,31 +4264,31 @@
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L69" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N69" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4323,28 +4323,28 @@
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L70" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N70" s="12" t="n">
         <v>0</v>
@@ -4385,7 +4385,7 @@
         <v>37</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H71" s="12" t="n">
         <v>1</v>
@@ -4403,7 +4403,7 @@
         <v>16</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N71" s="12" t="n">
         <v>0</v>
@@ -4417,17 +4417,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>54066</t>
+          <t>04677</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>PIETRASANTA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>UNITA' D'ITALIA 9</t>
+          <t>S.S. 71, KM. 151 LOC.CECILIANO</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4437,35 +4437,35 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L72" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N72" s="12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4476,17 +4476,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>04677</t>
+          <t>54066</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>PIETRASANTA</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>S.S. 71, KM. 151 LOC.CECILIANO</t>
+          <t>UNITA' D'ITALIA 9</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4496,35 +4496,35 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>46</v>
+        <v>109</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L73" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>05099</t>
+          <t>05055</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>S.G.C. FI/PI/LI LOC.GRECCIANO SUD 64</t>
+          <t>FRAZ-STAGNO SS-1</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4555,56 +4555,56 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H74" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="I74" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="K74" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I74" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="J74" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K74" s="12" t="n">
+      <c r="L74" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M74" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="N74" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L74" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="M74" s="12" t="n">
-        <v>61</v>
-      </c>
-      <c r="N74" s="12" t="n">
-        <v>16</v>
-      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06363</t>
+          <t>05099</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>BOMPORTO</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>VIA GORGHETTO, 2</t>
+          <t>S.G.C. FI/PI/LI LOC.GRECCIANO SUD 64</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4614,56 +4614,56 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="N75" s="12" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05055</t>
+          <t>06363</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>BOMPORTO</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>FRAZ-STAGNO SS-1</t>
+          <t>VIA GORGHETTO, 2</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -4673,35 +4673,35 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
         <v>30</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H76" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="I76" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="12" t="n">
-        <v>25</v>
-      </c>
       <c r="K76" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="N76" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4757,14 +4757,14 @@
         <v>9</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="N77" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4798,13 +4798,13 @@
         <v>27</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H78" s="12" t="n">
         <v>11</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J78" s="12" t="n">
         <v>18</v>
@@ -4875,7 +4875,7 @@
         <v>2</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N79" s="12" t="n">
         <v>1</v>
@@ -4913,13 +4913,13 @@
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I80" s="12" t="n">
         <v>6</v>
@@ -4931,13 +4931,13 @@
         <v>2</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="N80" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4972,19 +4972,19 @@
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K81" s="12" t="n">
         <v>6</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N81" s="12" t="n">
         <v>0</v>
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="F82" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H82" s="12" t="n">
         <v>1</v>
@@ -5043,7 +5043,7 @@
         <v>2</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K82" s="12" t="n">
         <v>3</v>
@@ -5093,7 +5093,7 @@
         <v>11</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H83" s="12" t="n">
         <v>0</v>
@@ -5155,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I84" s="12" t="n">
         <v>0</v>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -5211,13 +5211,13 @@
         <v>8</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H85" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J85" s="12" t="n">
         <v>4</v>
@@ -5270,13 +5270,13 @@
         <v>5</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J86" s="12" t="n">
         <v>1</v>
@@ -5329,13 +5329,13 @@
         <v>0</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J87" s="12" t="n">
         <v>0</v>
@@ -5388,7 +5388,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H88" s="12" t="n">
         <v>0</v>
@@ -5447,13 +5447,13 @@
         <v>0</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="H89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="J89" s="12" t="n">
         <v>0</v>
@@ -5565,13 +5565,13 @@
         <v>0</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="H91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>682</v>
+        <v>716</v>
       </c>
       <c r="J91" s="12" t="n">
         <v>0</v>
@@ -5624,13 +5624,13 @@
         <v>0</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H92" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J92" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>85</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>9901</v>
+        <v>10426</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>7392</v>
+        <v>7804</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>5019</v>
+        <v>5379</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>815</v>
+        <v>859</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>941</v>
+        <v>983</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>663</v>
+        <v>695</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>622</v>
+        <v>652</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>739</v>
+        <v>780</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>128</v>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>655</v>
+        <v>696</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>774</v>
+        <v>807</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>592</v>
+        <v>638</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>985</v>
+        <v>1032</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>482</v>
+        <v>509</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>582</v>
+        <v>626</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>5</v>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>485</v>
+        <v>516</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>496</v>
+        <v>513</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>550</v>
+        <v>581</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -995,17 +995,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>05112</t>
+          <t>06334</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>LUCCA</t>
+          <t>VIGNOLA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>FRAZ-S-VITO STR-PROV</t>
+          <t>VIA PER SPILAMBERTO 1015</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1015,56 +1015,56 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>522</v>
+        <v>329</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>67</v>
+        <v>310</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>201</v>
+        <v>371</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>300</v>
+        <v>335</v>
       </c>
       <c r="K14" s="12" t="n">
+        <v>188</v>
+      </c>
+      <c r="L14" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="M14" s="12" t="n">
+        <v>326</v>
+      </c>
+      <c r="N14" s="12" t="n">
         <v>127</v>
       </c>
-      <c r="L14" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="M14" s="12" t="n">
-        <v>316</v>
-      </c>
-      <c r="N14" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06334</t>
+          <t>05112</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>VIGNOLA</t>
+          <t>LUCCA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIA PER SPILAMBERTO 1015</t>
+          <t>FRAZ-S-VITO STR-PROV</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1074,39 +1074,39 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>324</v>
+        <v>547</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>291</v>
+        <v>73</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>355</v>
+        <v>213</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>117</v>
+        <v>11</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>445</v>
+        <v>466</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>94</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>101</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1258,13 +1258,13 @@
         <v>306</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>266</v>
@@ -1276,7 +1276,7 @@
         <v>44</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>45</v>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>516</v>
+        <v>536</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>19</v>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1408,17 +1408,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>05918</t>
+          <t>05245</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SANTARCANGELO DI ROMAGNA</t>
+          <t>VECCHIANO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA EMILIA, 1837</t>
+          <t>VIA PROV.LE VECCHIANESE 38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,39 +1428,39 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>297</v>
+        <v>61</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>15</v>
+        <v>244</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>146</v>
+        <v>213</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>158</v>
+        <v>191</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>64</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>378</v>
+        <v>406</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>05918</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>FAENZA</t>
+          <t>SANTARCANGELO DI ROMAGNA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>GRANAROLO, 177</t>
+          <t>VIA EMILIA, 1837</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1550,35 +1550,35 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>202</v>
+        <v>305</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>318</v>
+        <v>159</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1609,52 +1609,52 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>96</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>38</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>05245</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>VECCHIANO</t>
+          <t>FAENZA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA PROV.LE VECCHIANESE 38</t>
+          <t>GRANAROLO, 177</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,39 +1664,39 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>57</v>
+        <v>211</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>211</v>
+        <v>17</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>16</v>
+        <v>102</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>185</v>
+        <v>121</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>165</v>
+        <v>329</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I26" s="12" t="n">
         <v>51</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>574</v>
+        <v>611</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,35 +1786,35 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="I27" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>123</v>
+      </c>
+      <c r="K27" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="L27" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="J27" s="12" t="n">
-        <v>119</v>
-      </c>
-      <c r="K27" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="L27" s="12" t="n">
-        <v>61</v>
-      </c>
       <c r="M27" s="12" t="n">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1845,31 +1845,31 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>42</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>34723</t>
+          <t>04634</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>SAN GIOVANNI VALDARNO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIALE NENNI 19 -21</t>
+          <t>VIA UBALDINO PERUZZI</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,56 +1900,56 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>1</v>
+        <v>215</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>43</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>433</v>
+        <v>245</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>04634</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI VALDARNO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIA UBALDINO PERUZZI</t>
+          <t>VIALE NENNI 19 -21</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,39 +1959,39 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>207</v>
+        <v>1</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>226</v>
+        <v>460</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="G31" s="12" t="n">
+        <v>156</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="I31" s="12" t="n">
         <v>140</v>
       </c>
-      <c r="H31" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="I31" s="12" t="n">
-        <v>125</v>
-      </c>
       <c r="J31" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>9</v>
@@ -2081,52 +2081,52 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>53970</t>
+          <t>55380</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>MONTELUPO FIORENTINO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA CALCINARO 2460</t>
+          <t>VIA TOSCO ROMAGNOLO SUD 36 - LOC. FIBBIANA</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,35 +2136,35 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2175,17 +2175,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>55380</t>
+          <t>53970</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MONTELUPO FIORENTINO</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA TOSCO ROMAGNOLO SUD 36 - LOC. FIBBIANA</t>
+          <t>VIA CALCINARO 2460</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,35 +2195,35 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2258,28 +2258,28 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>21</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>7</v>
@@ -2317,35 +2317,35 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2376,31 +2376,31 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L37" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2435,31 +2435,31 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L38" s="12" t="n">
         <v>26</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2470,17 +2470,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>05514</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SAN GIOVANNI IN PERSICETO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA FERRARESE 166</t>
+          <t>VIA BOLOGNA 13</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2490,35 +2490,35 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>122</v>
+        <v>204</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2529,17 +2529,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>05514</t>
+          <t>34802</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI IN PERSICETO</t>
+          <t>PRATO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA BOLOGNA 13</t>
+          <t>XVI APRILE</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2549,39 +2549,39 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>71</v>
+        <v>142</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>2</v>
@@ -2647,17 +2647,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>14735</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>BORGO SAN LORENZO</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIALE DELL'INDUSTRIA 44</t>
+          <t>VIA DELLA RESISTENZA</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2667,35 +2667,35 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>214</v>
+        <v>37</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>232</v>
+        <v>184</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2706,17 +2706,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>34802</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>PRATO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>XVI APRILE</t>
+          <t>VIA FERRARESE 166</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2726,56 +2726,56 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>41</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>208</v>
+        <v>126</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>PIOMBINO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIALE UNITA' D'ITALIA 121</t>
+          <t>VIALE DELL'INDUSTRIA 44</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2785,56 +2785,56 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="G44" s="12" t="n">
+        <v>192</v>
+      </c>
+      <c r="H44" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="H44" s="12" t="n">
-        <v>25</v>
-      </c>
       <c r="I44" s="12" t="n">
-        <v>30</v>
+        <v>230</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>119</v>
+        <v>246</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>55416</t>
+          <t>53676</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>MONSUMMANO TERME</t>
+          <t>PIOMBINO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>DELLA COSTITUZIONE, 138</t>
+          <t>VIALE UNITA' D'ITALIA 121</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,35 +2844,35 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2883,17 +2883,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>05543</t>
+          <t>55416</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SASSO MARCONI</t>
+          <t>MONSUMMANO TERME</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>VIA KENNEDY 7</t>
+          <t>DELLA COSTITUZIONE, 138</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2903,56 +2903,56 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
+        <v>107</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="I46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="G46" s="12" t="n">
-        <v>114</v>
-      </c>
-      <c r="H46" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="I46" s="12" t="n">
-        <v>118</v>
-      </c>
-      <c r="J46" s="12" t="n">
-        <v>78</v>
-      </c>
       <c r="K46" s="12" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>207</v>
+        <v>146</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>14735</t>
+          <t>05543</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>BORGO SAN LORENZO</t>
+          <t>SASSO MARCONI</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA RESISTENZA</t>
+          <t>VIA KENNEDY 7</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2962,35 +2962,35 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
         <v>101</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>29</v>
+        <v>122</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -3028,13 +3028,13 @@
         <v>90</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J48" s="12" t="n">
         <v>60</v>
@@ -3046,7 +3046,7 @@
         <v>33</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>15</v>
@@ -3060,17 +3060,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>58000</t>
+          <t>55420</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>MIRANDOLA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>SS. SUD</t>
+          <t>VIA SHAKESPEARE SNC</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3080,56 +3080,56 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
         <v>85</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>55420</t>
+          <t>58000</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MIRANDOLA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>VIA SHAKESPEARE SNC</t>
+          <t>SS. SUD</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3139,39 +3139,39 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H51" s="12" t="n">
         <v>9</v>
@@ -3220,34 +3220,34 @@
         <v>12</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>05290</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>PONTEDERA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>VIA VIGNOLESE 1030</t>
+          <t>S.G.C. FIPILI KM 52,800 - LOC. CURIGLIANO</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3257,35 +3257,35 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>177</v>
+        <v>14</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>206</v>
+        <v>125</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3296,17 +3296,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>55491</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>BORGO A MOZZANO</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>VIA LUDOVICA</t>
+          <t>VIA VIGNOLESE 1030</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3316,56 +3316,56 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>39</v>
+        <v>210</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>05290</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>PONTEDERA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>S.G.C. FIPILI KM 52,800 - LOC. CURIGLIANO</t>
+          <t>VIA G. DOZZA, 33</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3375,46 +3375,46 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>VIA G. DOZZA, 33</t>
+          <t>VIA STALINGRADO 59/4</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3438,52 +3438,52 @@
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="H55" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="I55" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="J55" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="K55" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="I55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="K55" s="12" t="n">
-        <v>21</v>
-      </c>
       <c r="L55" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>05536</t>
+          <t>55491</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>BORGO A MOZZANO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>VIA ALDINI 186</t>
+          <t>VIA LUDOVICA</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3493,46 +3493,46 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L56" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M56" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="N56" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="M56" s="12" t="n">
-        <v>105</v>
-      </c>
-      <c r="N56" s="12" t="n">
-        <v>41</v>
-      </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>05536</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>VIA STALINGRADO 59/4</t>
+          <t>VIA ALDINI 186</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3552,35 +3552,35 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I57" s="12" t="n">
+        <v>142</v>
+      </c>
+      <c r="J57" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="K57" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="L57" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M57" s="12" t="n">
+        <v>106</v>
+      </c>
+      <c r="N57" s="12" t="n">
         <v>41</v>
-      </c>
-      <c r="J57" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="K57" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="L57" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="M57" s="12" t="n">
-        <v>151</v>
-      </c>
-      <c r="N57" s="12" t="n">
-        <v>23</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3591,17 +3591,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>04812</t>
+          <t>05408</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>CHIUSI</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>VIA DEL ROMITO</t>
+          <t>S.S. 146 - KM. 2+180 SNC</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3611,35 +3611,35 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K58" s="12" t="n">
         <v>21</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>185</v>
+        <v>120</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3650,17 +3650,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05408</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>CHIUSI</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>S.S. 146 - KM. 2+180 SNC</t>
+          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3670,35 +3670,35 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3709,17 +3709,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>04812</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>TANGENZIALE OVEST KM. 5,287</t>
+          <t>VIA DEL ROMITO</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3729,35 +3729,35 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>165</v>
+        <v>16</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>141</v>
+        <v>197</v>
       </c>
       <c r="N60" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3768,17 +3768,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>05530</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>VIA MASSARENTI, 221/3</t>
+          <t>TANGENZIALE OVEST KM. 5,287</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3788,56 +3788,56 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>2</v>
+        <v>115</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L61" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="M61" s="12" t="n">
+        <v>146</v>
+      </c>
+      <c r="N61" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="M61" s="12" t="n">
-        <v>84</v>
-      </c>
-      <c r="N61" s="12" t="n">
-        <v>25</v>
-      </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>05530</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
+          <t>VIA MASSARENTI, 221/3</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3847,56 +3847,56 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>04978</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SCARLINO</t>
+          <t>MALALBERGO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>SS 1 VAR.AURELIA KM.223,2</t>
+          <t>S.S. 64 LOCALITA' ALTEDO</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3906,56 +3906,56 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>2</v>
+        <v>143</v>
       </c>
       <c r="H63" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="I63" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="J63" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="K63" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L63" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="M63" s="12" t="n">
+        <v>124</v>
+      </c>
+      <c r="N63" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I63" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="K63" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L63" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="M63" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="N63" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>05982</t>
+          <t>04978</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>SCARLINO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>MARECCHIESE LOC SPAD</t>
+          <t>SS 1 VAR.AURELIA KM.223,2</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3965,56 +3965,56 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="N64" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>04653</t>
+          <t>05982</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLION FIORENTINO</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>SS 71 KM.131+073</t>
+          <t>MARECCHIESE LOC SPAD</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4024,26 +4024,26 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="L65" s="12" t="n">
         <v>12</v>
@@ -4052,7 +4052,7 @@
         <v>52</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -4063,17 +4063,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>04653</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>MALALBERGO</t>
+          <t>CASTIGLION FIORENTINO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>S.S. 64 LOCALITA' ALTEDO</t>
+          <t>SS 71 KM.131+073</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4083,35 +4083,35 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -4146,28 +4146,28 @@
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I67" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J67" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="K67" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L67" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="J67" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="K67" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L67" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="M67" s="12" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="N67" s="12" t="n">
         <v>14</v>
@@ -4205,28 +4205,28 @@
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="N68" s="12" t="n">
         <v>4</v>
@@ -4240,17 +4240,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>04601</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>SANTA CROCE SULL'ARNO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>SS71 KM141+597 S.ANASTASIO LOC.OLMO</t>
+          <t>VIA PROVINCIALE NUOVA FRANCESCA KM 8,000 SNC</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4260,56 +4260,56 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="J69" s="12" t="n">
         <v>31</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L69" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="N69" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>34201</t>
+          <t>04601</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SANTA CROCE SULL'ARNO</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>VIA PROVINCIALE NUOVA FRANCESCA KM 8,000 SNC</t>
+          <t>SS71 KM141+597 S.ANASTASIO LOC.OLMO</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4319,56 +4319,56 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="N70" s="12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>54066</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>PIETRASANTA</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>VIA CRISTOFORO COLOMBO 36</t>
+          <t>UNITA' D'ITALIA 9</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4378,35 +4378,35 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="G71" s="12" t="n">
+        <v>113</v>
+      </c>
+      <c r="H71" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="I71" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="G71" s="12" t="n">
-        <v>92</v>
-      </c>
-      <c r="H71" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I71" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="J71" s="12" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="N71" s="12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4441,28 +4441,28 @@
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H72" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I72" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J72" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K72" s="12" t="n">
         <v>11</v>
-      </c>
-      <c r="J72" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="K72" s="12" t="n">
-        <v>10</v>
       </c>
       <c r="L72" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="N72" s="12" t="n">
         <v>4</v>
@@ -4476,17 +4476,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>54066</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>PIETRASANTA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>UNITA' D'ITALIA 9</t>
+          <t>VIA CRISTOFORO COLOMBO 36</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4496,35 +4496,35 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4580,14 +4580,14 @@
         <v>9</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="N74" s="12" t="n">
         <v>5</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4621,13 +4621,13 @@
         <v>33</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J75" s="12" t="n">
         <v>20</v>
@@ -4639,7 +4639,7 @@
         <v>13</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N75" s="12" t="n">
         <v>17</v>
@@ -4677,28 +4677,28 @@
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G76" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L76" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N76" s="12" t="n">
         <v>2</v>
@@ -4736,28 +4736,28 @@
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="N77" s="12" t="n">
         <v>4</v>
@@ -4798,13 +4798,13 @@
         <v>27</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="H78" s="12" t="n">
         <v>11</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J78" s="12" t="n">
         <v>18</v>
@@ -4854,22 +4854,22 @@
         </is>
       </c>
       <c r="F79" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="K79" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L79" s="12" t="n">
         <v>2</v>
@@ -4913,28 +4913,28 @@
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H80" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K80" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="N80" s="12" t="n">
         <v>5</v>
@@ -4972,19 +4972,19 @@
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K81" s="12" t="n">
         <v>6</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N81" s="12" t="n">
         <v>0</v>
@@ -5034,7 +5034,7 @@
         <v>15</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H82" s="12" t="n">
         <v>1</v>
@@ -5052,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N82" s="12" t="n">
         <v>0</v>
@@ -5066,17 +5066,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05512</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN PIETRO TERME</t>
+          <t>MONTIGNOSO</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>VIA EMILIA PONENTE 210</t>
+          <t>VIA AURELIA KM 376 LOC. DEBBIA</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -5086,56 +5086,56 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="F83" s="12" t="n">
         <v>11</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="N83" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11295</t>
+          <t>05512</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>MONTIGNOSO</t>
+          <t>CASTEL SAN PIETRO TERME</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>VIA AURELIA KM 376 LOC. DEBBIA</t>
+          <t>VIA EMILIA PONENTE 210</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -5145,39 +5145,39 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F84" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="N84" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5211,13 +5211,13 @@
         <v>8</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H85" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J85" s="12" t="n">
         <v>4</v>
@@ -5270,13 +5270,13 @@
         <v>5</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J86" s="12" t="n">
         <v>1</v>
@@ -5329,7 +5329,7 @@
         <v>0</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H87" s="12" t="n">
         <v>0</v>
@@ -5388,7 +5388,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="H88" s="12" t="n">
         <v>0</v>
@@ -5447,13 +5447,13 @@
         <v>0</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="J89" s="12" t="n">
         <v>0</v>
@@ -5565,13 +5565,13 @@
         <v>0</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="H91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>716</v>
+        <v>764</v>
       </c>
       <c r="J91" s="12" t="n">
         <v>0</v>
@@ -5624,13 +5624,13 @@
         <v>0</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="H92" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J92" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>85</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>10426</v>
+        <v>10964</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>7804</v>
+        <v>8270</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>5379</v>
+        <v>5775</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>859</v>
+        <v>931</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>983</v>
+        <v>1032</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>363</v>
+        <v>416</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>695</v>
+        <v>733</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>652</v>
+        <v>717</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>259</v>
+        <v>292</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>780</v>
+        <v>841</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>696</v>
+        <v>762</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>807</v>
+        <v>845</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>638</v>
+        <v>704</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>1032</v>
+        <v>1088</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>509</v>
+        <v>568</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>211</v>
+        <v>240</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>626</v>
+        <v>680</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,52 +960,52 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>516</v>
+        <v>531</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>581</v>
+        <v>596</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06334</t>
+          <t>04845</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>VIGNOLA</t>
+          <t>FUCECCHIO</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>VIA PER SPILAMBERTO 1015</t>
+          <t>VIALE BUOZZI 122/124</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1015,39 +1015,39 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>329</v>
+        <v>417</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>310</v>
+        <v>65</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>371</v>
+        <v>119</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>188</v>
+        <v>128</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>326</v>
+        <v>223</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>127</v>
+        <v>65</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>547</v>
+        <v>567</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1113,17 +1113,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>04845</t>
+          <t>06334</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>FUCECCHIO</t>
+          <t>VIGNOLA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIALE BUOZZI 122/124</t>
+          <t>VIA PER SPILAMBERTO 1015</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1133,39 +1133,39 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>403</v>
+        <v>342</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>58</v>
+        <v>323</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>111</v>
+        <v>395</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>294</v>
+        <v>343</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>116</v>
+        <v>192</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>216</v>
+        <v>343</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>64</v>
+        <v>130</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>466</v>
+        <v>493</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>158</v>
@@ -1255,16 +1255,16 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>266</v>
@@ -1273,13 +1273,13 @@
         <v>161</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>536</v>
+        <v>569</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>87</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
+        <v>264</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>217</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>101</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>187</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>221</v>
+      </c>
+      <c r="K20" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="M20" s="12" t="n">
         <v>258</v>
       </c>
-      <c r="G20" s="12" t="n">
-        <v>212</v>
-      </c>
-      <c r="H20" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="I20" s="12" t="n">
-        <v>182</v>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>216</v>
-      </c>
-      <c r="K20" s="12" t="n">
-        <v>71</v>
-      </c>
-      <c r="L20" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="M20" s="12" t="n">
-        <v>241</v>
-      </c>
       <c r="N20" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,35 +1432,35 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>41</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>406</v>
+        <v>429</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>80</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>4</v>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>51840</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>BAGNO A RIPOLI</t>
+          <t>FAENZA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>SS 222 KM 2+340 PONTE A EMA</t>
+          <t>GRANAROLO, 177</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,35 +1605,35 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>186</v>
+        <v>220</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>192</v>
+        <v>126</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>273</v>
+        <v>349</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1644,17 +1644,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>FAENZA</t>
+          <t>BAGNO A RIPOLI</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>GRANAROLO, 177</t>
+          <t>SS 222 KM 2+340 PONTE A EMA</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,35 +1664,35 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>121</v>
+        <v>195</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>329</v>
+        <v>296</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>34710</t>
+          <t>06019</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>MISANO ADRIATICO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA ENRICO DE NICOLA 47/A - 47/B</t>
+          <t>VIA NAZIONALE ADRIATICA 148</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,56 +1723,56 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>324</v>
+        <v>191</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>32</v>
+        <v>122</v>
       </c>
       <c r="I26" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="J26" s="12" t="n">
+        <v>130</v>
+      </c>
+      <c r="K26" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="J26" s="12" t="n">
-        <v>138</v>
-      </c>
-      <c r="K26" s="12" t="n">
-        <v>50</v>
-      </c>
       <c r="L26" s="12" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>611</v>
+        <v>261</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>06019</t>
+          <t>34710</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>MISANO ADRIATICO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE ADRIATICA 148</t>
+          <t>VIA ENRICO DE NICOLA 47/A - 47/B</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,39 +1782,39 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>191</v>
+        <v>335</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>111</v>
+        <v>35</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>246</v>
+        <v>643</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1845,31 +1845,31 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>04634</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI VALDARNO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA UBALDINO PERUZZI</t>
+          <t>VIALE NENNI 19 -21</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,56 +1900,56 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>215</v>
+        <v>3</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>245</v>
+        <v>479</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>34723</t>
+          <t>04634</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>SAN GIOVANNI VALDARNO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIALE NENNI 19 -21</t>
+          <t>VIA UBALDINO PERUZZI</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,56 +1959,56 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1</v>
+        <v>222</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>460</v>
+        <v>257</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05911</t>
+          <t>55380</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>MONTELUPO FIORENTINO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMEA 1498</t>
+          <t>VIA TOSCO ROMAGNOLO SUD 36 - LOC. FIBBIANA</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,56 +2018,56 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>156</v>
+        <v>209</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>140</v>
+        <v>7</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>139</v>
+        <v>215</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>05915</t>
+          <t>05911</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VIA FLAMINIA 3</t>
+          <t>VIA ROMEA 1498</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,35 +2077,35 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>106</v>
+        <v>161</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>104</v>
+        <v>16</v>
       </c>
       <c r="I32" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="J32" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="K32" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="J32" s="12" t="n">
-        <v>114</v>
-      </c>
-      <c r="K32" s="12" t="n">
-        <v>44</v>
-      </c>
       <c r="L32" s="12" t="n">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>189</v>
+        <v>145</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>55380</t>
+          <t>05915</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>MONTELUPO FIORENTINO</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA TOSCO ROMAGNOLO SUD 36 - LOC. FIBBIANA</t>
+          <t>VIA FLAMINIA 3</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,56 +2136,56 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="J33" s="12" t="n">
+        <v>121</v>
+      </c>
+      <c r="K33" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="L33" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="M33" s="12" t="n">
+        <v>208</v>
+      </c>
+      <c r="N33" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="K33" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="L33" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="M33" s="12" t="n">
-        <v>195</v>
-      </c>
-      <c r="N33" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>53970</t>
+          <t>05239</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>SAN MINIATO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA CALCINARO 2460</t>
+          <t>VIA PANNOCCHIA 90 - LOC. PONTE A EGOLA</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,35 +2195,35 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2234,17 +2234,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05239</t>
+          <t>04892</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SAN MINIATO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA PANNOCCHIA 90 - LOC. PONTE A EGOLA</t>
+          <t>VIA SESTESE, 97/99</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,35 +2254,35 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>179</v>
+        <v>284</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>185</v>
+        <v>248</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2293,17 +2293,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>53970</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA SELICE KM. 2</t>
+          <t>VIA CALCINARO 2460</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,39 +2313,39 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>101</v>
+        <v>186</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>305</v>
+        <v>26</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>331</v>
+        <v>223</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2376,31 +2376,31 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L37" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2411,17 +2411,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>04892</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA SESTESE, 97/99</t>
+          <t>VIA SELICE KM. 2</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,39 +2431,39 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>262</v>
+        <v>103</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>22</v>
+        <v>287</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>41</v>
+        <v>317</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>231</v>
+        <v>358</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2494,35 +2494,35 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>71</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2553,31 +2553,31 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="L40" s="12" t="n">
         <v>26</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2588,17 +2588,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>05941</t>
+          <t>14735</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>FORLÌ</t>
+          <t>BORGO SAN LORENZO</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>VIA EUGENIO BERTINI</t>
+          <t>VIA DELLA RESISTENZA</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2608,35 +2608,35 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>131</v>
+        <v>39</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>545</v>
+        <v>42</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2647,17 +2647,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>14735</t>
+          <t>05941</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>BORGO SAN LORENZO</t>
+          <t>FORLÌ</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA RESISTENZA</t>
+          <t>VIA EUGENIO BERTINI</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2667,35 +2667,35 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>37</v>
+        <v>565</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>184</v>
+        <v>233</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2706,17 +2706,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>55416</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>MONSUMMANO TERME</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIA FERRARESE 166</t>
+          <t>DELLA COSTITUZIONE, 138</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2726,46 +2726,46 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>126</v>
+        <v>158</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIALE DELL'INDUSTRIA 44</t>
+          <t>VIA FERRARESE 166</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2789,52 +2789,52 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>192</v>
+        <v>99</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>230</v>
+        <v>78</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>246</v>
+        <v>127</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>PIOMBINO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>VIALE UNITA' D'ITALIA 121</t>
+          <t>VIALE DELL'INDUSTRIA 44</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,56 +2844,56 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G45" s="12" t="n">
+        <v>226</v>
+      </c>
+      <c r="H45" s="12" t="n">
         <v>103</v>
       </c>
-      <c r="H45" s="12" t="n">
-        <v>26</v>
-      </c>
       <c r="I45" s="12" t="n">
-        <v>30</v>
+        <v>257</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>127</v>
+        <v>260</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>55416</t>
+          <t>53676</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>MONSUMMANO TERME</t>
+          <t>PIOMBINO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>DELLA COSTITUZIONE, 138</t>
+          <t>VIALE UNITA' D'ITALIA 121</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2903,39 +2903,39 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>2</v>
+        <v>108</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2966,28 +2966,28 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L47" s="12" t="n">
         <v>20</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>2</v>
@@ -3025,28 +3025,28 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L48" s="12" t="n">
         <v>33</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>15</v>
@@ -3084,28 +3084,28 @@
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L49" s="12" t="n">
         <v>34</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="N49" s="12" t="n">
         <v>5</v>
@@ -3119,17 +3119,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>58000</t>
+          <t>04951</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>MIRANDOLA</t>
+          <t>GROSSETO</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>SS. SUD</t>
+          <t>VIA AURELIA NORD 162</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3139,56 +3139,56 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="G50" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="G50" s="12" t="n">
-        <v>103</v>
-      </c>
       <c r="H50" s="12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>04951</t>
+          <t>58000</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>GROSSETO</t>
+          <t>MIRANDOLA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>VIA AURELIA NORD 162</t>
+          <t>SS. SUD</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3198,56 +3198,56 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>05290</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>PONTEDERA</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>S.G.C. FIPILI KM 52,800 - LOC. CURIGLIANO</t>
+          <t>VIA VIGNOLESE 1030</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3257,35 +3257,35 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>14</v>
+        <v>226</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>125</v>
+        <v>223</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3296,17 +3296,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>05290</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>PONTEDERA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>VIA VIGNOLESE 1030</t>
+          <t>S.G.C. FIPILI KM 52,800 - LOC. CURIGLIANO</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3316,35 +3316,35 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>210</v>
+        <v>14</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>210</v>
+        <v>128</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3355,17 +3355,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>VIA G. DOZZA, 33</t>
+          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3375,56 +3375,56 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>150</v>
+        <v>107</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>55491</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>BORGO A MOZZANO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>VIA STALINGRADO 59/4</t>
+          <t>VIA LUDOVICA</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3434,56 +3434,56 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>160</v>
+        <v>45</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>55491</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>BORGO A MOZZANO</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>VIA LUDOVICA</t>
+          <t>VIA STALINGRADO 59/4</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3493,46 +3493,46 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="K56" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L56" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="M56" s="12" t="n">
+        <v>168</v>
+      </c>
+      <c r="N56" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L56" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M56" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="N56" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>05536</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>VIA ALDINI 186</t>
+          <t>VIA G. DOZZA, 33</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3552,56 +3552,56 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>142</v>
+        <v>1</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>106</v>
+        <v>157</v>
       </c>
       <c r="N57" s="12" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05408</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>CHIUSI</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>S.S. 146 - KM. 2+180 SNC</t>
+          <t>TANGENZIALE OVEST KM. 5,287</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3611,35 +3611,35 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>22</v>
+        <v>111</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>57</v>
+        <v>178</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>120</v>
+        <v>153</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3650,17 +3650,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>05408</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>CHIUSI</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>RACCORDO ANULARE AREZZO-BATTIFOLLE  S.S.679  KM 7</t>
+          <t>S.S. 146 - KM. 2+180 SNC</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3670,35 +3670,35 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3709,17 +3709,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>04812</t>
+          <t>05536</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>VIA DEL ROMITO</t>
+          <t>VIA ALDINI 186</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3729,35 +3729,35 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>16</v>
+        <v>144</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>197</v>
+        <v>106</v>
       </c>
       <c r="N60" s="12" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3768,17 +3768,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>04812</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>TANGENZIALE OVEST KM. 5,287</t>
+          <t>VIA DEL ROMITO</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3788,35 +3788,35 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>106</v>
+        <v>19</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>171</v>
+        <v>19</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>146</v>
+        <v>211</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3851,52 +3851,52 @@
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G62" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K62" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>05982</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>MALALBERGO</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>S.S. 64 LOCALITA' ALTEDO</t>
+          <t>MARECCHIESE LOC SPAD</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3906,35 +3906,35 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>143</v>
+        <v>70</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>124</v>
+        <v>56</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3945,17 +3945,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>04978</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SCARLINO</t>
+          <t>MALALBERGO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>SS 1 VAR.AURELIA KM.223,2</t>
+          <t>S.S. 64 LOCALITA' ALTEDO</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3965,56 +3965,56 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>3</v>
+        <v>148</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>42</v>
+        <v>136</v>
       </c>
       <c r="N64" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>05982</t>
+          <t>04978</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>SCARLINO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>MARECCHIESE LOC SPAD</t>
+          <t>SS 1 VAR.AURELIA KM.223,2</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4024,39 +4024,39 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4087,19 +4087,19 @@
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G66" s="12" t="n">
         <v>65</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K66" s="12" t="n">
         <v>10</v>
@@ -4108,7 +4108,7 @@
         <v>13</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N66" s="12" t="n">
         <v>2</v>
@@ -4146,19 +4146,19 @@
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I67" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K67" s="12" t="n">
         <v>16</v>
@@ -4167,7 +4167,7 @@
         <v>7</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="N67" s="12" t="n">
         <v>14</v>
@@ -4205,28 +4205,28 @@
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H68" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K68" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="N68" s="12" t="n">
         <v>4</v>
@@ -4264,19 +4264,19 @@
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="H69" s="12" t="n">
         <v>23</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K69" s="12" t="n">
         <v>11</v>
@@ -4285,10 +4285,10 @@
         <v>10</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="N69" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4299,17 +4299,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04601</t>
+          <t>06363</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>BOMPORTO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>SS71 KM141+597 S.ANASTASIO LOC.OLMO</t>
+          <t>VIA GORGHETTO, 2</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4319,56 +4319,56 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M70" s="12" t="n">
         <v>30</v>
       </c>
       <c r="N70" s="12" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>54066</t>
+          <t>05055</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>PIETRASANTA</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>UNITA' D'ITALIA 9</t>
+          <t>FRAZ-STAGNO SS-1</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4378,56 +4378,56 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="N71" s="12" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>04677</t>
+          <t>54066</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>PIETRASANTA</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>S.S. 71, KM. 151 LOC.CECILIANO</t>
+          <t>UNITA' D'ITALIA 9</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4437,35 +4437,35 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>52</v>
+        <v>118</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="J72" s="12" t="n">
         <v>32</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="N72" s="12" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4476,17 +4476,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>04601</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>VIA CRISTOFORO COLOMBO 36</t>
+          <t>SS71 KM141+597 S.ANASTASIO LOC.OLMO</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4496,56 +4496,56 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>05055</t>
+          <t>04677</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>FRAZ-STAGNO SS-1</t>
+          <t>S.S. 71, KM. 151 LOC.CECILIANO</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4555,56 +4555,56 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="N74" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>05099</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>S.G.C. FI/PI/LI LOC.GRECCIANO SUD 64</t>
+          <t>VIA CRISTOFORO COLOMBO 36</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4614,35 +4614,35 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="N75" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4653,17 +4653,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>06363</t>
+          <t>54479</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>BOMPORTO</t>
+          <t>BENTIVOGLIO</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>VIA GORGHETTO, 2</t>
+          <t>TRASVERSALE DI PIANURA</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -4673,56 +4673,56 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="N76" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>54479</t>
+          <t>05099</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>BENTIVOGLIO</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>TRASVERSALE DI PIANURA</t>
+          <t>S.G.C. FI/PI/LI LOC.GRECCIANO SUD 64</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4732,39 +4732,39 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="H77" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I77" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="G77" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H77" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="I77" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="J77" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="N77" s="12" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4798,13 +4798,13 @@
         <v>27</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H78" s="12" t="n">
         <v>11</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J78" s="12" t="n">
         <v>18</v>
@@ -4854,22 +4854,22 @@
         </is>
       </c>
       <c r="F79" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="G79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="G79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="I79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="12" t="n">
-        <v>21</v>
-      </c>
       <c r="K79" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L79" s="12" t="n">
         <v>2</v>
@@ -4916,7 +4916,7 @@
         <v>23</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="H80" s="12" t="n">
         <v>2</v>
@@ -4934,7 +4934,7 @@
         <v>12</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="N80" s="12" t="n">
         <v>5</v>
@@ -4972,19 +4972,19 @@
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K81" s="12" t="n">
         <v>6</v>
@@ -4993,14 +4993,14 @@
         <v>0</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="N81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5034,13 +5034,13 @@
         <v>15</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J82" s="12" t="n">
         <v>14</v>
@@ -5052,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="N82" s="12" t="n">
         <v>0</v>
@@ -5090,28 +5090,28 @@
         </is>
       </c>
       <c r="F83" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="G83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="G83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="I83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="K83" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N83" s="12" t="n">
         <v>1</v>
@@ -5211,7 +5211,7 @@
         <v>8</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H85" s="12" t="n">
         <v>1</v>
@@ -5270,13 +5270,13 @@
         <v>5</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J86" s="12" t="n">
         <v>1</v>
@@ -5295,7 +5295,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H88" s="12" t="n">
         <v>0</v>
@@ -5447,13 +5447,13 @@
         <v>0</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="H89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="J89" s="12" t="n">
         <v>0</v>
@@ -5565,13 +5565,13 @@
         <v>0</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="H91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>764</v>
+        <v>807</v>
       </c>
       <c r="J91" s="12" t="n">
         <v>0</v>
@@ -5624,13 +5624,13 @@
         <v>0</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="H92" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="J92" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
@@ -1133,7 +1133,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>ZOTTI VINCENZO MARIA</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>ZOTTI VINCENZO MARIA</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>ZOTTI VINCENZO MARIA</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>ZOTTI VINCENZO MARIA</t>
         </is>
       </c>
       <c r="F86" s="12" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F93" s="12" t="n">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F94" s="12" t="n">

--- a/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Tino Vincenzo.xlsx
@@ -684,13 +684,13 @@
         <v>85</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>10964</v>
+        <v>10918</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>8270</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>5775</v>
+        <v>5675</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>931</v>
+        <v>920</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1032</v>
+        <v>1017</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>733</v>
+        <v>724</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>717</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>292</v>
@@ -863,7 +863,7 @@
         <v>203</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>841</v>
+        <v>831</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>144</v>
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>845</v>
+        <v>821</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>704</v>
+        <v>688</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>1088</v>
+        <v>1056</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>568</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>240</v>
@@ -922,7 +922,7 @@
         <v>198</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>6</v>
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>531</v>
+        <v>516</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>596</v>
+        <v>579</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>246</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>432</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>219</v>
@@ -981,10 +981,10 @@
         <v>84</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -995,17 +995,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>04845</t>
+          <t>06334</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>FUCECCHIO</t>
+          <t>VIGNOLA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>VIALE BUOZZI 122/124</t>
+          <t>VIA PER SPILAMBERTO 1015</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1015,39 +1015,39 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>417</v>
+        <v>342</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>65</v>
+        <v>323</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>119</v>
+        <v>395</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>313</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>223</v>
+        <v>343</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1081,16 +1081,16 @@
         <v>391</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>136</v>
@@ -1099,7 +1099,7 @@
         <v>71</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>15</v>
@@ -1113,17 +1113,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>06334</t>
+          <t>04845</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>VIGNOLA</t>
+          <t>FUCECCHIO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIA PER SPILAMBERTO 1015</t>
+          <t>VIALE BUOZZI 122/124</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1133,39 +1133,39 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>342</v>
+        <v>412</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>323</v>
+        <v>65</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>395</v>
+        <v>115</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>343</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>192</v>
+        <v>128</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>343</v>
+        <v>221</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>130</v>
+        <v>63</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>193</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>105</v>
@@ -1217,10 +1217,10 @@
         <v>89</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,19 +1255,19 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>152</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>266</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>161</v>
@@ -1276,7 +1276,7 @@
         <v>45</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>47</v>
@@ -1314,19 +1314,19 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>108</v>
@@ -1335,7 +1335,7 @@
         <v>87</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>21</v>
@@ -1373,19 +1373,19 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>73</v>
@@ -1394,7 +1394,7 @@
         <v>44</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>10</v>
@@ -1435,16 +1435,16 @@
         <v>261</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>25</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>129</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>72</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>100</v>
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>63</v>
@@ -1571,7 +1571,7 @@
         <v>80</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>4</v>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>20</v>
@@ -1621,7 +1621,7 @@
         <v>102</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>53</v>
@@ -1630,7 +1630,7 @@
         <v>103</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>10</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>108</v>
@@ -1680,7 +1680,7 @@
         <v>101</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>87</v>
@@ -1689,7 +1689,7 @@
         <v>33</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>38</v>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>06019</t>
+          <t>34710</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MISANO ADRIATICO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE ADRIATICA 148</t>
+          <t>VIA ENRICO DE NICOLA 47/A - 47/B</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,56 +1723,56 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>191</v>
+        <v>329</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>122</v>
+        <v>31</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>261</v>
+        <v>628</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>34710</t>
+          <t>06019</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>MISANO ADRIATICO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA ENRICO DE NICOLA 47/A - 47/B</t>
+          <t>VIA NAZIONALE ADRIATICA 148</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,56 +1782,56 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>335</v>
+        <v>187</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>643</v>
+        <v>258</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA NUOVA BAZZANESE 8</t>
+          <t>VIALE NENNI 19 -21</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,56 +1841,56 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>224</v>
+        <v>2</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>368</v>
+        <v>466</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>34723</t>
+          <t>25554</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIALE NENNI 19 -21</t>
+          <t>VIA NUOVA BAZZANESE 8</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,39 +1900,39 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>3</v>
+        <v>223</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>479</v>
+        <v>361</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1963,19 +1963,19 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>31</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>46</v>
@@ -1984,7 +1984,7 @@
         <v>46</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>3</v>
@@ -1998,17 +1998,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>55380</t>
+          <t>05915</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>MONTELUPO FIORENTINO</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIA TOSCO ROMAGNOLO SUD 36 - LOC. FIBBIANA</t>
+          <t>VIA FLAMINIA 3</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,56 +2018,56 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>209</v>
+        <v>110</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>15</v>
+        <v>118</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>05911</t>
+          <t>55380</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>MONTELUPO FIORENTINO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMEA 1498</t>
+          <t>VIA TOSCO ROMAGNOLO SUD 36 - LOC. FIBBIANA</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,35 +2077,35 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>161</v>
+        <v>202</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>145</v>
+        <v>7</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>145</v>
+        <v>208</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>05915</t>
+          <t>05911</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA FLAMINIA 3</t>
+          <t>VIA ROMEA 1498</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,56 +2136,56 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>112</v>
+        <v>157</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>23</v>
+        <v>145</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>208</v>
+        <v>146</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>93</v>
+        <v>10</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05239</t>
+          <t>04892</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SAN MINIATO</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA PANNOCCHIA 90 - LOC. PONTE A EGOLA</t>
+          <t>VIA SESTESE, 97/99</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,35 +2195,35 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ZOTTI VINCENZO MARIA</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>186</v>
+        <v>278</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>195</v>
+        <v>247</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2234,17 +2234,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>04892</t>
+          <t>53970</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA SESTESE, 97/99</t>
+          <t>VIA CALCINARO 2460</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,35 +2254,35 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
         <v>147</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>284</v>
+        <v>180</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I35" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="J35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="J35" s="12" t="n">
-        <v>127</v>
-      </c>
-      <c r="K35" s="12" t="n">
-        <v>58</v>
-      </c>
       <c r="L35" s="12" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>248</v>
+        <v>221</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2293,17 +2293,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>53970</t>
+          <t>05239</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>SAN MINIATO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA CALCINARO 2460</t>
+          <t>VIA PANNOCCHIA 90 - LOC. PONTE A EGOLA</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,56 +2313,56 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>ZOTTI VINCENZO MARIA</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>06210</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CARPI</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VIA MANZONI</t>
+          <t>VIA SELICE KM. 2</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,35 +2372,35 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>30</v>
+        <v>286</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>139</v>
+        <v>358</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2411,17 +2411,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>34802</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>PRATO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA SELICE KM. 2</t>
+          <t>XVI APRILE</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,56 +2431,56 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>287</v>
+        <v>48</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>317</v>
+        <v>73</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>358</v>
+        <v>239</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>05514</t>
+          <t>06210</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI IN PERSICETO</t>
+          <t>CARPI</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA BOLOGNA 13</t>
+          <t>VIA MANZONI</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2494,52 +2494,52 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>219</v>
+        <v>136</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>34802</t>
+          <t>05514</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>PRATO</t>
+          <t>SAN GIOVANNI IN PERSICETO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>XVI APRILE</t>
+          <t>VIA BOLOGNA 13</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2549,39 +2549,39 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
         <v>132</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>145</v>
+        <v>68</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2612,19 +2612,19 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>42</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>33</v>
@@ -2633,7 +2633,7 @@
         <v>27</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>8</v>
@@ -2671,19 +2671,19 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>18</v>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43" s="12" t="n">
         <v>73</v>
@@ -2742,7 +2742,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>31</v>
@@ -2765,7 +2765,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA FERRARESE 166</t>
+          <t>VIALE DELL'INDUSTRIA 44</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2789,42 +2789,42 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>99</v>
+        <v>222</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>78</v>
+        <v>257</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>127</v>
+        <v>258</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>VIALE DELL'INDUSTRIA 44</t>
+          <t>VIA FERRARESE 166</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2848,35 +2848,35 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>226</v>
+        <v>92</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>257</v>
+        <v>78</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>260</v>
+        <v>127</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2907,19 +2907,19 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>29</v>
@@ -2928,7 +2928,7 @@
         <v>28</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>14</v>
@@ -2966,19 +2966,19 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>34</v>
@@ -2987,7 +2987,7 @@
         <v>20</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>2</v>
@@ -3025,10 +3025,10 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>2</v>
@@ -3037,7 +3037,7 @@
         <v>10</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>19</v>
@@ -3046,10 +3046,10 @@
         <v>33</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G49" s="12" t="n">
         <v>73</v>
@@ -3096,7 +3096,7 @@
         <v>13</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>16</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G50" s="12" t="n">
         <v>85</v>
@@ -3155,7 +3155,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="K50" s="12" t="n">
         <v>14</v>
@@ -3164,14 +3164,14 @@
         <v>26</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="N50" s="12" t="n">
         <v>16</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3202,19 +3202,19 @@
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H51" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>11</v>
@@ -3223,7 +3223,7 @@
         <v>41</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N51" s="12" t="n">
         <v>4</v>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H52" s="12" t="n">
         <v>34</v>
@@ -3273,7 +3273,7 @@
         <v>226</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="K52" s="12" t="n">
         <v>17</v>
@@ -3323,16 +3323,16 @@
         <v>75</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H53" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K53" s="12" t="n">
         <v>7</v>
@@ -3341,10 +3341,10 @@
         <v>35</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>24</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K54" s="12" t="n">
         <v>17</v>
@@ -3400,7 +3400,7 @@
         <v>22</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="N54" s="12" t="n">
         <v>3</v>
@@ -3450,7 +3450,7 @@
         <v>0</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="K55" s="12" t="n">
         <v>26</v>
@@ -3473,7 +3473,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>VIA STALINGRADO 59/4</t>
+          <t>VIA G. DOZZA, 33</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3497,42 +3497,42 @@
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>112</v>
+        <v>2</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>VIA G. DOZZA, 33</t>
+          <t>VIA STALINGRADO 59/4</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3556,35 +3556,35 @@
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K57" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L57" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="M57" s="12" t="n">
+        <v>168</v>
+      </c>
+      <c r="N57" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L57" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="M57" s="12" t="n">
-        <v>157</v>
-      </c>
-      <c r="N57" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3618,16 +3618,16 @@
         <v>67</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K58" s="12" t="n">
         <v>10</v>
@@ -3636,7 +3636,7 @@
         <v>24</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="N58" s="12" t="n">
         <v>9</v>
@@ -3650,17 +3650,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05408</t>
+          <t>04812</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>CHIUSI</t>
+          <t>FIRENZE</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>S.S. 146 - KM. 2+180 SNC</t>
+          <t>VIA DEL ROMITO</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3670,35 +3670,35 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>CORSI PAOLA</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
         <v>66</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K59" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L59" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="M59" s="12" t="n">
+        <v>206</v>
+      </c>
+      <c r="N59" s="12" t="n">
         <v>14</v>
-      </c>
-      <c r="M59" s="12" t="n">
-        <v>127</v>
-      </c>
-      <c r="N59" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3709,17 +3709,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>05536</t>
+          <t>05408</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>CHIUSI</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>VIA ALDINI 186</t>
+          <t>S.S. 146 - KM. 2+180 SNC</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3729,35 +3729,35 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="N60" s="12" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3768,17 +3768,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04812</t>
+          <t>05530</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>FIRENZE</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>VIA DEL ROMITO</t>
+          <t>VIA MASSARENTI, 221/3</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3788,46 +3788,46 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>CORSI PAOLA</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
         <v>64</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>211</v>
+        <v>94</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>05530</t>
+          <t>05536</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>VIA MASSARENTI, 221/3</t>
+          <t>VIA ALDINI 186</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3851,35 +3851,35 @@
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>2</v>
+        <v>142</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3910,19 +3910,19 @@
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H63" s="12" t="n">
         <v>43</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K63" s="12" t="n">
         <v>24</v>
@@ -3972,16 +3972,16 @@
         <v>59</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K64" s="12" t="n">
         <v>15</v>
@@ -3990,10 +3990,10 @@
         <v>19</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="N64" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G65" s="12" t="n">
         <v>6</v>
@@ -4040,7 +4040,7 @@
         <v>2</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K65" s="12" t="n">
         <v>17</v>
@@ -4049,7 +4049,7 @@
         <v>4</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N65" s="12" t="n">
         <v>1</v>
@@ -4063,17 +4063,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>04653</t>
+          <t>06259</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLION FIORENTINO</t>
+          <t>MODENA</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>SS 71 KM.131+073</t>
+          <t>VIA CANALETTO, 62</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4083,35 +4083,35 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>PIETRANTONIO GIULIANO</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -4122,17 +4122,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06259</t>
+          <t>04653</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>MODENA</t>
+          <t>CASTIGLION FIORENTINO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>VIA CANALETTO, 62</t>
+          <t>SS 71 KM.131+073</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4142,35 +4142,35 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>PIETRANTONIO GIULIANO</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I67" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="J67" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="J67" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="K67" s="12" t="n">
-        <v>16</v>
-      </c>
       <c r="L67" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>127</v>
+        <v>58</v>
       </c>
       <c r="N67" s="12" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H68" s="12" t="n">
         <v>4</v>
@@ -4217,7 +4217,7 @@
         <v>67</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K68" s="12" t="n">
         <v>11</v>
@@ -4240,17 +4240,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>34201</t>
+          <t>04601</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SANTA CROCE SULL'ARNO</t>
+          <t>AREZZO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>VIA PROVINCIALE NUOVA FRANCESCA KM 8,000 SNC</t>
+          <t>SS71 KM141+597 S.ANASTASIO LOC.OLMO</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4260,56 +4260,56 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>ZOTTI VINCENZO MARIA</t>
+          <t>PETRELLI DANIELE</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K69" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L69" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L69" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="M69" s="12" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="N69" s="12" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>06363</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>BOMPORTO</t>
+          <t>SANTA CROCE SULL'ARNO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>VIA GORGHETTO, 2</t>
+          <t>VIA PROVINCIALE NUOVA FRANCESCA KM 8,000 SNC</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4319,56 +4319,56 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>ZOTTI VINCENZO MARIA</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
         <v>42</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="N70" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>05055</t>
+          <t>06363</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>BOMPORTO</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>FRAZ-STAGNO SS-1</t>
+          <t>VIA GORGHETTO, 2</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4378,35 +4378,35 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
         <v>42</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N71" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4417,17 +4417,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>54066</t>
+          <t>05055</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>PIETRASANTA</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>UNITA' D'ITALIA 9</t>
+          <t>FRAZ-STAGNO SS-1</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4437,46 +4437,46 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
         <v>42</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="N72" s="12" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>04601</t>
+          <t>04677</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>SS71 KM141+597 S.ANASTASIO LOC.OLMO</t>
+          <t>S.S. 71, KM. 151 LOC.CECILIANO</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4500,52 +4500,52 @@
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>04677</t>
+          <t>54066</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>AREZZO</t>
+          <t>PIETRASANTA</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>S.S. 71, KM. 151 LOC.CECILIANO</t>
+          <t>UNITA' D'ITALIA 9</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4555,35 +4555,35 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>PETRELLI DANIELE</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>53</v>
+        <v>118</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="N74" s="12" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4594,17 +4594,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>05099</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>VIA CRISTOFORO COLOMBO 36</t>
+          <t>S.G.C. FI/PI/LI LOC.GRECCIANO SUD 64</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4614,35 +4614,35 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>MURGO LORENZO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I75" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="J75" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L75" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="M75" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="N75" s="12" t="n">
         <v>19</v>
-      </c>
-      <c r="J75" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="K75" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L75" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="M75" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="N75" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G76" s="12" t="n">
         <v>3</v>
@@ -4689,7 +4689,7 @@
         <v>3</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K76" s="12" t="n">
         <v>8</v>
@@ -4705,24 +4705,24 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05099</t>
+          <t>54044</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>SIENA</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>S.G.C. FI/PI/LI LOC.GRECCIANO SUD 64</t>
+          <t>VIALE BRACCI SNC</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4732,39 +4732,39 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>AMELIO ANTONIO FRANCESCO</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="N77" s="12" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H78" s="12" t="n">
         <v>11</v>
@@ -4807,7 +4807,7 @@
         <v>66</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K78" s="12" t="n">
         <v>7</v>
@@ -4816,10 +4816,10 @@
         <v>7</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="N78" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4830,17 +4830,17 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>54044</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SIENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>VIALE BRACCI SNC</t>
+          <t>VIA CRISTOFORO COLOMBO 36</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4850,39 +4850,39 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
+          <t>MURGO LORENZO</t>
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="N79" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
         <v>23</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H80" s="12" t="n">
         <v>2</v>
@@ -4925,7 +4925,7 @@
         <v>7</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K80" s="12" t="n">
         <v>2</v>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G81" s="12" t="n">
         <v>0</v>
@@ -4984,7 +4984,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K81" s="12" t="n">
         <v>6</v>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
         </is>
       </c>
       <c r="F82" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G82" s="12" t="n">
         <v>30</v>
@@ -5043,7 +5043,7 @@
         <v>4</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K82" s="12" t="n">
         <v>3</v>
@@ -5052,14 +5052,14 @@
         <v>0</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="N82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K83" s="12" t="n">
         <v>3</v>
@@ -5161,7 +5161,7 @@
         <v>3</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K84" s="12" t="n">
         <v>5</v>
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="F85" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H85" s="12" t="n">
         <v>1</v>
@@ -5220,7 +5220,7 @@
         <v>9</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K85" s="12" t="n">
         <v>1</v>
@@ -5229,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N85" s="12" t="n">
         <v>1</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="F86" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G86" s="12" t="n">
         <v>4</v>
@@ -5279,7 +5279,7 @@
         <v>5</v>
       </c>
       <c r="J86" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K86" s="12" t="n">
         <v>1</v>
@@ -5295,7 +5295,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="H88" s="12" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J89" s="12" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H90" s="12" t="n">
         <v>0</v>
@@ -5565,13 +5565,13 @@
         <v>0</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>523</v>
+        <v>509</v>
       </c>
       <c r="H91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>807</v>
+        <v>797</v>
       </c>
       <c r="J91" s="12" t="n">
         <v>0</v>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
